--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ДОБРИЧКА/ОБЩИНА ДОБРИЧКА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ДОБРИЧКА/ОБЩИНА ДОБРИЧКА.xlsx
@@ -667,7 +667,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -677,12 +677,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -732,17 +726,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ДОБРИЧКА/ОБЩИНА ДОБРИЧКА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ДОБРИЧКА/ОБЩИНА ДОБРИЧКА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="269">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,6 +52,12 @@
     <t>Час</t>
   </si>
   <si>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-06-01</t>
   </si>
   <si>
@@ -112,10 +121,19 @@
     <t>2026-06-25</t>
   </si>
   <si>
-    <t>Добрич Добруджа</t>
-  </si>
-  <si>
-    <t>Севлиево</t>
+    <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>1156 Добрич бул. Добруджа</t>
+  </si>
+  <si>
+    <t>1186 Севлиево</t>
   </si>
   <si>
     <t>ТХ2626КХ</t>
@@ -154,21 +172,21 @@
     <t>ТХ0224АТ</t>
   </si>
   <si>
+    <t>ТХ1573ТМ</t>
+  </si>
+  <si>
     <t>ТХ0344АР</t>
   </si>
   <si>
-    <t>ТХ1573ТМ</t>
-  </si>
-  <si>
     <t>ТХ8900АТ</t>
   </si>
   <si>
+    <t>ТХ8896АТ</t>
+  </si>
+  <si>
     <t>ТХ4225ХР</t>
   </si>
   <si>
-    <t>ТХ8896АТ</t>
-  </si>
-  <si>
     <t>ТХ3500РХ</t>
   </si>
   <si>
@@ -181,10 +199,16 @@
     <t>ТХ4223ХР</t>
   </si>
   <si>
+    <t>ТХ7827ТМ</t>
+  </si>
+  <si>
     <t>ТХ1578ТМ</t>
   </si>
   <si>
-    <t>ТХ7827ТМ</t>
+    <t>ТХ0259МТ</t>
+  </si>
+  <si>
+    <t>ТХ1932РХ</t>
   </si>
   <si>
     <t>78970151027720682</t>
@@ -223,21 +247,21 @@
     <t>78970151027720856</t>
   </si>
   <si>
+    <t>78970151027720997</t>
+  </si>
+  <si>
     <t>78970151027720914</t>
   </si>
   <si>
-    <t>78970151027720997</t>
-  </si>
-  <si>
     <t>78970151027720880</t>
   </si>
   <si>
+    <t>78970151027721037</t>
+  </si>
+  <si>
     <t>78970151027720872</t>
   </si>
   <si>
-    <t>78970151027721037</t>
-  </si>
-  <si>
     <t>78970151027720708</t>
   </si>
   <si>
@@ -250,10 +274,16 @@
     <t>78970151027720740</t>
   </si>
   <si>
+    <t>78970151027721003</t>
+  </si>
+  <si>
     <t>78970151027720989</t>
   </si>
   <si>
-    <t>78970151027721003</t>
+    <t>78970151027720930</t>
+  </si>
+  <si>
+    <t>78970151027720716</t>
   </si>
   <si>
     <t>95 EKONOMY UNLEADED</t>
@@ -268,181 +298,511 @@
     <t>DIESEL DOUBLE FILTERED</t>
   </si>
   <si>
-    <t>2026-06-01 11:33:03</t>
-  </si>
-  <si>
-    <t>2026-06-01 21:08:10</t>
-  </si>
-  <si>
-    <t>2026-06-02 15:45:08</t>
-  </si>
-  <si>
-    <t>2026-06-03 10:23:34</t>
-  </si>
-  <si>
-    <t>2026-06-03 11:31:05</t>
-  </si>
-  <si>
-    <t>2026-06-03 15:47:47</t>
-  </si>
-  <si>
-    <t>2026-06-04 09:07:21</t>
-  </si>
-  <si>
-    <t>2026-06-04 09:46:19</t>
-  </si>
-  <si>
-    <t>2026-06-04 16:25:58</t>
-  </si>
-  <si>
-    <t>2026-06-04 16:42:44</t>
-  </si>
-  <si>
-    <t>2026-06-04 17:28:01</t>
-  </si>
-  <si>
-    <t>2026-06-05 08:01:43</t>
-  </si>
-  <si>
-    <t>2026-06-05 08:43:08</t>
-  </si>
-  <si>
-    <t>2026-06-05 17:09:53</t>
-  </si>
-  <si>
-    <t>2026-06-08 12:48:00</t>
-  </si>
-  <si>
-    <t>2026-06-09 13:05:16</t>
-  </si>
-  <si>
-    <t>2026-06-09 13:54:29</t>
-  </si>
-  <si>
-    <t>2026-06-09 13:54:59</t>
-  </si>
-  <si>
-    <t>2026-06-10 08:48:21</t>
-  </si>
-  <si>
-    <t>2026-06-10 17:46:07</t>
-  </si>
-  <si>
-    <t>2026-06-11 07:29:19</t>
-  </si>
-  <si>
-    <t>2026-06-11 08:52:44</t>
-  </si>
-  <si>
-    <t>2026-06-11 16:59:45</t>
-  </si>
-  <si>
-    <t>2026-06-12 10:51:51</t>
-  </si>
-  <si>
-    <t>2026-06-12 15:31:40</t>
-  </si>
-  <si>
-    <t>2026-06-13 08:50:19</t>
-  </si>
-  <si>
-    <t>2026-06-15 08:44:37</t>
-  </si>
-  <si>
-    <t>2026-06-15 13:10:08</t>
-  </si>
-  <si>
-    <t>2026-06-15 13:37:33</t>
-  </si>
-  <si>
-    <t>2026-06-16 08:17:36</t>
-  </si>
-  <si>
-    <t>2026-06-16 08:30:09</t>
-  </si>
-  <si>
-    <t>2026-06-16 13:58:52</t>
-  </si>
-  <si>
-    <t>2026-06-16 14:24:29</t>
-  </si>
-  <si>
-    <t>2026-06-17 08:54:25</t>
-  </si>
-  <si>
-    <t>2026-06-17 08:56:16</t>
-  </si>
-  <si>
-    <t>2026-06-17 12:16:36</t>
-  </si>
-  <si>
-    <t>2026-06-17 13:46:31</t>
-  </si>
-  <si>
-    <t>2026-06-17 17:03:53</t>
-  </si>
-  <si>
-    <t>2026-06-18 13:20:49</t>
-  </si>
-  <si>
-    <t>2026-06-18 13:43:39</t>
-  </si>
-  <si>
-    <t>2026-06-19 09:20:43</t>
-  </si>
-  <si>
-    <t>2026-06-19 11:40:30</t>
-  </si>
-  <si>
-    <t>2026-06-19 12:28:47</t>
-  </si>
-  <si>
-    <t>2026-06-19 13:24:51</t>
-  </si>
-  <si>
-    <t>2026-06-20 13:22:39</t>
-  </si>
-  <si>
-    <t>2026-06-22 11:12:21</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:20:30</t>
-  </si>
-  <si>
-    <t>2026-06-22 13:10:18</t>
-  </si>
-  <si>
-    <t>2026-06-22 14:08:07</t>
-  </si>
-  <si>
-    <t>2026-06-23 08:36:47</t>
-  </si>
-  <si>
-    <t>2026-06-23 08:47:01</t>
-  </si>
-  <si>
-    <t>2026-06-23 10:58:19</t>
-  </si>
-  <si>
-    <t>2026-06-23 17:06:15</t>
-  </si>
-  <si>
-    <t>2026-06-24 12:24:47</t>
-  </si>
-  <si>
-    <t>2026-06-25 07:38:36</t>
-  </si>
-  <si>
-    <t>2026-06-25 08:23:12</t>
-  </si>
-  <si>
-    <t>2026-06-25 08:34:14</t>
-  </si>
-  <si>
-    <t>2026-06-25 11:26:18</t>
-  </si>
-  <si>
-    <t>2026-06-25 16:30:21</t>
+    <t>10 Л. ДOБABKA ADBLUE ДИЗEЛOBИ ДBИГATEЛИ</t>
+  </si>
+  <si>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>PC</t>
+  </si>
+  <si>
+    <t>11:32:00</t>
+  </si>
+  <si>
+    <t>21:08:00</t>
+  </si>
+  <si>
+    <t>15:45:00</t>
+  </si>
+  <si>
+    <t>10:23:00</t>
+  </si>
+  <si>
+    <t>11:30:00</t>
+  </si>
+  <si>
+    <t>15:47:00</t>
+  </si>
+  <si>
+    <t>09:46:00</t>
+  </si>
+  <si>
+    <t>09:07:00</t>
+  </si>
+  <si>
+    <t>16:42:00</t>
+  </si>
+  <si>
+    <t>16:25:00</t>
+  </si>
+  <si>
+    <t>17:27:00</t>
+  </si>
+  <si>
+    <t>08:01:00</t>
+  </si>
+  <si>
+    <t>08:42:00</t>
+  </si>
+  <si>
+    <t>17:09:00</t>
+  </si>
+  <si>
+    <t>12:47:00</t>
+  </si>
+  <si>
+    <t>13:05:00</t>
+  </si>
+  <si>
+    <t>13:54:00</t>
+  </si>
+  <si>
+    <t>08:48:00</t>
+  </si>
+  <si>
+    <t>17:46:00</t>
+  </si>
+  <si>
+    <t>08:52:00</t>
+  </si>
+  <si>
+    <t>07:29:00</t>
+  </si>
+  <si>
+    <t>16:59:00</t>
+  </si>
+  <si>
+    <t>10:51:00</t>
+  </si>
+  <si>
+    <t>15:31:00</t>
+  </si>
+  <si>
+    <t>08:50:00</t>
+  </si>
+  <si>
+    <t>08:44:00</t>
+  </si>
+  <si>
+    <t>13:37:00</t>
+  </si>
+  <si>
+    <t>13:09:00</t>
+  </si>
+  <si>
+    <t>08:17:00</t>
+  </si>
+  <si>
+    <t>08:30:00</t>
+  </si>
+  <si>
+    <t>13:58:00</t>
+  </si>
+  <si>
+    <t>14:24:00</t>
+  </si>
+  <si>
+    <t>08:56:00</t>
+  </si>
+  <si>
+    <t>08:54:00</t>
+  </si>
+  <si>
+    <t>12:16:00</t>
+  </si>
+  <si>
+    <t>13:46:00</t>
+  </si>
+  <si>
+    <t>17:03:00</t>
+  </si>
+  <si>
+    <t>13:20:00</t>
+  </si>
+  <si>
+    <t>13:43:00</t>
+  </si>
+  <si>
+    <t>09:20:00</t>
+  </si>
+  <si>
+    <t>13:24:00</t>
+  </si>
+  <si>
+    <t>12:28:00</t>
+  </si>
+  <si>
+    <t>11:40:00</t>
+  </si>
+  <si>
+    <t>13:22:00</t>
+  </si>
+  <si>
+    <t>11:12:00</t>
+  </si>
+  <si>
+    <t>14:07:00</t>
+  </si>
+  <si>
+    <t>12:20:00</t>
+  </si>
+  <si>
+    <t>13:10:00</t>
+  </si>
+  <si>
+    <t>08:46:00</t>
+  </si>
+  <si>
+    <t>10:58:00</t>
+  </si>
+  <si>
+    <t>08:36:00</t>
+  </si>
+  <si>
+    <t>17:06:00</t>
+  </si>
+  <si>
+    <t>12:24:00</t>
+  </si>
+  <si>
+    <t>07:38:00</t>
+  </si>
+  <si>
+    <t>08:34:00</t>
+  </si>
+  <si>
+    <t>08:23:00</t>
+  </si>
+  <si>
+    <t>11:26:00</t>
+  </si>
+  <si>
+    <t>16:30:00</t>
+  </si>
+  <si>
+    <t>13:00:00</t>
+  </si>
+  <si>
+    <t>16:56:00</t>
+  </si>
+  <si>
+    <t>17:26:00</t>
+  </si>
+  <si>
+    <t>16:00:00</t>
+  </si>
+  <si>
+    <t>13:08:00</t>
+  </si>
+  <si>
+    <t>10:37:00</t>
+  </si>
+  <si>
+    <t>16:05:00</t>
+  </si>
+  <si>
+    <t>08:40:00</t>
+  </si>
+  <si>
+    <t>12:02:00</t>
+  </si>
+  <si>
+    <t>14:15:00</t>
+  </si>
+  <si>
+    <t>13:07:00</t>
+  </si>
+  <si>
+    <t>12:00:00</t>
+  </si>
+  <si>
+    <t>12:25:00</t>
+  </si>
+  <si>
+    <t>13:19:00</t>
+  </si>
+  <si>
+    <t>14:53:00</t>
+  </si>
+  <si>
+    <t>13:28:00</t>
+  </si>
+  <si>
+    <t>14:13:00</t>
+  </si>
+  <si>
+    <t>13:40:00</t>
+  </si>
+  <si>
+    <t>14:55:00</t>
+  </si>
+  <si>
+    <t>15:39:00</t>
+  </si>
+  <si>
+    <t>15:37:00</t>
+  </si>
+  <si>
+    <t>16:57:00</t>
+  </si>
+  <si>
+    <t>16:51:00</t>
+  </si>
+  <si>
+    <t>3232727386 3232727386</t>
+  </si>
+  <si>
+    <t>3232727447 3232727447</t>
+  </si>
+  <si>
+    <t>3232775336 3232775336</t>
+  </si>
+  <si>
+    <t>3232813781 3232813781</t>
+  </si>
+  <si>
+    <t>3232819508 3232819508</t>
+  </si>
+  <si>
+    <t>3232821710 3232821710</t>
+  </si>
+  <si>
+    <t>3232860920 3232860920</t>
+  </si>
+  <si>
+    <t>3232863128 3232863128</t>
+  </si>
+  <si>
+    <t>3232866883 3232866883</t>
+  </si>
+  <si>
+    <t>3232867867 3232867867</t>
+  </si>
+  <si>
+    <t>3232870408 3232870408</t>
+  </si>
+  <si>
+    <t>3232918516 3232918516</t>
+  </si>
+  <si>
+    <t>3232919412 3232919412</t>
+  </si>
+  <si>
+    <t>3232924416 3232924416</t>
+  </si>
+  <si>
+    <t>3233063819 3233063819</t>
+  </si>
+  <si>
+    <t>3233107792 3233107792</t>
+  </si>
+  <si>
+    <t>3233108095 3233108095</t>
+  </si>
+  <si>
+    <t>3233108479 3233108479</t>
+  </si>
+  <si>
+    <t>3233155511 3233155511</t>
+  </si>
+  <si>
+    <t>3233159127 3233159127</t>
+  </si>
+  <si>
+    <t>3233195772 3233195772</t>
+  </si>
+  <si>
+    <t>3233203434 3233203434</t>
+  </si>
+  <si>
+    <t>3233208254 3233208254</t>
+  </si>
+  <si>
+    <t>3233260265 3233260265</t>
+  </si>
+  <si>
+    <t>3233264536 3233264536</t>
+  </si>
+  <si>
+    <t>3233307136 3233307136</t>
+  </si>
+  <si>
+    <t>3233385491 3233385491</t>
+  </si>
+  <si>
+    <t>3233397455 3233397455</t>
+  </si>
+  <si>
+    <t>3233401443 3233401443</t>
+  </si>
+  <si>
+    <t>3233435293 3233435293</t>
+  </si>
+  <si>
+    <t>3233439498 3233439498</t>
+  </si>
+  <si>
+    <t>3233448032 3233448032</t>
+  </si>
+  <si>
+    <t>3233448733 3233448733</t>
+  </si>
+  <si>
+    <t>3233489285 3233489285</t>
+  </si>
+  <si>
+    <t>3233490622 3233490622</t>
+  </si>
+  <si>
+    <t>3233491980 3233491980</t>
+  </si>
+  <si>
+    <t>3233493771 3233493771</t>
+  </si>
+  <si>
+    <t>3233497026 3233497026</t>
+  </si>
+  <si>
+    <t>3233541383 3233541383</t>
+  </si>
+  <si>
+    <t>3233543503 3233543503</t>
+  </si>
+  <si>
+    <t>3233591381 3233591381</t>
+  </si>
+  <si>
+    <t>3233594492 3233594492</t>
+  </si>
+  <si>
+    <t>3233595506 3233595506</t>
+  </si>
+  <si>
+    <t>3233586588 3233586588</t>
+  </si>
+  <si>
+    <t>3233645485 3233645485</t>
+  </si>
+  <si>
+    <t>3233732601 3233732601</t>
+  </si>
+  <si>
+    <t>3233732947 3233732947</t>
+  </si>
+  <si>
+    <t>3233733115 3233733115</t>
+  </si>
+  <si>
+    <t>3233733717 3233733717</t>
+  </si>
+  <si>
+    <t>3233759284 3233759284</t>
+  </si>
+  <si>
+    <t>3233764276 3233764276</t>
+  </si>
+  <si>
+    <t>3233769778 3233769778</t>
+  </si>
+  <si>
+    <t>3233776296 3233776296</t>
+  </si>
+  <si>
+    <t>3233821417 3233821417</t>
+  </si>
+  <si>
+    <t>3233859898 3233859898</t>
+  </si>
+  <si>
+    <t>3233865837 3233865837</t>
+  </si>
+  <si>
+    <t>3233866109 3233866109</t>
+  </si>
+  <si>
+    <t>3233868060 3233868060</t>
+  </si>
+  <si>
+    <t>3233871384 3233871384</t>
+  </si>
+  <si>
+    <t>3233959912 3233959912</t>
+  </si>
+  <si>
+    <t>3234066270 3234066270</t>
+  </si>
+  <si>
+    <t>3234067117 3234067117</t>
+  </si>
+  <si>
+    <t>3234069379 3234069379</t>
+  </si>
+  <si>
+    <t>3234069632 3234069632</t>
+  </si>
+  <si>
+    <t>3234099335 3234099335</t>
+  </si>
+  <si>
+    <t>3234099699 3234099699</t>
+  </si>
+  <si>
+    <t>3234101385 3234101385</t>
+  </si>
+  <si>
+    <t>3234103598 3234103598</t>
+  </si>
+  <si>
+    <t>3234108294 3234108294</t>
+  </si>
+  <si>
+    <t>3234110035 3234110035</t>
+  </si>
+  <si>
+    <t>3234110438 3234110438</t>
+  </si>
+  <si>
+    <t>3234111281 3234111281</t>
+  </si>
+  <si>
+    <t>3234113502 3234113502</t>
+  </si>
+  <si>
+    <t>3234114308 3234114308</t>
+  </si>
+  <si>
+    <t>3234114441 3234114441</t>
+  </si>
+  <si>
+    <t>3234114452 3234114452</t>
+  </si>
+  <si>
+    <t>3234115273 3234115273</t>
+  </si>
+  <si>
+    <t>3234115420 3234115420</t>
+  </si>
+  <si>
+    <t>3234115765 3234115765</t>
+  </si>
+  <si>
+    <t>3234115816 3234115816</t>
+  </si>
+  <si>
+    <t>3234117928 3234117928</t>
+  </si>
+  <si>
+    <t>3234118334 3234118334</t>
+  </si>
+  <si>
+    <t>3234118910 3234118910</t>
+  </si>
+  <si>
+    <t>3234118995 3234118995</t>
+  </si>
+  <si>
+    <t>3234121513 3234121513</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОБЩИНА ДОБРИЧКА</t>
@@ -860,7 +1220,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K69"/>
+  <dimension ref="A1:N97"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -869,14 +1229,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -910,2203 +1273,3951 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="E2" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F2">
         <v>12</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H2">
         <v>1.53</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>18.36</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.57</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>18.84</v>
       </c>
-      <c r="K2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2" t="s">
+        <v>97</v>
+      </c>
+      <c r="M2">
+        <v>74500</v>
+      </c>
+      <c r="N2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="E3" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="F3">
         <v>36</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>95</v>
+      </c>
+      <c r="H3">
         <v>1.65</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>59.4</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.69</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>60.84</v>
       </c>
-      <c r="K3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="L3" t="s">
+        <v>98</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="E4" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="F4">
         <v>36</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>95</v>
+      </c>
+      <c r="H4">
         <v>1.77</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>63.72</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.82</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>65.52</v>
       </c>
-      <c r="K4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="L4" t="s">
+        <v>99</v>
+      </c>
+      <c r="M4">
+        <v>179980</v>
+      </c>
+      <c r="N4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="E5" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F5">
         <v>20.03</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>95</v>
+      </c>
+      <c r="H5">
         <v>1.53</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>30.65</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.57</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>31.45</v>
       </c>
-      <c r="K5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="L5" t="s">
+        <v>100</v>
+      </c>
+      <c r="M5">
+        <v>324535</v>
+      </c>
+      <c r="N5" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="E6" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F6">
         <v>24</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>95</v>
+      </c>
+      <c r="H6">
         <v>1.53</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>36.72</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.57</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>37.68</v>
       </c>
-      <c r="K6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="L6" t="s">
+        <v>101</v>
+      </c>
+      <c r="M6">
+        <v>5600</v>
+      </c>
+      <c r="N6" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="E7" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F7">
         <v>15.01</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>95</v>
+      </c>
+      <c r="H7">
         <v>1.53</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>22.97</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.57</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>23.57</v>
       </c>
-      <c r="K7" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="L7" t="s">
+        <v>102</v>
+      </c>
+      <c r="M7">
+        <v>74645</v>
+      </c>
+      <c r="N7" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E8" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="F8">
+        <v>30</v>
+      </c>
+      <c r="G8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H8">
+        <v>1.53</v>
+      </c>
+      <c r="I8" s="1">
+        <v>45.9</v>
+      </c>
+      <c r="J8">
+        <v>1.57</v>
+      </c>
+      <c r="K8" s="1">
+        <v>47.1</v>
+      </c>
+      <c r="L8" t="s">
+        <v>103</v>
+      </c>
+      <c r="M8">
+        <v>324995</v>
+      </c>
+      <c r="N8" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" t="s">
+        <v>91</v>
+      </c>
+      <c r="F9">
         <v>42.32</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H9">
         <v>1.62</v>
       </c>
-      <c r="H8">
+      <c r="I9" s="1">
         <v>68.56</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J9">
         <v>1.66</v>
       </c>
-      <c r="J8">
+      <c r="K9" s="1">
         <v>70.25</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L9" t="s">
+        <v>104</v>
+      </c>
+      <c r="M9">
+        <v>39809</v>
+      </c>
+      <c r="N9" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E10" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" t="s">
-        <v>60</v>
-      </c>
-      <c r="E9" t="s">
-        <v>80</v>
-      </c>
-      <c r="F9">
-        <v>30</v>
-      </c>
-      <c r="G9" s="1">
+      <c r="F10">
+        <v>6</v>
+      </c>
+      <c r="G10" t="s">
+        <v>95</v>
+      </c>
+      <c r="H10">
         <v>1.53</v>
       </c>
-      <c r="H9">
-        <v>45.9</v>
-      </c>
-      <c r="I9" s="1">
+      <c r="I10" s="1">
+        <v>9.18</v>
+      </c>
+      <c r="J10">
         <v>1.57</v>
       </c>
-      <c r="J9">
-        <v>47.1</v>
-      </c>
-      <c r="K9" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" t="s">
-        <v>59</v>
-      </c>
-      <c r="E10" t="s">
-        <v>82</v>
-      </c>
-      <c r="F10">
+      <c r="K10" s="1">
+        <v>9.42</v>
+      </c>
+      <c r="L10" t="s">
+        <v>105</v>
+      </c>
+      <c r="M10">
+        <v>325075</v>
+      </c>
+      <c r="N10" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" t="s">
+        <v>67</v>
+      </c>
+      <c r="E11" t="s">
+        <v>92</v>
+      </c>
+      <c r="F11">
         <v>29</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G11" t="s">
+        <v>95</v>
+      </c>
+      <c r="H11">
         <v>1.77</v>
       </c>
-      <c r="H10">
+      <c r="I11" s="1">
         <v>51.33</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J11">
         <v>1.82</v>
       </c>
-      <c r="J10">
+      <c r="K11" s="1">
         <v>52.78</v>
       </c>
-      <c r="K10" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" t="s">
-        <v>60</v>
-      </c>
-      <c r="E11" t="s">
-        <v>80</v>
-      </c>
-      <c r="F11">
-        <v>6</v>
-      </c>
-      <c r="G11" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="H11">
-        <v>9.18</v>
-      </c>
-      <c r="I11" s="1">
-        <v>1.57</v>
-      </c>
-      <c r="J11">
-        <v>9.42</v>
-      </c>
-      <c r="K11" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="L11" t="s">
+        <v>106</v>
+      </c>
+      <c r="M11">
+        <v>180314</v>
+      </c>
+      <c r="N11" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="E12" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F12">
         <v>16</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" t="s">
+        <v>95</v>
+      </c>
+      <c r="H12">
         <v>1.53</v>
       </c>
-      <c r="H12">
+      <c r="I12" s="1">
         <v>24.48</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12">
         <v>1.57</v>
       </c>
-      <c r="J12">
+      <c r="K12" s="1">
         <v>25.12</v>
       </c>
-      <c r="K12" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="L12" t="s">
+        <v>107</v>
+      </c>
+      <c r="M12">
+        <v>74830</v>
+      </c>
+      <c r="N12" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="E13" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F13">
         <v>42.66</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" t="s">
+        <v>95</v>
+      </c>
+      <c r="H13">
         <v>1.53</v>
       </c>
-      <c r="H13">
+      <c r="I13" s="1">
         <v>65.27</v>
       </c>
-      <c r="I13" s="1">
+      <c r="J13">
         <v>1.57</v>
       </c>
-      <c r="J13">
+      <c r="K13" s="1">
         <v>66.98</v>
       </c>
-      <c r="K13" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
+      <c r="L13" t="s">
+        <v>108</v>
+      </c>
+      <c r="M13">
+        <v>232970</v>
+      </c>
+      <c r="N13" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="E14" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="F14">
         <v>37</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14" t="s">
+        <v>95</v>
+      </c>
+      <c r="H14">
         <v>1.62</v>
       </c>
-      <c r="H14">
+      <c r="I14" s="1">
         <v>59.94</v>
       </c>
-      <c r="I14" s="1">
+      <c r="J14">
         <v>1.66</v>
       </c>
-      <c r="J14">
+      <c r="K14" s="1">
         <v>61.42</v>
       </c>
-      <c r="K14" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
+      <c r="L14" t="s">
+        <v>109</v>
+      </c>
+      <c r="M14">
+        <v>241005</v>
+      </c>
+      <c r="N14" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C15" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E15" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="F15">
         <v>50</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G15" t="s">
+        <v>95</v>
+      </c>
+      <c r="H15">
         <v>1.62</v>
       </c>
-      <c r="H15">
+      <c r="I15" s="1">
         <v>81</v>
       </c>
-      <c r="I15" s="1">
+      <c r="J15">
         <v>1.66</v>
       </c>
-      <c r="J15">
+      <c r="K15" s="1">
         <v>83</v>
       </c>
-      <c r="K15" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
+      <c r="L15" t="s">
+        <v>110</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C16" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D16" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="E16" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="F16">
         <v>41</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G16" t="s">
+        <v>95</v>
+      </c>
+      <c r="H16">
         <v>1.76</v>
       </c>
-      <c r="H16">
+      <c r="I16" s="1">
         <v>72.16</v>
       </c>
-      <c r="I16" s="1">
+      <c r="J16">
         <v>1.81</v>
       </c>
-      <c r="J16">
+      <c r="K16" s="1">
         <v>74.20999999999999</v>
       </c>
-      <c r="K16" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
+      <c r="L16" t="s">
+        <v>111</v>
+      </c>
+      <c r="M16">
+        <v>180826</v>
+      </c>
+      <c r="N16" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C17" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="E17" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="F17">
         <v>50.18</v>
       </c>
-      <c r="G17" s="1">
+      <c r="G17" t="s">
+        <v>95</v>
+      </c>
+      <c r="H17">
         <v>1.6</v>
       </c>
-      <c r="H17">
+      <c r="I17" s="1">
         <v>80.29000000000001</v>
       </c>
-      <c r="I17" s="1">
+      <c r="J17">
         <v>1.64</v>
       </c>
-      <c r="J17">
+      <c r="K17" s="1">
         <v>82.3</v>
       </c>
-      <c r="K17" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
+      <c r="L17" t="s">
+        <v>112</v>
+      </c>
+      <c r="M17">
+        <v>282583</v>
+      </c>
+      <c r="N17" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D18" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="E18" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="F18">
-        <v>35</v>
-      </c>
-      <c r="G18" s="1">
-        <v>1.52</v>
+        <v>33.77</v>
+      </c>
+      <c r="G18" t="s">
+        <v>95</v>
       </c>
       <c r="H18">
-        <v>53.2</v>
+        <v>1.6</v>
       </c>
       <c r="I18" s="1">
-        <v>1.56</v>
+        <v>54.03</v>
       </c>
       <c r="J18">
-        <v>54.6</v>
-      </c>
-      <c r="K18" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
+        <v>1.64</v>
+      </c>
+      <c r="K18" s="1">
+        <v>55.38</v>
+      </c>
+      <c r="L18" t="s">
+        <v>113</v>
+      </c>
+      <c r="M18">
+        <v>254100</v>
+      </c>
+      <c r="N18" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s">
         <v>44</v>
       </c>
       <c r="D19" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E19" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="F19">
-        <v>33.77</v>
-      </c>
-      <c r="G19" s="1">
-        <v>1.6</v>
+        <v>35</v>
+      </c>
+      <c r="G19" t="s">
+        <v>95</v>
       </c>
       <c r="H19">
-        <v>54.03</v>
+        <v>1.52</v>
       </c>
       <c r="I19" s="1">
-        <v>1.64</v>
+        <v>53.2</v>
       </c>
       <c r="J19">
-        <v>55.38</v>
-      </c>
-      <c r="K19" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
+        <v>1.56</v>
+      </c>
+      <c r="K19" s="1">
+        <v>54.6</v>
+      </c>
+      <c r="L19" t="s">
+        <v>113</v>
+      </c>
+      <c r="M19">
+        <v>6130</v>
+      </c>
+      <c r="N19" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D20" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="E20" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F20">
         <v>25</v>
       </c>
-      <c r="G20" s="1">
+      <c r="G20" t="s">
+        <v>95</v>
+      </c>
+      <c r="H20">
         <v>1.52</v>
       </c>
-      <c r="H20">
-        <v>38</v>
-      </c>
       <c r="I20" s="1">
+        <v>38</v>
+      </c>
+      <c r="J20">
         <v>1.56</v>
       </c>
-      <c r="J20">
+      <c r="K20" s="1">
         <v>39</v>
       </c>
-      <c r="K20" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
+      <c r="L20" t="s">
+        <v>114</v>
+      </c>
+      <c r="M20">
+        <v>325430</v>
+      </c>
+      <c r="N20" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C21" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D21" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="E21" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="F21">
         <v>31.45</v>
       </c>
-      <c r="G21" s="1">
+      <c r="G21" t="s">
+        <v>95</v>
+      </c>
+      <c r="H21">
         <v>1.59</v>
       </c>
-      <c r="H21">
+      <c r="I21" s="1">
         <v>50.01</v>
       </c>
-      <c r="I21" s="1">
+      <c r="J21">
         <v>1.63</v>
       </c>
-      <c r="J21">
+      <c r="K21" s="1">
         <v>51.26</v>
       </c>
-      <c r="K21" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
+      <c r="L21" t="s">
+        <v>115</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C22" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D22" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E22" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="F22">
+        <v>15</v>
+      </c>
+      <c r="G22" t="s">
+        <v>95</v>
+      </c>
+      <c r="H22">
+        <v>1.52</v>
+      </c>
+      <c r="I22" s="1">
+        <v>22.8</v>
+      </c>
+      <c r="J22">
+        <v>1.56</v>
+      </c>
+      <c r="K22" s="1">
+        <v>23.4</v>
+      </c>
+      <c r="L22" t="s">
+        <v>116</v>
+      </c>
+      <c r="M22">
+        <v>9550</v>
+      </c>
+      <c r="N22" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" t="s">
+        <v>78</v>
+      </c>
+      <c r="E23" t="s">
+        <v>91</v>
+      </c>
+      <c r="F23">
         <v>45.96</v>
       </c>
-      <c r="G22" s="1">
+      <c r="G23" t="s">
+        <v>95</v>
+      </c>
+      <c r="H23">
         <v>1.58</v>
       </c>
-      <c r="H22">
+      <c r="I23" s="1">
         <v>72.62</v>
       </c>
-      <c r="I22" s="1">
+      <c r="J23">
         <v>1.62</v>
       </c>
-      <c r="J22">
+      <c r="K23" s="1">
         <v>74.45999999999999</v>
       </c>
-      <c r="K22" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="A23" t="s">
-        <v>19</v>
-      </c>
-      <c r="B23" t="s">
-        <v>32</v>
-      </c>
-      <c r="C23" t="s">
-        <v>47</v>
-      </c>
-      <c r="D23" t="s">
-        <v>70</v>
-      </c>
-      <c r="E23" t="s">
-        <v>80</v>
-      </c>
-      <c r="F23">
-        <v>15</v>
-      </c>
-      <c r="G23" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="H23">
-        <v>22.8</v>
-      </c>
-      <c r="I23" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="J23">
-        <v>23.4</v>
-      </c>
-      <c r="K23" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
+      <c r="L23" t="s">
+        <v>117</v>
+      </c>
+      <c r="M23">
+        <v>288600</v>
+      </c>
+      <c r="N23" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C24" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D24" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E24" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="F24">
         <v>48</v>
       </c>
-      <c r="G24" s="1">
+      <c r="G24" t="s">
+        <v>95</v>
+      </c>
+      <c r="H24">
         <v>1.58</v>
       </c>
-      <c r="H24">
+      <c r="I24" s="1">
         <v>75.84</v>
       </c>
-      <c r="I24" s="1">
+      <c r="J24">
         <v>1.62</v>
       </c>
-      <c r="J24">
+      <c r="K24" s="1">
         <v>77.76000000000001</v>
       </c>
-      <c r="K24" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
+      <c r="L24" t="s">
+        <v>118</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C25" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D25" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E25" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="F25">
         <v>48.41</v>
       </c>
-      <c r="G25" s="1">
+      <c r="G25" t="s">
+        <v>95</v>
+      </c>
+      <c r="H25">
         <v>1.57</v>
       </c>
-      <c r="H25">
+      <c r="I25" s="1">
         <v>76</v>
       </c>
-      <c r="I25" s="1">
+      <c r="J25">
         <v>1.61</v>
       </c>
-      <c r="J25">
+      <c r="K25" s="1">
         <v>77.94</v>
       </c>
-      <c r="K25" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
+      <c r="L25" t="s">
+        <v>119</v>
+      </c>
+      <c r="M25">
+        <v>263161</v>
+      </c>
+      <c r="N25" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C26" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D26" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="E26" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="F26">
         <v>40</v>
       </c>
-      <c r="G26" s="1">
+      <c r="G26" t="s">
+        <v>95</v>
+      </c>
+      <c r="H26">
         <v>1.76</v>
       </c>
-      <c r="H26">
+      <c r="I26" s="1">
         <v>70.40000000000001</v>
       </c>
-      <c r="I26" s="1">
+      <c r="J26">
         <v>1.81</v>
       </c>
-      <c r="J26">
+      <c r="K26" s="1">
         <v>72.40000000000001</v>
       </c>
-      <c r="K26" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
+      <c r="L26" t="s">
+        <v>120</v>
+      </c>
+      <c r="M26">
+        <v>181250</v>
+      </c>
+      <c r="N26" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C27" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D27" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="E27" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="F27">
         <v>40</v>
       </c>
-      <c r="G27" s="1">
+      <c r="G27" t="s">
+        <v>95</v>
+      </c>
+      <c r="H27">
         <v>1.56</v>
       </c>
-      <c r="H27">
+      <c r="I27" s="1">
         <v>62.4</v>
       </c>
-      <c r="I27" s="1">
+      <c r="J27">
         <v>1.6</v>
       </c>
-      <c r="J27">
+      <c r="K27" s="1">
         <v>64</v>
       </c>
-      <c r="K27" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
+      <c r="L27" t="s">
+        <v>121</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C28" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D28" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="E28" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="F28">
         <v>45</v>
       </c>
-      <c r="G28" s="1">
+      <c r="G28" t="s">
+        <v>95</v>
+      </c>
+      <c r="H28">
         <v>1.56</v>
       </c>
-      <c r="H28">
+      <c r="I28" s="1">
         <v>70.2</v>
       </c>
-      <c r="I28" s="1">
+      <c r="J28">
         <v>1.6</v>
       </c>
-      <c r="J28">
+      <c r="K28" s="1">
         <v>72</v>
       </c>
-      <c r="K28" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
+      <c r="L28" t="s">
+        <v>122</v>
+      </c>
+      <c r="M28">
+        <v>40147</v>
+      </c>
+      <c r="N28" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C29" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D29" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E29" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="F29">
+        <v>25</v>
+      </c>
+      <c r="G29" t="s">
+        <v>95</v>
+      </c>
+      <c r="H29">
+        <v>1.56</v>
+      </c>
+      <c r="I29" s="1">
+        <v>39</v>
+      </c>
+      <c r="J29">
+        <v>1.6</v>
+      </c>
+      <c r="K29" s="1">
+        <v>40</v>
+      </c>
+      <c r="L29" t="s">
+        <v>123</v>
+      </c>
+      <c r="M29">
+        <v>234852</v>
+      </c>
+      <c r="N29" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" t="s">
+        <v>25</v>
+      </c>
+      <c r="B30" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30" t="s">
+        <v>56</v>
+      </c>
+      <c r="D30" t="s">
+        <v>81</v>
+      </c>
+      <c r="E30" t="s">
+        <v>90</v>
+      </c>
+      <c r="F30">
         <v>26.48</v>
       </c>
-      <c r="G29" s="1">
+      <c r="G30" t="s">
+        <v>95</v>
+      </c>
+      <c r="H30">
         <v>1.52</v>
       </c>
-      <c r="H29">
+      <c r="I30" s="1">
         <v>40.25</v>
       </c>
-      <c r="I29" s="1">
+      <c r="J30">
         <v>1.56</v>
       </c>
-      <c r="J29">
+      <c r="K30" s="1">
         <v>41.31</v>
       </c>
-      <c r="K29" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
-      <c r="A30" t="s">
-        <v>22</v>
-      </c>
-      <c r="B30" t="s">
-        <v>32</v>
-      </c>
-      <c r="C30" t="s">
-        <v>50</v>
-      </c>
-      <c r="D30" t="s">
-        <v>73</v>
-      </c>
-      <c r="E30" t="s">
-        <v>81</v>
-      </c>
-      <c r="F30">
-        <v>25</v>
-      </c>
-      <c r="G30" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="H30">
-        <v>39</v>
-      </c>
-      <c r="I30" s="1">
-        <v>1.6</v>
-      </c>
-      <c r="J30">
-        <v>40</v>
-      </c>
-      <c r="K30" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
+      <c r="L30" t="s">
+        <v>124</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
       <c r="A31" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B31" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C31" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D31" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="E31" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F31">
         <v>39</v>
       </c>
-      <c r="G31" s="1">
+      <c r="G31" t="s">
+        <v>95</v>
+      </c>
+      <c r="H31">
         <v>1.52</v>
       </c>
-      <c r="H31">
+      <c r="I31" s="1">
         <v>59.28</v>
       </c>
-      <c r="I31" s="1">
+      <c r="J31">
         <v>1.56</v>
       </c>
-      <c r="J31">
+      <c r="K31" s="1">
         <v>60.84</v>
       </c>
-      <c r="K31" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
+      <c r="L31" t="s">
+        <v>125</v>
+      </c>
+      <c r="M31">
+        <v>299160</v>
+      </c>
+      <c r="N31" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
       <c r="A32" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C32" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D32" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="E32" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="F32">
         <v>64</v>
       </c>
-      <c r="G32" s="1">
+      <c r="G32" t="s">
+        <v>95</v>
+      </c>
+      <c r="H32">
         <v>1.55</v>
       </c>
-      <c r="H32">
+      <c r="I32" s="1">
         <v>99.2</v>
       </c>
-      <c r="I32" s="1">
+      <c r="J32">
         <v>1.59</v>
       </c>
-      <c r="J32">
+      <c r="K32" s="1">
         <v>101.76</v>
       </c>
-      <c r="K32" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11">
+      <c r="L32" t="s">
+        <v>126</v>
+      </c>
+      <c r="M32">
+        <v>109490</v>
+      </c>
+      <c r="N32" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B33" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C33" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D33" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="E33" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="F33">
         <v>52</v>
       </c>
-      <c r="G33" s="1">
+      <c r="G33" t="s">
+        <v>95</v>
+      </c>
+      <c r="H33">
         <v>1.55</v>
       </c>
-      <c r="H33">
+      <c r="I33" s="1">
         <v>80.59999999999999</v>
       </c>
-      <c r="I33" s="1">
+      <c r="J33">
         <v>1.59</v>
       </c>
-      <c r="J33">
+      <c r="K33" s="1">
         <v>82.68000000000001</v>
       </c>
-      <c r="K33" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11">
+      <c r="L33" t="s">
+        <v>127</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C34" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D34" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="E34" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F34">
         <v>43.29</v>
       </c>
-      <c r="G34" s="1">
+      <c r="G34" t="s">
+        <v>95</v>
+      </c>
+      <c r="H34">
         <v>1.52</v>
       </c>
-      <c r="H34">
+      <c r="I34" s="1">
         <v>65.8</v>
       </c>
-      <c r="I34" s="1">
+      <c r="J34">
         <v>1.56</v>
       </c>
-      <c r="J34">
+      <c r="K34" s="1">
         <v>67.53</v>
       </c>
-      <c r="K34" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11">
+      <c r="L34" t="s">
+        <v>128</v>
+      </c>
+      <c r="M34">
+        <v>233670</v>
+      </c>
+      <c r="N34" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
       <c r="A35" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C35" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="D35" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="E35" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F35">
+        <v>20</v>
+      </c>
+      <c r="G35" t="s">
+        <v>95</v>
+      </c>
+      <c r="H35">
+        <v>1.51</v>
+      </c>
+      <c r="I35" s="1">
+        <v>30.2</v>
+      </c>
+      <c r="J35">
+        <v>1.55</v>
+      </c>
+      <c r="K35" s="1">
+        <v>31</v>
+      </c>
+      <c r="L35" t="s">
+        <v>129</v>
+      </c>
+      <c r="M35">
+        <v>9702</v>
+      </c>
+      <c r="N35" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
+      <c r="A36" t="s">
         <v>27</v>
       </c>
-      <c r="G35" s="1">
+      <c r="B36" t="s">
+        <v>38</v>
+      </c>
+      <c r="C36" t="s">
+        <v>43</v>
+      </c>
+      <c r="D36" t="s">
+        <v>68</v>
+      </c>
+      <c r="E36" t="s">
+        <v>90</v>
+      </c>
+      <c r="F36">
+        <v>27</v>
+      </c>
+      <c r="G36" t="s">
+        <v>95</v>
+      </c>
+      <c r="H36">
         <v>1.51</v>
       </c>
-      <c r="H35">
+      <c r="I36" s="1">
         <v>40.77</v>
       </c>
-      <c r="I35" s="1">
+      <c r="J36">
         <v>1.55</v>
       </c>
-      <c r="J35">
+      <c r="K36" s="1">
         <v>41.85</v>
       </c>
-      <c r="K35" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11">
-      <c r="A36" t="s">
-        <v>24</v>
-      </c>
-      <c r="B36" t="s">
-        <v>32</v>
-      </c>
-      <c r="C36" t="s">
+      <c r="L36" t="s">
+        <v>130</v>
+      </c>
+      <c r="M36">
+        <v>325830</v>
+      </c>
+      <c r="N36" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" t="s">
+        <v>27</v>
+      </c>
+      <c r="B37" t="s">
+        <v>38</v>
+      </c>
+      <c r="C37" t="s">
         <v>47</v>
       </c>
-      <c r="D36" t="s">
-        <v>70</v>
-      </c>
-      <c r="E36" t="s">
-        <v>80</v>
-      </c>
-      <c r="F36">
-        <v>20</v>
-      </c>
-      <c r="G36" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="H36">
-        <v>30.2</v>
-      </c>
-      <c r="I36" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="J36">
-        <v>31</v>
-      </c>
-      <c r="K36" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11">
-      <c r="A37" t="s">
-        <v>24</v>
-      </c>
-      <c r="B37" t="s">
-        <v>32</v>
-      </c>
-      <c r="C37" t="s">
-        <v>41</v>
-      </c>
       <c r="D37" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="E37" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="F37">
         <v>25</v>
       </c>
-      <c r="G37" s="1">
+      <c r="G37" t="s">
+        <v>95</v>
+      </c>
+      <c r="H37">
         <v>1.8</v>
       </c>
-      <c r="H37">
+      <c r="I37" s="1">
         <v>45</v>
       </c>
-      <c r="I37" s="1">
+      <c r="J37">
         <v>1.85</v>
       </c>
-      <c r="J37">
+      <c r="K37" s="1">
         <v>46.25</v>
       </c>
-      <c r="K37" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11">
+      <c r="L37" t="s">
+        <v>131</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
       <c r="A38" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B38" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C38" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D38" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="E38" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="F38">
         <v>64</v>
       </c>
-      <c r="G38" s="1">
+      <c r="G38" t="s">
+        <v>95</v>
+      </c>
+      <c r="H38">
         <v>1.55</v>
       </c>
-      <c r="H38">
+      <c r="I38" s="1">
         <v>99.2</v>
       </c>
-      <c r="I38" s="1">
+      <c r="J38">
         <v>1.59</v>
       </c>
-      <c r="J38">
+      <c r="K38" s="1">
         <v>101.76</v>
       </c>
-      <c r="K38" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11">
+      <c r="L38" t="s">
+        <v>132</v>
+      </c>
+      <c r="M38">
+        <v>285400</v>
+      </c>
+      <c r="N38" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
       <c r="A39" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B39" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C39" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D39" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E39" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="F39">
         <v>45.8</v>
       </c>
-      <c r="G39" s="1">
+      <c r="G39" t="s">
+        <v>95</v>
+      </c>
+      <c r="H39">
         <v>1.55</v>
       </c>
-      <c r="H39">
+      <c r="I39" s="1">
         <v>70.98999999999999</v>
       </c>
-      <c r="I39" s="1">
+      <c r="J39">
         <v>1.59</v>
       </c>
-      <c r="J39">
+      <c r="K39" s="1">
         <v>72.81999999999999</v>
       </c>
-      <c r="K39" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11">
+      <c r="L39" t="s">
+        <v>133</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
       <c r="A40" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B40" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C40" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D40" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="E40" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F40">
         <v>19</v>
       </c>
-      <c r="G40" s="1">
+      <c r="G40" t="s">
+        <v>95</v>
+      </c>
+      <c r="H40">
         <v>1.51</v>
       </c>
-      <c r="H40">
+      <c r="I40" s="1">
         <v>28.69</v>
       </c>
-      <c r="I40" s="1">
+      <c r="J40">
         <v>1.55</v>
       </c>
-      <c r="J40">
+      <c r="K40" s="1">
         <v>29.45</v>
       </c>
-      <c r="K40" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11">
+      <c r="L40" t="s">
+        <v>134</v>
+      </c>
+      <c r="M40">
+        <v>75030</v>
+      </c>
+      <c r="N40" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
       <c r="A41" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B41" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C41" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D41" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="E41" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="F41">
         <v>53</v>
       </c>
-      <c r="G41" s="1">
+      <c r="G41" t="s">
+        <v>95</v>
+      </c>
+      <c r="H41">
         <v>1.54</v>
       </c>
-      <c r="H41">
+      <c r="I41" s="1">
         <v>81.62</v>
       </c>
-      <c r="I41" s="1">
+      <c r="J41">
         <v>1.58</v>
       </c>
-      <c r="J41">
+      <c r="K41" s="1">
         <v>83.73999999999999</v>
       </c>
-      <c r="K41" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11">
+      <c r="L41" t="s">
+        <v>135</v>
+      </c>
+      <c r="M41">
+        <v>283078</v>
+      </c>
+      <c r="N41" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
       <c r="A42" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C42" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D42" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="E42" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F42">
         <v>18.06</v>
       </c>
-      <c r="G42" s="1">
+      <c r="G42" t="s">
+        <v>95</v>
+      </c>
+      <c r="H42">
         <v>1.5</v>
       </c>
-      <c r="H42">
+      <c r="I42" s="1">
         <v>27.09</v>
       </c>
-      <c r="I42" s="1">
+      <c r="J42">
         <v>1.54</v>
       </c>
-      <c r="J42">
+      <c r="K42" s="1">
         <v>27.81</v>
       </c>
-      <c r="K42" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11">
+      <c r="L42" t="s">
+        <v>136</v>
+      </c>
+      <c r="M42">
+        <v>326105</v>
+      </c>
+      <c r="N42" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
       <c r="A43" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C43" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D43" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E43" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="F43">
-        <v>50.02</v>
-      </c>
-      <c r="G43" s="1">
-        <v>1.52</v>
+        <v>10.01</v>
+      </c>
+      <c r="G43" t="s">
+        <v>95</v>
       </c>
       <c r="H43">
-        <v>76.03</v>
+        <v>1.5</v>
       </c>
       <c r="I43" s="1">
-        <v>1.56</v>
+        <v>15.02</v>
       </c>
       <c r="J43">
-        <v>78.03</v>
-      </c>
-      <c r="K43" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11">
+        <v>1.54</v>
+      </c>
+      <c r="K43" s="1">
+        <v>15.42</v>
+      </c>
+      <c r="L43" t="s">
+        <v>137</v>
+      </c>
+      <c r="M43">
+        <v>75140</v>
+      </c>
+      <c r="N43" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
       <c r="A44" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C44" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D44" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="E44" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="F44">
         <v>37</v>
       </c>
-      <c r="G44" s="1">
+      <c r="G44" t="s">
+        <v>95</v>
+      </c>
+      <c r="H44">
         <v>1.52</v>
       </c>
-      <c r="H44">
+      <c r="I44" s="1">
         <v>56.24</v>
       </c>
-      <c r="I44" s="1">
+      <c r="J44">
         <v>1.56</v>
       </c>
-      <c r="J44">
+      <c r="K44" s="1">
         <v>57.72</v>
       </c>
-      <c r="K44" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11">
+      <c r="L44" t="s">
+        <v>138</v>
+      </c>
+      <c r="M44">
+        <v>254550</v>
+      </c>
+      <c r="N44" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
       <c r="A45" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B45" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C45" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D45" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="E45" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="F45">
-        <v>10.01</v>
-      </c>
-      <c r="G45" s="1">
-        <v>1.5</v>
+        <v>50.02</v>
+      </c>
+      <c r="G45" t="s">
+        <v>95</v>
       </c>
       <c r="H45">
-        <v>15.02</v>
+        <v>1.52</v>
       </c>
       <c r="I45" s="1">
-        <v>1.54</v>
+        <v>76.03</v>
       </c>
       <c r="J45">
-        <v>15.42</v>
-      </c>
-      <c r="K45" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11">
+        <v>1.56</v>
+      </c>
+      <c r="K45" s="1">
+        <v>78.03</v>
+      </c>
+      <c r="L45" t="s">
+        <v>139</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
       <c r="A46" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C46" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D46" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="E46" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F46">
         <v>20.01</v>
       </c>
-      <c r="G46" s="1">
+      <c r="G46" t="s">
+        <v>95</v>
+      </c>
+      <c r="H46">
         <v>1.49</v>
       </c>
-      <c r="H46">
+      <c r="I46" s="1">
         <v>29.81</v>
       </c>
-      <c r="I46" s="1">
+      <c r="J46">
         <v>1.53</v>
       </c>
-      <c r="J46">
+      <c r="K46" s="1">
         <v>30.62</v>
       </c>
-      <c r="K46" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11">
+      <c r="L46" t="s">
+        <v>140</v>
+      </c>
+      <c r="M46">
+        <v>9885</v>
+      </c>
+      <c r="N46" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
       <c r="A47" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C47" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D47" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="E47" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F47">
         <v>6</v>
       </c>
-      <c r="G47" s="1">
+      <c r="G47" t="s">
+        <v>95</v>
+      </c>
+      <c r="H47">
         <v>1.47</v>
       </c>
-      <c r="H47">
+      <c r="I47" s="1">
         <v>8.82</v>
       </c>
-      <c r="I47" s="1">
+      <c r="J47">
         <v>1.51</v>
       </c>
-      <c r="J47">
+      <c r="K47" s="1">
         <v>9.06</v>
       </c>
-      <c r="K47" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11">
+      <c r="L47" t="s">
+        <v>141</v>
+      </c>
+      <c r="M47">
+        <v>75150</v>
+      </c>
+      <c r="N47" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
       <c r="A48" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B48" t="s">
+        <v>38</v>
+      </c>
+      <c r="C48" t="s">
+        <v>61</v>
+      </c>
+      <c r="D48" t="s">
+        <v>86</v>
+      </c>
+      <c r="E48" t="s">
+        <v>90</v>
+      </c>
+      <c r="F48">
+        <v>29.01</v>
+      </c>
+      <c r="G48" t="s">
+        <v>95</v>
+      </c>
+      <c r="H48">
+        <v>1.47</v>
+      </c>
+      <c r="I48" s="1">
+        <v>42.64</v>
+      </c>
+      <c r="J48">
+        <v>1.51</v>
+      </c>
+      <c r="K48" s="1">
+        <v>43.81</v>
+      </c>
+      <c r="L48" t="s">
+        <v>142</v>
+      </c>
+      <c r="M48">
+        <v>20370</v>
+      </c>
+      <c r="N48" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14">
+      <c r="A49" t="s">
+        <v>31</v>
+      </c>
+      <c r="B49" t="s">
+        <v>38</v>
+      </c>
+      <c r="C49" t="s">
+        <v>42</v>
+      </c>
+      <c r="D49" t="s">
+        <v>67</v>
+      </c>
+      <c r="E49" t="s">
+        <v>92</v>
+      </c>
+      <c r="F49">
+        <v>45</v>
+      </c>
+      <c r="G49" t="s">
+        <v>95</v>
+      </c>
+      <c r="H49">
+        <v>1.72</v>
+      </c>
+      <c r="I49" s="1">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="J49">
+        <v>1.77</v>
+      </c>
+      <c r="K49" s="1">
+        <v>79.65000000000001</v>
+      </c>
+      <c r="L49" t="s">
+        <v>143</v>
+      </c>
+      <c r="M49">
+        <v>171800</v>
+      </c>
+      <c r="N49" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14">
+      <c r="A50" t="s">
+        <v>31</v>
+      </c>
+      <c r="B50" t="s">
+        <v>38</v>
+      </c>
+      <c r="C50" t="s">
+        <v>62</v>
+      </c>
+      <c r="D50" t="s">
+        <v>87</v>
+      </c>
+      <c r="E50" t="s">
+        <v>91</v>
+      </c>
+      <c r="F50">
+        <v>48</v>
+      </c>
+      <c r="G50" t="s">
+        <v>95</v>
+      </c>
+      <c r="H50">
+        <v>1.48</v>
+      </c>
+      <c r="I50" s="1">
+        <v>71.04000000000001</v>
+      </c>
+      <c r="J50">
+        <v>1.52</v>
+      </c>
+      <c r="K50" s="1">
+        <v>72.95999999999999</v>
+      </c>
+      <c r="L50" t="s">
+        <v>144</v>
+      </c>
+      <c r="M50">
+        <v>25906</v>
+      </c>
+      <c r="N50" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14">
+      <c r="A51" t="s">
         <v>32</v>
       </c>
-      <c r="C48" t="s">
-        <v>36</v>
-      </c>
-      <c r="D48" t="s">
-        <v>59</v>
-      </c>
-      <c r="E48" t="s">
+      <c r="B51" t="s">
+        <v>38</v>
+      </c>
+      <c r="C51" t="s">
+        <v>51</v>
+      </c>
+      <c r="D51" t="s">
+        <v>76</v>
+      </c>
+      <c r="E51" t="s">
+        <v>91</v>
+      </c>
+      <c r="F51">
+        <v>35.17</v>
+      </c>
+      <c r="G51" t="s">
+        <v>95</v>
+      </c>
+      <c r="H51">
+        <v>1.48</v>
+      </c>
+      <c r="I51" s="1">
+        <v>52.05</v>
+      </c>
+      <c r="J51">
+        <v>1.52</v>
+      </c>
+      <c r="K51" s="1">
+        <v>53.46</v>
+      </c>
+      <c r="L51" t="s">
+        <v>145</v>
+      </c>
+      <c r="M51">
+        <v>0</v>
+      </c>
+      <c r="N51" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14">
+      <c r="A52" t="s">
+        <v>32</v>
+      </c>
+      <c r="B52" t="s">
+        <v>38</v>
+      </c>
+      <c r="C52" t="s">
+        <v>57</v>
+      </c>
+      <c r="D52" t="s">
         <v>82</v>
       </c>
-      <c r="F48">
+      <c r="E52" t="s">
+        <v>90</v>
+      </c>
+      <c r="F52">
+        <v>37</v>
+      </c>
+      <c r="G52" t="s">
+        <v>95</v>
+      </c>
+      <c r="H52">
+        <v>1.47</v>
+      </c>
+      <c r="I52" s="1">
+        <v>54.39</v>
+      </c>
+      <c r="J52">
+        <v>1.51</v>
+      </c>
+      <c r="K52" s="1">
+        <v>55.87</v>
+      </c>
+      <c r="L52" t="s">
+        <v>146</v>
+      </c>
+      <c r="M52">
+        <v>299580</v>
+      </c>
+      <c r="N52" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14">
+      <c r="A53" t="s">
+        <v>32</v>
+      </c>
+      <c r="B53" t="s">
+        <v>38</v>
+      </c>
+      <c r="C53" t="s">
         <v>45</v>
       </c>
-      <c r="G48" s="1">
-        <v>1.72</v>
-      </c>
-      <c r="H48">
-        <v>77.40000000000001</v>
-      </c>
-      <c r="I48" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="J48">
-        <v>79.65000000000001</v>
-      </c>
-      <c r="K48" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11">
-      <c r="A49" t="s">
-        <v>28</v>
-      </c>
-      <c r="B49" t="s">
+      <c r="D53" t="s">
+        <v>70</v>
+      </c>
+      <c r="E53" t="s">
+        <v>91</v>
+      </c>
+      <c r="F53">
+        <v>42.93</v>
+      </c>
+      <c r="G53" t="s">
+        <v>95</v>
+      </c>
+      <c r="H53">
+        <v>1.48</v>
+      </c>
+      <c r="I53" s="1">
+        <v>63.54</v>
+      </c>
+      <c r="J53">
+        <v>1.52</v>
+      </c>
+      <c r="K53" s="1">
+        <v>65.25</v>
+      </c>
+      <c r="L53" t="s">
+        <v>147</v>
+      </c>
+      <c r="M53">
+        <v>40471</v>
+      </c>
+      <c r="N53" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14">
+      <c r="A54" t="s">
         <v>32</v>
       </c>
-      <c r="C49" t="s">
-        <v>55</v>
-      </c>
-      <c r="D49" t="s">
-        <v>78</v>
-      </c>
-      <c r="E49" t="s">
-        <v>81</v>
-      </c>
-      <c r="F49">
+      <c r="B54" t="s">
+        <v>38</v>
+      </c>
+      <c r="C54" t="s">
         <v>48</v>
       </c>
-      <c r="G49" s="1">
-        <v>1.48</v>
-      </c>
-      <c r="H49">
-        <v>71.04000000000001</v>
-      </c>
-      <c r="I49" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="J49">
-        <v>72.95999999999999</v>
-      </c>
-      <c r="K49" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11">
-      <c r="A50" t="s">
-        <v>28</v>
-      </c>
-      <c r="B50" t="s">
-        <v>32</v>
-      </c>
-      <c r="C50" t="s">
-        <v>56</v>
-      </c>
-      <c r="D50" t="s">
-        <v>79</v>
-      </c>
-      <c r="E50" t="s">
-        <v>80</v>
-      </c>
-      <c r="F50">
-        <v>29.01</v>
-      </c>
-      <c r="G50" s="1">
-        <v>1.47</v>
-      </c>
-      <c r="H50">
-        <v>42.64</v>
-      </c>
-      <c r="I50" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="J50">
-        <v>43.81</v>
-      </c>
-      <c r="K50" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11">
-      <c r="A51" t="s">
-        <v>29</v>
-      </c>
-      <c r="B51" t="s">
-        <v>32</v>
-      </c>
-      <c r="C51" t="s">
-        <v>39</v>
-      </c>
-      <c r="D51" t="s">
-        <v>62</v>
-      </c>
-      <c r="E51" t="s">
-        <v>81</v>
-      </c>
-      <c r="F51">
-        <v>42.93</v>
-      </c>
-      <c r="G51" s="1">
-        <v>1.48</v>
-      </c>
-      <c r="H51">
-        <v>63.54</v>
-      </c>
-      <c r="I51" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="J51">
-        <v>65.25</v>
-      </c>
-      <c r="K51" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11">
-      <c r="A52" t="s">
-        <v>29</v>
-      </c>
-      <c r="B52" t="s">
-        <v>32</v>
-      </c>
-      <c r="C52" t="s">
-        <v>45</v>
-      </c>
-      <c r="D52" t="s">
-        <v>68</v>
-      </c>
-      <c r="E52" t="s">
-        <v>81</v>
-      </c>
-      <c r="F52">
-        <v>35.17</v>
-      </c>
-      <c r="G52" s="1">
-        <v>1.48</v>
-      </c>
-      <c r="H52">
-        <v>52.05</v>
-      </c>
-      <c r="I52" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="J52">
-        <v>53.46</v>
-      </c>
-      <c r="K52" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11">
-      <c r="A53" t="s">
-        <v>29</v>
-      </c>
-      <c r="B53" t="s">
-        <v>32</v>
-      </c>
-      <c r="C53" t="s">
-        <v>51</v>
-      </c>
-      <c r="D53" t="s">
-        <v>74</v>
-      </c>
-      <c r="E53" t="s">
-        <v>80</v>
-      </c>
-      <c r="F53">
-        <v>37</v>
-      </c>
-      <c r="G53" s="1">
-        <v>1.47</v>
-      </c>
-      <c r="H53">
-        <v>54.39</v>
-      </c>
-      <c r="I53" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="J53">
-        <v>55.87</v>
-      </c>
-      <c r="K53" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11">
-      <c r="A54" t="s">
-        <v>29</v>
-      </c>
-      <c r="B54" t="s">
-        <v>32</v>
-      </c>
-      <c r="C54" t="s">
-        <v>42</v>
-      </c>
       <c r="D54" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E54" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="F54">
         <v>54</v>
       </c>
-      <c r="G54" s="1">
+      <c r="G54" t="s">
+        <v>95</v>
+      </c>
+      <c r="H54">
         <v>1.48</v>
       </c>
-      <c r="H54">
+      <c r="I54" s="1">
         <v>79.92</v>
       </c>
-      <c r="I54" s="1">
+      <c r="J54">
         <v>1.52</v>
       </c>
-      <c r="J54">
+      <c r="K54" s="1">
         <v>82.08</v>
       </c>
-      <c r="K54" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11">
+      <c r="L54" t="s">
+        <v>148</v>
+      </c>
+      <c r="M54">
+        <v>0</v>
+      </c>
+      <c r="N54" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14">
       <c r="A55" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B55" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C55" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D55" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="E55" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="F55">
         <v>28</v>
       </c>
-      <c r="G55" s="1">
+      <c r="G55" t="s">
+        <v>95</v>
+      </c>
+      <c r="H55">
         <v>1.47</v>
       </c>
-      <c r="H55">
+      <c r="I55" s="1">
         <v>41.16</v>
       </c>
-      <c r="I55" s="1">
+      <c r="J55">
         <v>1.51</v>
       </c>
-      <c r="J55">
+      <c r="K55" s="1">
         <v>42.28</v>
       </c>
-      <c r="K55" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11">
+      <c r="L55" t="s">
+        <v>149</v>
+      </c>
+      <c r="M55">
+        <v>0</v>
+      </c>
+      <c r="N55" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14">
       <c r="A56" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B56" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C56" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D56" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="E56" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="F56">
         <v>47.09</v>
       </c>
-      <c r="G56" s="1">
+      <c r="G56" t="s">
+        <v>95</v>
+      </c>
+      <c r="H56">
         <v>1.47</v>
       </c>
-      <c r="H56">
+      <c r="I56" s="1">
         <v>69.22</v>
       </c>
-      <c r="I56" s="1">
+      <c r="J56">
         <v>1.51</v>
       </c>
-      <c r="J56">
+      <c r="K56" s="1">
         <v>71.11</v>
       </c>
-      <c r="K56" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11">
+      <c r="L56" t="s">
+        <v>150</v>
+      </c>
+      <c r="M56">
+        <v>289430</v>
+      </c>
+      <c r="N56" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14">
       <c r="A57" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B57" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C57" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="D57" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="E57" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="F57">
-        <v>37.82</v>
-      </c>
-      <c r="G57" s="1">
+        <v>38.59</v>
+      </c>
+      <c r="G57" t="s">
+        <v>95</v>
+      </c>
+      <c r="H57">
         <v>1.47</v>
       </c>
-      <c r="H57">
-        <v>55.6</v>
-      </c>
       <c r="I57" s="1">
+        <v>56.73</v>
+      </c>
+      <c r="J57">
         <v>1.51</v>
       </c>
-      <c r="J57">
-        <v>57.11</v>
-      </c>
-      <c r="K57" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11">
+      <c r="K57" s="1">
+        <v>58.27</v>
+      </c>
+      <c r="L57" t="s">
+        <v>151</v>
+      </c>
+      <c r="M57">
+        <v>234285</v>
+      </c>
+      <c r="N57" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14">
       <c r="A58" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B58" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C58" t="s">
+        <v>41</v>
+      </c>
+      <c r="D58" t="s">
+        <v>66</v>
+      </c>
+      <c r="E58" t="s">
+        <v>91</v>
+      </c>
+      <c r="F58">
+        <v>37.81</v>
+      </c>
+      <c r="G58" t="s">
+        <v>95</v>
+      </c>
+      <c r="H58">
+        <v>1.47</v>
+      </c>
+      <c r="I58" s="1">
+        <v>55.58</v>
+      </c>
+      <c r="J58">
+        <v>1.51</v>
+      </c>
+      <c r="K58" s="1">
+        <v>57.09</v>
+      </c>
+      <c r="L58" t="s">
+        <v>152</v>
+      </c>
+      <c r="M58">
+        <v>0</v>
+      </c>
+      <c r="N58" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14">
+      <c r="A59" t="s">
+        <v>34</v>
+      </c>
+      <c r="B59" t="s">
+        <v>38</v>
+      </c>
+      <c r="C59" t="s">
         <v>40</v>
       </c>
-      <c r="D58" t="s">
-        <v>63</v>
-      </c>
-      <c r="E58" t="s">
-        <v>80</v>
-      </c>
-      <c r="F58">
-        <v>38.59</v>
-      </c>
-      <c r="G58" s="1">
-        <v>1.47</v>
-      </c>
-      <c r="H58">
-        <v>56.73</v>
-      </c>
-      <c r="I58" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="J58">
-        <v>58.27</v>
-      </c>
-      <c r="K58" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11">
-      <c r="A59" t="s">
-        <v>31</v>
-      </c>
-      <c r="B59" t="s">
-        <v>32</v>
-      </c>
-      <c r="C59" t="s">
-        <v>34</v>
-      </c>
       <c r="D59" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="E59" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F59">
         <v>6.16</v>
       </c>
-      <c r="G59" s="1">
+      <c r="G59" t="s">
+        <v>95</v>
+      </c>
+      <c r="H59">
         <v>1.47</v>
       </c>
-      <c r="H59">
+      <c r="I59" s="1">
         <v>9.06</v>
       </c>
-      <c r="I59" s="1">
+      <c r="J59">
         <v>1.51</v>
       </c>
-      <c r="J59">
+      <c r="K59" s="1">
         <v>9.300000000000001</v>
       </c>
-      <c r="K59" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11">
+      <c r="L59" t="s">
+        <v>153</v>
+      </c>
+      <c r="M59">
+        <v>75270</v>
+      </c>
+      <c r="N59" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14">
       <c r="A60" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B60" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C60" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D60" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="E60" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F60">
         <v>26</v>
       </c>
-      <c r="G60" s="1">
+      <c r="G60" t="s">
+        <v>95</v>
+      </c>
+      <c r="H60">
         <v>1.47</v>
       </c>
-      <c r="H60">
+      <c r="I60" s="1">
         <v>38.22</v>
       </c>
-      <c r="I60" s="1">
+      <c r="J60">
         <v>1.51</v>
       </c>
-      <c r="J60">
+      <c r="K60" s="1">
         <v>39.26</v>
       </c>
-      <c r="K60" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11">
-      <c r="A63" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="B63" s="3"/>
-      <c r="C63" s="3"/>
-      <c r="D63" s="3"/>
-      <c r="E63" s="3"/>
-      <c r="F63" s="3"/>
-    </row>
-    <row r="64" spans="1:11">
-      <c r="A64" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="B64" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C64" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="E64" s="4" t="s">
+      <c r="L60" t="s">
+        <v>154</v>
+      </c>
+      <c r="M60">
+        <v>9990</v>
+      </c>
+      <c r="N60" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14">
+      <c r="A61" t="s">
+        <v>35</v>
+      </c>
+      <c r="B61" t="s">
+        <v>38</v>
+      </c>
+      <c r="C61" t="s">
+        <v>43</v>
+      </c>
+      <c r="D61" t="s">
+        <v>68</v>
+      </c>
+      <c r="E61" t="s">
+        <v>90</v>
+      </c>
+      <c r="F61">
+        <v>23.01</v>
+      </c>
+      <c r="G61" t="s">
+        <v>95</v>
+      </c>
+      <c r="H61">
+        <v>1.46</v>
+      </c>
+      <c r="I61" s="1">
+        <v>33.59</v>
+      </c>
+      <c r="J61">
+        <v>1.5</v>
+      </c>
+      <c r="K61" s="1">
+        <v>34.52</v>
+      </c>
+      <c r="L61" t="s">
+        <v>115</v>
+      </c>
+      <c r="M61">
+        <v>326650</v>
+      </c>
+      <c r="N61" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14">
+      <c r="A62" t="s">
+        <v>36</v>
+      </c>
+      <c r="B62" t="s">
+        <v>38</v>
+      </c>
+      <c r="C62" t="s">
+        <v>49</v>
+      </c>
+      <c r="D62" t="s">
+        <v>74</v>
+      </c>
+      <c r="E62" t="s">
+        <v>91</v>
+      </c>
+      <c r="F62">
+        <v>53</v>
+      </c>
+      <c r="G62" t="s">
+        <v>95</v>
+      </c>
+      <c r="H62">
+        <v>1.47</v>
+      </c>
+      <c r="I62" s="1">
+        <v>77.91</v>
+      </c>
+      <c r="J62">
+        <v>1.51</v>
+      </c>
+      <c r="K62" s="1">
+        <v>80.03</v>
+      </c>
+      <c r="L62" t="s">
+        <v>155</v>
+      </c>
+      <c r="M62">
+        <v>283763</v>
+      </c>
+      <c r="N62" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14">
+      <c r="A63" t="s">
+        <v>36</v>
+      </c>
+      <c r="B63" t="s">
+        <v>38</v>
+      </c>
+      <c r="C63" t="s">
+        <v>48</v>
+      </c>
+      <c r="D63" t="s">
+        <v>73</v>
+      </c>
+      <c r="E63" t="s">
+        <v>91</v>
+      </c>
+      <c r="F63">
+        <v>48.99</v>
+      </c>
+      <c r="G63" t="s">
+        <v>95</v>
+      </c>
+      <c r="H63">
+        <v>1.47</v>
+      </c>
+      <c r="I63" s="1">
+        <v>72.02</v>
+      </c>
+      <c r="J63">
+        <v>1.51</v>
+      </c>
+      <c r="K63" s="1">
+        <v>73.97</v>
+      </c>
+      <c r="L63" t="s">
+        <v>156</v>
+      </c>
+      <c r="M63">
+        <v>0</v>
+      </c>
+      <c r="N63" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14">
+      <c r="A64" t="s">
+        <v>36</v>
+      </c>
+      <c r="B64" t="s">
+        <v>38</v>
+      </c>
+      <c r="C64" t="s">
+        <v>40</v>
+      </c>
+      <c r="D64" t="s">
+        <v>65</v>
+      </c>
+      <c r="E64" t="s">
+        <v>90</v>
+      </c>
+      <c r="F64">
         <v>7</v>
       </c>
-      <c r="F64" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B65" s="6">
-        <v>1191.92</v>
-      </c>
-      <c r="C65" s="6">
-        <v>27</v>
-      </c>
-      <c r="D65" s="7">
-        <v>1.5485</v>
-      </c>
-      <c r="E65" s="6">
-        <v>1845.7</v>
-      </c>
-      <c r="F65" s="6">
-        <v>1893.37</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66" s="5" t="s">
+      <c r="G64" t="s">
+        <v>95</v>
+      </c>
+      <c r="H64">
+        <v>1.46</v>
+      </c>
+      <c r="I64" s="1">
+        <v>10.22</v>
+      </c>
+      <c r="J64">
+        <v>1.5</v>
+      </c>
+      <c r="K64" s="1">
+        <v>10.5</v>
+      </c>
+      <c r="L64" t="s">
+        <v>157</v>
+      </c>
+      <c r="M64">
+        <v>75360</v>
+      </c>
+      <c r="N64" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14">
+      <c r="A65" t="s">
+        <v>36</v>
+      </c>
+      <c r="B65" t="s">
+        <v>38</v>
+      </c>
+      <c r="C65" t="s">
+        <v>63</v>
+      </c>
+      <c r="D65" t="s">
+        <v>88</v>
+      </c>
+      <c r="E65" t="s">
+        <v>93</v>
+      </c>
+      <c r="F65">
+        <v>10</v>
+      </c>
+      <c r="G65" t="s">
+        <v>95</v>
+      </c>
+      <c r="H65">
+        <v>1.72</v>
+      </c>
+      <c r="I65" s="1">
+        <v>17.2</v>
+      </c>
+      <c r="J65">
+        <v>1.77</v>
+      </c>
+      <c r="K65" s="1">
+        <v>17.7</v>
+      </c>
+      <c r="L65" t="s">
+        <v>158</v>
+      </c>
+      <c r="M65">
+        <v>9894</v>
+      </c>
+      <c r="N65" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14">
+      <c r="A66" t="s">
+        <v>36</v>
+      </c>
+      <c r="B66" t="s">
+        <v>38</v>
+      </c>
+      <c r="C66" t="s">
+        <v>63</v>
+      </c>
+      <c r="D66" t="s">
+        <v>88</v>
+      </c>
+      <c r="E66" t="s">
+        <v>94</v>
+      </c>
+      <c r="F66">
+        <v>1</v>
+      </c>
+      <c r="G66" t="s">
+        <v>96</v>
+      </c>
+      <c r="H66">
+        <v>23.79</v>
+      </c>
+      <c r="I66" s="1">
+        <v>23.79</v>
+      </c>
+      <c r="J66">
+        <v>23.79</v>
+      </c>
+      <c r="K66" s="1">
+        <v>23.79</v>
+      </c>
+      <c r="L66" t="s">
+        <v>158</v>
+      </c>
+      <c r="M66">
+        <v>9894</v>
+      </c>
+      <c r="N66" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14">
+      <c r="A67" t="s">
+        <v>37</v>
+      </c>
+      <c r="B67" t="s">
+        <v>38</v>
+      </c>
+      <c r="C67" t="s">
+        <v>45</v>
+      </c>
+      <c r="D67" t="s">
+        <v>70</v>
+      </c>
+      <c r="E67" t="s">
+        <v>91</v>
+      </c>
+      <c r="F67">
+        <v>41.8</v>
+      </c>
+      <c r="G67" t="s">
+        <v>95</v>
+      </c>
+      <c r="H67">
+        <v>1.47</v>
+      </c>
+      <c r="I67" s="1">
+        <v>61.45</v>
+      </c>
+      <c r="J67">
+        <v>1.51</v>
+      </c>
+      <c r="K67" s="1">
+        <v>63.12</v>
+      </c>
+      <c r="L67" t="s">
+        <v>159</v>
+      </c>
+      <c r="M67">
+        <v>40770</v>
+      </c>
+      <c r="N67" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14">
+      <c r="A68" t="s">
+        <v>37</v>
+      </c>
+      <c r="B68" t="s">
+        <v>38</v>
+      </c>
+      <c r="C68" t="s">
+        <v>54</v>
+      </c>
+      <c r="D68" t="s">
+        <v>79</v>
+      </c>
+      <c r="E68" t="s">
+        <v>91</v>
+      </c>
+      <c r="F68">
+        <v>47.87</v>
+      </c>
+      <c r="G68" t="s">
+        <v>95</v>
+      </c>
+      <c r="H68">
+        <v>1.47</v>
+      </c>
+      <c r="I68" s="1">
+        <v>70.37</v>
+      </c>
+      <c r="J68">
+        <v>1.51</v>
+      </c>
+      <c r="K68" s="1">
+        <v>72.28</v>
+      </c>
+      <c r="L68" t="s">
+        <v>160</v>
+      </c>
+      <c r="M68">
+        <v>263857</v>
+      </c>
+      <c r="N68" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14">
+      <c r="A69" t="s">
+        <v>37</v>
+      </c>
+      <c r="B69" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" t="s">
+        <v>61</v>
+      </c>
+      <c r="D69" t="s">
+        <v>86</v>
+      </c>
+      <c r="E69" t="s">
+        <v>90</v>
+      </c>
+      <c r="F69">
+        <v>17.91</v>
+      </c>
+      <c r="G69" t="s">
+        <v>95</v>
+      </c>
+      <c r="H69">
+        <v>1.46</v>
+      </c>
+      <c r="I69" s="1">
+        <v>26.15</v>
+      </c>
+      <c r="J69">
+        <v>1.5</v>
+      </c>
+      <c r="K69" s="1">
+        <v>26.86</v>
+      </c>
+      <c r="L69" t="s">
+        <v>161</v>
+      </c>
+      <c r="M69">
+        <v>20615</v>
+      </c>
+      <c r="N69" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14">
+      <c r="A70" t="s">
+        <v>37</v>
+      </c>
+      <c r="B70" t="s">
+        <v>38</v>
+      </c>
+      <c r="C70" t="s">
+        <v>40</v>
+      </c>
+      <c r="D70" t="s">
+        <v>65</v>
+      </c>
+      <c r="E70" t="s">
+        <v>90</v>
+      </c>
+      <c r="F70">
+        <v>8</v>
+      </c>
+      <c r="G70" t="s">
+        <v>95</v>
+      </c>
+      <c r="H70">
+        <v>1.46</v>
+      </c>
+      <c r="I70" s="1">
+        <v>11.68</v>
+      </c>
+      <c r="J70">
+        <v>1.5</v>
+      </c>
+      <c r="K70" s="1">
+        <v>12</v>
+      </c>
+      <c r="L70" t="s">
+        <v>138</v>
+      </c>
+      <c r="M70">
+        <v>75435</v>
+      </c>
+      <c r="N70" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14">
+      <c r="A71" t="s">
+        <v>37</v>
+      </c>
+      <c r="B71" t="s">
+        <v>38</v>
+      </c>
+      <c r="C71" t="s">
+        <v>58</v>
+      </c>
+      <c r="D71" t="s">
+        <v>83</v>
+      </c>
+      <c r="E71" t="s">
+        <v>91</v>
+      </c>
+      <c r="F71">
+        <v>66</v>
+      </c>
+      <c r="G71" t="s">
+        <v>95</v>
+      </c>
+      <c r="H71">
+        <v>1.47</v>
+      </c>
+      <c r="I71" s="1">
+        <v>97.02</v>
+      </c>
+      <c r="J71">
+        <v>1.51</v>
+      </c>
+      <c r="K71" s="1">
+        <v>99.66</v>
+      </c>
+      <c r="L71" t="s">
+        <v>162</v>
+      </c>
+      <c r="M71">
+        <v>110245</v>
+      </c>
+      <c r="N71" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14">
+      <c r="A72" t="s">
+        <v>37</v>
+      </c>
+      <c r="B72" t="s">
+        <v>38</v>
+      </c>
+      <c r="C72" t="s">
+        <v>47</v>
+      </c>
+      <c r="D72" t="s">
+        <v>72</v>
+      </c>
+      <c r="E72" t="s">
+        <v>91</v>
+      </c>
+      <c r="F72">
+        <v>39.01</v>
+      </c>
+      <c r="G72" t="s">
+        <v>95</v>
+      </c>
+      <c r="H72">
+        <v>1.47</v>
+      </c>
+      <c r="I72" s="1">
+        <v>57.34</v>
+      </c>
+      <c r="J72">
+        <v>1.51</v>
+      </c>
+      <c r="K72" s="1">
+        <v>58.91</v>
+      </c>
+      <c r="L72" t="s">
+        <v>163</v>
+      </c>
+      <c r="M72">
+        <v>241979</v>
+      </c>
+      <c r="N72" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14">
+      <c r="A73" t="s">
+        <v>37</v>
+      </c>
+      <c r="B73" t="s">
+        <v>38</v>
+      </c>
+      <c r="C73" t="s">
+        <v>62</v>
+      </c>
+      <c r="D73" t="s">
+        <v>87</v>
+      </c>
+      <c r="E73" t="s">
+        <v>91</v>
+      </c>
+      <c r="F73">
+        <v>21</v>
+      </c>
+      <c r="G73" t="s">
+        <v>95</v>
+      </c>
+      <c r="H73">
+        <v>1.47</v>
+      </c>
+      <c r="I73" s="1">
+        <v>30.87</v>
+      </c>
+      <c r="J73">
+        <v>1.51</v>
+      </c>
+      <c r="K73" s="1">
+        <v>31.71</v>
+      </c>
+      <c r="L73" t="s">
+        <v>164</v>
+      </c>
+      <c r="M73">
+        <v>26242</v>
+      </c>
+      <c r="N73" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14">
+      <c r="A74" t="s">
+        <v>37</v>
+      </c>
+      <c r="B74" t="s">
+        <v>38</v>
+      </c>
+      <c r="C74" t="s">
+        <v>41</v>
+      </c>
+      <c r="D74" t="s">
+        <v>66</v>
+      </c>
+      <c r="E74" t="s">
+        <v>91</v>
+      </c>
+      <c r="F74">
+        <v>32</v>
+      </c>
+      <c r="G74" t="s">
+        <v>95</v>
+      </c>
+      <c r="H74">
+        <v>1.47</v>
+      </c>
+      <c r="I74" s="1">
+        <v>47.04</v>
+      </c>
+      <c r="J74">
+        <v>1.51</v>
+      </c>
+      <c r="K74" s="1">
+        <v>48.32</v>
+      </c>
+      <c r="L74" t="s">
+        <v>165</v>
+      </c>
+      <c r="M74">
+        <v>0</v>
+      </c>
+      <c r="N74" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14">
+      <c r="A75" t="s">
+        <v>37</v>
+      </c>
+      <c r="B75" t="s">
+        <v>38</v>
+      </c>
+      <c r="C75" t="s">
+        <v>53</v>
+      </c>
+      <c r="D75" t="s">
+        <v>78</v>
+      </c>
+      <c r="E75" t="s">
+        <v>91</v>
+      </c>
+      <c r="F75">
+        <v>19.97</v>
+      </c>
+      <c r="G75" t="s">
+        <v>95</v>
+      </c>
+      <c r="H75">
+        <v>1.47</v>
+      </c>
+      <c r="I75" s="1">
+        <v>29.36</v>
+      </c>
+      <c r="J75">
+        <v>1.51</v>
+      </c>
+      <c r="K75" s="1">
+        <v>30.15</v>
+      </c>
+      <c r="L75" t="s">
+        <v>166</v>
+      </c>
+      <c r="M75">
+        <v>289785</v>
+      </c>
+      <c r="N75" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14">
+      <c r="A76" t="s">
+        <v>37</v>
+      </c>
+      <c r="B76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C76" t="s">
+        <v>50</v>
+      </c>
+      <c r="D76" t="s">
+        <v>75</v>
+      </c>
+      <c r="E76" t="s">
+        <v>91</v>
+      </c>
+      <c r="F76">
+        <v>37</v>
+      </c>
+      <c r="G76" t="s">
+        <v>95</v>
+      </c>
+      <c r="H76">
+        <v>1.47</v>
+      </c>
+      <c r="I76" s="1">
+        <v>54.39</v>
+      </c>
+      <c r="J76">
+        <v>1.51</v>
+      </c>
+      <c r="K76" s="1">
+        <v>55.87</v>
+      </c>
+      <c r="L76" t="s">
+        <v>167</v>
+      </c>
+      <c r="M76">
+        <v>255013</v>
+      </c>
+      <c r="N76" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14">
+      <c r="A77" t="s">
+        <v>37</v>
+      </c>
+      <c r="B77" t="s">
+        <v>38</v>
+      </c>
+      <c r="C77" t="s">
+        <v>51</v>
+      </c>
+      <c r="D77" t="s">
+        <v>76</v>
+      </c>
+      <c r="E77" t="s">
+        <v>91</v>
+      </c>
+      <c r="F77">
+        <v>23</v>
+      </c>
+      <c r="G77" t="s">
+        <v>95</v>
+      </c>
+      <c r="H77">
+        <v>1.47</v>
+      </c>
+      <c r="I77" s="1">
+        <v>33.81</v>
+      </c>
+      <c r="J77">
+        <v>1.51</v>
+      </c>
+      <c r="K77" s="1">
+        <v>34.73</v>
+      </c>
+      <c r="L77" t="s">
+        <v>168</v>
+      </c>
+      <c r="M77">
+        <v>0</v>
+      </c>
+      <c r="N77" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14">
+      <c r="A78" t="s">
+        <v>37</v>
+      </c>
+      <c r="B78" t="s">
+        <v>38</v>
+      </c>
+      <c r="C78" t="s">
+        <v>44</v>
+      </c>
+      <c r="D78" t="s">
+        <v>69</v>
+      </c>
+      <c r="E78" t="s">
+        <v>90</v>
+      </c>
+      <c r="F78">
+        <v>35.01</v>
+      </c>
+      <c r="G78" t="s">
+        <v>95</v>
+      </c>
+      <c r="H78">
+        <v>1.46</v>
+      </c>
+      <c r="I78" s="1">
+        <v>51.11</v>
+      </c>
+      <c r="J78">
+        <v>1.5</v>
+      </c>
+      <c r="K78" s="1">
+        <v>52.52</v>
+      </c>
+      <c r="L78" t="s">
+        <v>137</v>
+      </c>
+      <c r="M78">
+        <v>6660</v>
+      </c>
+      <c r="N78" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14">
+      <c r="A79" t="s">
+        <v>37</v>
+      </c>
+      <c r="B79" t="s">
+        <v>38</v>
+      </c>
+      <c r="C79" t="s">
+        <v>58</v>
+      </c>
+      <c r="D79" t="s">
+        <v>83</v>
+      </c>
+      <c r="E79" t="s">
+        <v>91</v>
+      </c>
+      <c r="F79">
+        <v>14</v>
+      </c>
+      <c r="G79" t="s">
+        <v>95</v>
+      </c>
+      <c r="H79">
+        <v>1.47</v>
+      </c>
+      <c r="I79" s="1">
+        <v>20.58</v>
+      </c>
+      <c r="J79">
+        <v>1.51</v>
+      </c>
+      <c r="K79" s="1">
+        <v>21.14</v>
+      </c>
+      <c r="L79" t="s">
+        <v>169</v>
+      </c>
+      <c r="M79">
+        <v>110375</v>
+      </c>
+      <c r="N79" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14">
+      <c r="A80" t="s">
+        <v>37</v>
+      </c>
+      <c r="B80" t="s">
+        <v>38</v>
+      </c>
+      <c r="C80" t="s">
+        <v>59</v>
+      </c>
+      <c r="D80" t="s">
+        <v>84</v>
+      </c>
+      <c r="E80" t="s">
+        <v>91</v>
+      </c>
+      <c r="F80">
+        <v>28</v>
+      </c>
+      <c r="G80" t="s">
+        <v>95</v>
+      </c>
+      <c r="H80">
+        <v>1.47</v>
+      </c>
+      <c r="I80" s="1">
+        <v>41.16</v>
+      </c>
+      <c r="J80">
+        <v>1.51</v>
+      </c>
+      <c r="K80" s="1">
+        <v>42.28</v>
+      </c>
+      <c r="L80" t="s">
+        <v>170</v>
+      </c>
+      <c r="M80">
+        <v>0</v>
+      </c>
+      <c r="N80" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14">
+      <c r="A81" t="s">
+        <v>37</v>
+      </c>
+      <c r="B81" t="s">
+        <v>38</v>
+      </c>
+      <c r="C81" t="s">
+        <v>55</v>
+      </c>
+      <c r="D81" t="s">
         <v>80</v>
       </c>
-      <c r="B66" s="6">
-        <v>606.3099999999999</v>
-      </c>
-      <c r="C66" s="6">
-        <v>26</v>
-      </c>
-      <c r="D66" s="7">
-        <v>1.508</v>
-      </c>
-      <c r="E66" s="6">
-        <v>914.3</v>
-      </c>
-      <c r="F66" s="6">
-        <v>938.5599999999999</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67" s="5" t="s">
+      <c r="E81" t="s">
+        <v>91</v>
+      </c>
+      <c r="F81">
+        <v>30</v>
+      </c>
+      <c r="G81" t="s">
+        <v>95</v>
+      </c>
+      <c r="H81">
+        <v>1.47</v>
+      </c>
+      <c r="I81" s="1">
+        <v>44.1</v>
+      </c>
+      <c r="J81">
+        <v>1.51</v>
+      </c>
+      <c r="K81" s="1">
+        <v>45.3</v>
+      </c>
+      <c r="L81" t="s">
+        <v>171</v>
+      </c>
+      <c r="M81">
+        <v>235282</v>
+      </c>
+      <c r="N81" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14">
+      <c r="A82" t="s">
+        <v>37</v>
+      </c>
+      <c r="B82" t="s">
+        <v>38</v>
+      </c>
+      <c r="C82" t="s">
+        <v>49</v>
+      </c>
+      <c r="D82" t="s">
+        <v>74</v>
+      </c>
+      <c r="E82" t="s">
+        <v>91</v>
+      </c>
+      <c r="F82">
+        <v>9.01</v>
+      </c>
+      <c r="G82" t="s">
+        <v>95</v>
+      </c>
+      <c r="H82">
+        <v>1.47</v>
+      </c>
+      <c r="I82" s="1">
+        <v>13.24</v>
+      </c>
+      <c r="J82">
+        <v>1.51</v>
+      </c>
+      <c r="K82" s="1">
+        <v>13.61</v>
+      </c>
+      <c r="L82" t="s">
+        <v>172</v>
+      </c>
+      <c r="M82">
+        <v>283868</v>
+      </c>
+      <c r="N82" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14">
+      <c r="A83" t="s">
+        <v>37</v>
+      </c>
+      <c r="B83" t="s">
+        <v>38</v>
+      </c>
+      <c r="C83" t="s">
+        <v>57</v>
+      </c>
+      <c r="D83" t="s">
         <v>82</v>
       </c>
-      <c r="B67" s="6">
-        <v>191</v>
-      </c>
-      <c r="C67" s="6">
-        <v>5</v>
-      </c>
-      <c r="D67" s="7">
-        <v>1.754</v>
-      </c>
-      <c r="E67" s="6">
-        <v>335.01</v>
-      </c>
-      <c r="F67" s="6">
-        <v>344.56</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="B68" s="6">
-        <v>25</v>
-      </c>
-      <c r="C68" s="6">
+      <c r="E83" t="s">
+        <v>90</v>
+      </c>
+      <c r="F83">
+        <v>35</v>
+      </c>
+      <c r="G83" t="s">
+        <v>95</v>
+      </c>
+      <c r="H83">
+        <v>1.46</v>
+      </c>
+      <c r="I83" s="1">
+        <v>51.1</v>
+      </c>
+      <c r="J83">
+        <v>1.5</v>
+      </c>
+      <c r="K83" s="1">
+        <v>52.5</v>
+      </c>
+      <c r="L83" t="s">
+        <v>173</v>
+      </c>
+      <c r="M83">
+        <v>299950</v>
+      </c>
+      <c r="N83" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14">
+      <c r="A84" t="s">
+        <v>37</v>
+      </c>
+      <c r="B84" t="s">
+        <v>38</v>
+      </c>
+      <c r="C84" t="s">
+        <v>64</v>
+      </c>
+      <c r="D84" t="s">
+        <v>89</v>
+      </c>
+      <c r="E84" t="s">
+        <v>90</v>
+      </c>
+      <c r="F84">
+        <v>38</v>
+      </c>
+      <c r="G84" t="s">
+        <v>95</v>
+      </c>
+      <c r="H84">
+        <v>1.46</v>
+      </c>
+      <c r="I84" s="1">
+        <v>55.48</v>
+      </c>
+      <c r="J84">
+        <v>1.5</v>
+      </c>
+      <c r="K84" s="1">
+        <v>57</v>
+      </c>
+      <c r="L84" t="s">
+        <v>174</v>
+      </c>
+      <c r="M84">
+        <v>71810</v>
+      </c>
+      <c r="N84" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14">
+      <c r="A85" t="s">
+        <v>37</v>
+      </c>
+      <c r="B85" t="s">
+        <v>38</v>
+      </c>
+      <c r="C85" t="s">
+        <v>52</v>
+      </c>
+      <c r="D85" t="s">
+        <v>77</v>
+      </c>
+      <c r="E85" t="s">
+        <v>90</v>
+      </c>
+      <c r="F85">
+        <v>23</v>
+      </c>
+      <c r="G85" t="s">
+        <v>95</v>
+      </c>
+      <c r="H85">
+        <v>1.46</v>
+      </c>
+      <c r="I85" s="1">
+        <v>33.58</v>
+      </c>
+      <c r="J85">
+        <v>1.5</v>
+      </c>
+      <c r="K85" s="1">
+        <v>34.5</v>
+      </c>
+      <c r="L85" t="s">
+        <v>175</v>
+      </c>
+      <c r="M85">
+        <v>10120</v>
+      </c>
+      <c r="N85" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14">
+      <c r="A86" t="s">
+        <v>37</v>
+      </c>
+      <c r="B86" t="s">
+        <v>38</v>
+      </c>
+      <c r="C86" t="s">
+        <v>48</v>
+      </c>
+      <c r="D86" t="s">
+        <v>73</v>
+      </c>
+      <c r="E86" t="s">
+        <v>91</v>
+      </c>
+      <c r="F86">
+        <v>13</v>
+      </c>
+      <c r="G86" t="s">
+        <v>95</v>
+      </c>
+      <c r="H86">
+        <v>1.47</v>
+      </c>
+      <c r="I86" s="1">
+        <v>19.11</v>
+      </c>
+      <c r="J86">
+        <v>1.51</v>
+      </c>
+      <c r="K86" s="1">
+        <v>19.63</v>
+      </c>
+      <c r="L86" t="s">
+        <v>176</v>
+      </c>
+      <c r="M86">
+        <v>0</v>
+      </c>
+      <c r="N86" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14">
+      <c r="A87" t="s">
+        <v>37</v>
+      </c>
+      <c r="B87" t="s">
+        <v>38</v>
+      </c>
+      <c r="C87" t="s">
+        <v>42</v>
+      </c>
+      <c r="D87" t="s">
+        <v>67</v>
+      </c>
+      <c r="E87" t="s">
+        <v>92</v>
+      </c>
+      <c r="F87">
+        <v>32</v>
+      </c>
+      <c r="G87" t="s">
+        <v>95</v>
+      </c>
+      <c r="H87">
+        <v>1.71</v>
+      </c>
+      <c r="I87" s="1">
+        <v>54.72</v>
+      </c>
+      <c r="J87">
+        <v>1.76</v>
+      </c>
+      <c r="K87" s="1">
+        <v>56.32</v>
+      </c>
+      <c r="L87" t="s">
+        <v>177</v>
+      </c>
+      <c r="M87">
+        <v>182030</v>
+      </c>
+      <c r="N87" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14">
+      <c r="A90" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="B90" s="3"/>
+      <c r="C90" s="3"/>
+      <c r="D90" s="3"/>
+      <c r="E90" s="3"/>
+      <c r="F90" s="3"/>
+    </row>
+    <row r="91" spans="1:14">
+      <c r="A91" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14">
+      <c r="A92" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B92" s="6">
+        <v>1715.56</v>
+      </c>
+      <c r="C92" s="6">
+        <v>43</v>
+      </c>
+      <c r="D92" s="7">
+        <v>1.5245</v>
+      </c>
+      <c r="E92" s="6">
+        <v>2615.45</v>
+      </c>
+      <c r="F92" s="6">
+        <v>2684.06</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14">
+      <c r="A93" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B93" s="6">
+        <v>793.24</v>
+      </c>
+      <c r="C93" s="6">
+        <v>34</v>
+      </c>
+      <c r="D93" s="7">
+        <v>1.4967</v>
+      </c>
+      <c r="E93" s="6">
+        <v>1187.21</v>
+      </c>
+      <c r="F93" s="6">
+        <v>1218.96</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14">
+      <c r="A94" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B94" s="6">
+        <v>223</v>
+      </c>
+      <c r="C94" s="6">
+        <v>6</v>
+      </c>
+      <c r="D94" s="7">
+        <v>1.7477</v>
+      </c>
+      <c r="E94" s="6">
+        <v>389.73</v>
+      </c>
+      <c r="F94" s="6">
+        <v>400.88</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14">
+      <c r="A95" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B95" s="6">
+        <v>35</v>
+      </c>
+      <c r="C95" s="6">
+        <v>2</v>
+      </c>
+      <c r="D95" s="7">
+        <v>1.7771</v>
+      </c>
+      <c r="E95" s="6">
+        <v>62.2</v>
+      </c>
+      <c r="F95" s="6">
+        <v>63.95</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14">
+      <c r="A96" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B96" s="6">
         <v>1</v>
       </c>
-      <c r="D68" s="7">
-        <v>1.8</v>
-      </c>
-      <c r="E68" s="6">
-        <v>45</v>
-      </c>
-      <c r="F68" s="6">
-        <v>46.25</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="B69" s="9">
-        <v>2014.23</v>
-      </c>
-      <c r="C69" s="9">
-        <v>59</v>
-      </c>
-      <c r="D69" s="7"/>
-      <c r="E69" s="9">
-        <v>3140.01</v>
-      </c>
-      <c r="F69" s="9">
-        <v>3222.74</v>
+      <c r="C96" s="6">
+        <v>1</v>
+      </c>
+      <c r="D96" s="7">
+        <v>23.79</v>
+      </c>
+      <c r="E96" s="6">
+        <v>23.79</v>
+      </c>
+      <c r="F96" s="6">
+        <v>23.79</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6">
+      <c r="A97" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="B97" s="9">
+        <v>2767.8</v>
+      </c>
+      <c r="C97" s="9">
+        <v>86</v>
+      </c>
+      <c r="D97" s="7"/>
+      <c r="E97" s="9">
+        <v>4278.38</v>
+      </c>
+      <c r="F97" s="9">
+        <v>4391.64</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="A90:F90"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ДОБРИЧКА/ОБЩИНА ДОБРИЧКА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ДОБРИЧКА/ОБЩИНА ДОБРИЧКА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="227">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,6 +55,9 @@
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-07-01</t>
   </si>
   <si>
@@ -79,48 +85,81 @@
     <t>2026-07-15</t>
   </si>
   <si>
-    <t>Добрич Добруджа</t>
-  </si>
-  <si>
-    <t>В.Търново</t>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>2026-07-20</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>2026-07-22</t>
+  </si>
+  <si>
+    <t>2026-07-23</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>2026-07-28</t>
+  </si>
+  <si>
+    <t>2026-07-29</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>1156 Добрич бул. Добруджа</t>
+  </si>
+  <si>
+    <t>1103 Велико Търново изход</t>
   </si>
   <si>
     <t>ТХ0223АТ</t>
   </si>
   <si>
+    <t>ТХ1759АК</t>
+  </si>
+  <si>
     <t>ТХ4225ХР</t>
   </si>
   <si>
-    <t>ТХ1759АК</t>
-  </si>
-  <si>
     <t>ТХ9465МТ</t>
   </si>
   <si>
+    <t>ТХ4223ХР</t>
+  </si>
+  <si>
     <t>ТХ3756ХК</t>
   </si>
   <si>
-    <t>ТХ4223ХР</t>
+    <t>ТХ7827ТМ</t>
   </si>
   <si>
     <t>ТХ7828ТМ</t>
   </si>
   <si>
-    <t>ТХ7827ТМ</t>
-  </si>
-  <si>
     <t>ТХ3541МТ</t>
   </si>
   <si>
+    <t>ТХ4444КХ</t>
+  </si>
+  <si>
     <t>ТХ0222АТ</t>
   </si>
   <si>
     <t>ТХ0224АТ</t>
   </si>
   <si>
-    <t>ТХ4444КХ</t>
-  </si>
-  <si>
     <t>ТХ8668АН</t>
   </si>
   <si>
@@ -133,42 +172,69 @@
     <t>ТХ8900АТ</t>
   </si>
   <si>
+    <t>ТХ4221ХР</t>
+  </si>
+  <si>
+    <t>ТХ8896АТ</t>
+  </si>
+  <si>
+    <t>ТХ3400РХ</t>
+  </si>
+  <si>
+    <t>ТХ1573ТМ</t>
+  </si>
+  <si>
+    <t>ТХ1578ТМ</t>
+  </si>
+  <si>
+    <t>ТХ3713АН</t>
+  </si>
+  <si>
+    <t>ТХ2626КХ</t>
+  </si>
+  <si>
+    <t>ТХ2560КХ</t>
+  </si>
+  <si>
+    <t>ТХ8897АТ</t>
+  </si>
+  <si>
     <t>78970151027720849</t>
   </si>
   <si>
+    <t>78970151027720732</t>
+  </si>
+  <si>
     <t>78970151027720872</t>
   </si>
   <si>
-    <t>78970151027720732</t>
-  </si>
-  <si>
     <t>78970151027720971</t>
   </si>
   <si>
+    <t>78970151027720740</t>
+  </si>
+  <si>
     <t>78970151027720773</t>
   </si>
   <si>
-    <t>78970151027720740</t>
+    <t>78970151027721003</t>
   </si>
   <si>
     <t>78970151027721011</t>
   </si>
   <si>
-    <t>78970151027721003</t>
-  </si>
-  <si>
     <t>78970151027720922</t>
   </si>
   <si>
+    <t>78970151027720674</t>
+  </si>
+  <si>
     <t>78970151027720831</t>
   </si>
   <si>
     <t>78970151027720856</t>
   </si>
   <si>
-    <t>78970151027720674</t>
-  </si>
-  <si>
     <t>78970151027720815</t>
   </si>
   <si>
@@ -181,6 +247,33 @@
     <t>78970151027720880</t>
   </si>
   <si>
+    <t>78970151027721029</t>
+  </si>
+  <si>
+    <t>78970151027721037</t>
+  </si>
+  <si>
+    <t>78970151027720690</t>
+  </si>
+  <si>
+    <t>78970151027720997</t>
+  </si>
+  <si>
+    <t>78970151027720989</t>
+  </si>
+  <si>
+    <t>78970151027720823</t>
+  </si>
+  <si>
+    <t>78970151027720682</t>
+  </si>
+  <si>
+    <t>78970151027720724</t>
+  </si>
+  <si>
+    <t>78970151027720898</t>
+  </si>
+  <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
@@ -190,61 +283,400 @@
     <t>EKO RACING 100</t>
   </si>
   <si>
-    <t>2026-07-01 13:38:36</t>
-  </si>
-  <si>
-    <t>2026-07-06 12:54:17</t>
-  </si>
-  <si>
-    <t>2026-07-06 16:53:35</t>
-  </si>
-  <si>
-    <t>2026-07-07 13:34:04</t>
-  </si>
-  <si>
-    <t>2026-07-07 14:09:54</t>
-  </si>
-  <si>
-    <t>2026-07-07 15:18:54</t>
-  </si>
-  <si>
-    <t>2026-07-08 08:45:34</t>
-  </si>
-  <si>
-    <t>2026-07-08 08:46:35</t>
-  </si>
-  <si>
-    <t>2026-07-09 14:22:03</t>
-  </si>
-  <si>
-    <t>2026-07-10 12:12:13</t>
-  </si>
-  <si>
-    <t>2026-07-10 13:29:35</t>
-  </si>
-  <si>
-    <t>2026-07-10 13:53:41</t>
-  </si>
-  <si>
-    <t>2026-07-10 17:02:17</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:46:50</t>
-  </si>
-  <si>
-    <t>2026-07-13 14:59:16</t>
-  </si>
-  <si>
-    <t>2026-07-14 11:14:31</t>
-  </si>
-  <si>
-    <t>2026-07-14 18:24:09</t>
-  </si>
-  <si>
-    <t>2026-07-15 10:23:31</t>
-  </si>
-  <si>
-    <t>2026-07-15 14:23:01</t>
+    <t>10 L. EKO ADBLUE</t>
+  </si>
+  <si>
+    <t>5 L. EKO ADBLUE</t>
+  </si>
+  <si>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>PC</t>
+  </si>
+  <si>
+    <t>13:38:00</t>
+  </si>
+  <si>
+    <t>16:53:00</t>
+  </si>
+  <si>
+    <t>12:54:00</t>
+  </si>
+  <si>
+    <t>13:33:00</t>
+  </si>
+  <si>
+    <t>15:18:00</t>
+  </si>
+  <si>
+    <t>14:09:00</t>
+  </si>
+  <si>
+    <t>08:46:00</t>
+  </si>
+  <si>
+    <t>08:45:00</t>
+  </si>
+  <si>
+    <t>14:21:00</t>
+  </si>
+  <si>
+    <t>13:53:00</t>
+  </si>
+  <si>
+    <t>12:12:00</t>
+  </si>
+  <si>
+    <t>13:29:00</t>
+  </si>
+  <si>
+    <t>17:02:00</t>
+  </si>
+  <si>
+    <t>10:46:00</t>
+  </si>
+  <si>
+    <t>14:58:00</t>
+  </si>
+  <si>
+    <t>18:25:00</t>
+  </si>
+  <si>
+    <t>11:14:00</t>
+  </si>
+  <si>
+    <t>10:23:00</t>
+  </si>
+  <si>
+    <t>14:22:00</t>
+  </si>
+  <si>
+    <t>10:56:00</t>
+  </si>
+  <si>
+    <t>14:14:00</t>
+  </si>
+  <si>
+    <t>07:21:00</t>
+  </si>
+  <si>
+    <t>13:22:00</t>
+  </si>
+  <si>
+    <t>13:45:00</t>
+  </si>
+  <si>
+    <t>08:42:00</t>
+  </si>
+  <si>
+    <t>08:12:00</t>
+  </si>
+  <si>
+    <t>13:37:00</t>
+  </si>
+  <si>
+    <t>12:29:00</t>
+  </si>
+  <si>
+    <t>13:34:00</t>
+  </si>
+  <si>
+    <t>14:49:00</t>
+  </si>
+  <si>
+    <t>08:19:00</t>
+  </si>
+  <si>
+    <t>08:39:00</t>
+  </si>
+  <si>
+    <t>09:56:00</t>
+  </si>
+  <si>
+    <t>11:48:00</t>
+  </si>
+  <si>
+    <t>08:24:00</t>
+  </si>
+  <si>
+    <t>12:44:00</t>
+  </si>
+  <si>
+    <t>08:50:00</t>
+  </si>
+  <si>
+    <t>10:42:00</t>
+  </si>
+  <si>
+    <t>12:58:00</t>
+  </si>
+  <si>
+    <t>13:13:00</t>
+  </si>
+  <si>
+    <t>08:33:00</t>
+  </si>
+  <si>
+    <t>13:58:00</t>
+  </si>
+  <si>
+    <t>16:48:00</t>
+  </si>
+  <si>
+    <t>08:05:00</t>
+  </si>
+  <si>
+    <t>08:38:00</t>
+  </si>
+  <si>
+    <t>08:43:00</t>
+  </si>
+  <si>
+    <t>14:59:00</t>
+  </si>
+  <si>
+    <t>10:33:00</t>
+  </si>
+  <si>
+    <t>11:08:00</t>
+  </si>
+  <si>
+    <t>11:04:00</t>
+  </si>
+  <si>
+    <t>14:19:00</t>
+  </si>
+  <si>
+    <t>12:13:00</t>
+  </si>
+  <si>
+    <t>16:34:00</t>
+  </si>
+  <si>
+    <t>12:51:00</t>
+  </si>
+  <si>
+    <t>12:52:00</t>
+  </si>
+  <si>
+    <t>13:54:00</t>
+  </si>
+  <si>
+    <t>13:15:00</t>
+  </si>
+  <si>
+    <t>14:18:00</t>
+  </si>
+  <si>
+    <t>14:41:00</t>
+  </si>
+  <si>
+    <t>17:03:00</t>
+  </si>
+  <si>
+    <t>3234168517 3234168517</t>
+  </si>
+  <si>
+    <t>3234403419 3234403419</t>
+  </si>
+  <si>
+    <t>3234406536 3234406536</t>
+  </si>
+  <si>
+    <t>3234453038 3234453038</t>
+  </si>
+  <si>
+    <t>3234454065 3234454065</t>
+  </si>
+  <si>
+    <t>3234454916 3234454916</t>
+  </si>
+  <si>
+    <t>3234481237 3234481237</t>
+  </si>
+  <si>
+    <t>3234483617 3234483617</t>
+  </si>
+  <si>
+    <t>3234552054 3234552054</t>
+  </si>
+  <si>
+    <t>3234638787 3234638787</t>
+  </si>
+  <si>
+    <t>3234642170 3234642170</t>
+  </si>
+  <si>
+    <t>3234644615 3234644615</t>
+  </si>
+  <si>
+    <t>3234649002 3234649002</t>
+  </si>
+  <si>
+    <t>3234753804 3234753804</t>
+  </si>
+  <si>
+    <t>3234755841 3234755841</t>
+  </si>
+  <si>
+    <t>3234795992 3234795992</t>
+  </si>
+  <si>
+    <t>3234800839 3234800839</t>
+  </si>
+  <si>
+    <t>3234830631 3234830631</t>
+  </si>
+  <si>
+    <t>3234849461 3234849461</t>
+  </si>
+  <si>
+    <t>3234898498 3234898498</t>
+  </si>
+  <si>
+    <t>3234898933 3234898933</t>
+  </si>
+  <si>
+    <t>3234900973 3234900973</t>
+  </si>
+  <si>
+    <t>3234951876 3234951876</t>
+  </si>
+  <si>
+    <t>3235098550 3235098550</t>
+  </si>
+  <si>
+    <t>3235101940 3235101940</t>
+  </si>
+  <si>
+    <t>3235102790 3235102790</t>
+  </si>
+  <si>
+    <t>3235104200 3235104200</t>
+  </si>
+  <si>
+    <t>3235104233 3235104233</t>
+  </si>
+  <si>
+    <t>3235105713 3235105713</t>
+  </si>
+  <si>
+    <t>3235105952 3235105952</t>
+  </si>
+  <si>
+    <t>3235106550 3235106550</t>
+  </si>
+  <si>
+    <t>3235153301 3235153301</t>
+  </si>
+  <si>
+    <t>3235199517 3235199517</t>
+  </si>
+  <si>
+    <t>3235199907 3235199907</t>
+  </si>
+  <si>
+    <t>3235234432 3235234432</t>
+  </si>
+  <si>
+    <t>3235241191 3235241191</t>
+  </si>
+  <si>
+    <t>3235246845 3235246845</t>
+  </si>
+  <si>
+    <t>3235249577 3235249577</t>
+  </si>
+  <si>
+    <t>3235301381 3235301381</t>
+  </si>
+  <si>
+    <t>3235304386 3235304386</t>
+  </si>
+  <si>
+    <t>3235308225 3235308225</t>
+  </si>
+  <si>
+    <t>3235445986 3235445986</t>
+  </si>
+  <si>
+    <t>3235447897 3235447897</t>
+  </si>
+  <si>
+    <t>3235492538 3235492538</t>
+  </si>
+  <si>
+    <t>3235498310 3235498310</t>
+  </si>
+  <si>
+    <t>3235499937 3235499937</t>
+  </si>
+  <si>
+    <t>3235529854 3235529854</t>
+  </si>
+  <si>
+    <t>3235536777 3235536777</t>
+  </si>
+  <si>
+    <t>3235539581 3235539581</t>
+  </si>
+  <si>
+    <t>3235643198 3235643198</t>
+  </si>
+  <si>
+    <t>3235645569 3235645569</t>
+  </si>
+  <si>
+    <t>3235647097 3235647097</t>
+  </si>
+  <si>
+    <t>3235649124 3235649124</t>
+  </si>
+  <si>
+    <t>3235649369 3235649369</t>
+  </si>
+  <si>
+    <t>3235649967 3235649967</t>
+  </si>
+  <si>
+    <t>3235650046 3235650046</t>
+  </si>
+  <si>
+    <t>3235650884 3235650884</t>
+  </si>
+  <si>
+    <t>3235651358 3235651358</t>
+  </si>
+  <si>
+    <t>3235652435 3235652435</t>
+  </si>
+  <si>
+    <t>3235652554 3235652554</t>
+  </si>
+  <si>
+    <t>3235652943 3235652943</t>
+  </si>
+  <si>
+    <t>3235653064 3235653064</t>
+  </si>
+  <si>
+    <t>3235653188 3235653188</t>
+  </si>
+  <si>
+    <t>3235653907 3235653907</t>
+  </si>
+  <si>
+    <t>3235654394 3235654394</t>
+  </si>
+  <si>
+    <t>3235656102 3235656102</t>
+  </si>
+  <si>
+    <t>3235656603 3235656603</t>
+  </si>
+  <si>
+    <t>3235661019 3235661019</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОБЩИНА ДОБРИЧКА</t>
@@ -662,7 +1094,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:N81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -671,15 +1103,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -716,840 +1150,3244 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="E2" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="F2">
         <v>33.82</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H2">
         <v>1.46</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>49.38</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.5</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>50.73</v>
       </c>
-      <c r="K2" t="s">
-        <v>58</v>
-      </c>
-      <c r="L2">
+      <c r="L2" t="s">
+        <v>93</v>
+      </c>
+      <c r="M2">
         <v>234743</v>
       </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="N2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="E3" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="F3">
+        <v>49.35</v>
+      </c>
+      <c r="G3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H3">
+        <v>1.48</v>
+      </c>
+      <c r="I3" s="1">
+        <v>73.04000000000001</v>
+      </c>
+      <c r="J3">
+        <v>1.52</v>
+      </c>
+      <c r="K3" s="1">
+        <v>75.01000000000001</v>
+      </c>
+      <c r="L3" t="s">
+        <v>94</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F4">
         <v>16.89</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H4">
         <v>1.46</v>
       </c>
-      <c r="H3">
+      <c r="I4" s="1">
         <v>24.66</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J4">
         <v>1.5</v>
       </c>
-      <c r="J3">
+      <c r="K4" s="1">
         <v>25.34</v>
       </c>
-      <c r="K3" t="s">
-        <v>59</v>
-      </c>
-      <c r="L3">
+      <c r="L4" t="s">
+        <v>95</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F4">
-        <v>49.35</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1.48</v>
-      </c>
-      <c r="H4">
-        <v>73.04000000000001</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="J4">
-        <v>75.01000000000001</v>
-      </c>
-      <c r="K4" t="s">
-        <v>60</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="N4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="E5" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="F5">
         <v>45.46</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>91</v>
+      </c>
+      <c r="H5">
         <v>1.48</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>67.28</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.52</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>69.09999999999999</v>
       </c>
-      <c r="K5" t="s">
-        <v>61</v>
-      </c>
-      <c r="L5">
+      <c r="L5" t="s">
+        <v>96</v>
+      </c>
+      <c r="M5">
         <v>41143</v>
       </c>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="N5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F6">
+        <v>41</v>
+      </c>
+      <c r="G6" t="s">
+        <v>91</v>
+      </c>
+      <c r="H6">
+        <v>1.48</v>
+      </c>
+      <c r="I6" s="1">
+        <v>60.68</v>
+      </c>
+      <c r="J6">
+        <v>1.52</v>
+      </c>
+      <c r="K6" s="1">
+        <v>62.32</v>
+      </c>
+      <c r="L6" t="s">
+        <v>97</v>
+      </c>
+      <c r="M6">
+        <v>285990</v>
+      </c>
+      <c r="N6" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F7">
+        <v>23.85</v>
+      </c>
+      <c r="G7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H7">
+        <v>1.48</v>
+      </c>
+      <c r="I7" s="1">
+        <v>35.3</v>
+      </c>
+      <c r="J7">
+        <v>1.52</v>
+      </c>
+      <c r="K7" s="1">
+        <v>36.25</v>
+      </c>
+      <c r="L7" t="s">
+        <v>98</v>
+      </c>
+      <c r="M7">
+        <v>242359</v>
+      </c>
+      <c r="N7" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" t="s">
+        <v>67</v>
+      </c>
+      <c r="E8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F8">
+        <v>22</v>
+      </c>
+      <c r="G8" t="s">
+        <v>91</v>
+      </c>
+      <c r="H8">
+        <v>1.45</v>
+      </c>
+      <c r="I8" s="1">
+        <v>31.9</v>
+      </c>
+      <c r="J8">
+        <v>1.49</v>
+      </c>
+      <c r="K8" s="1">
+        <v>32.78</v>
+      </c>
+      <c r="L8" t="s">
+        <v>99</v>
+      </c>
+      <c r="M8">
+        <v>20945</v>
+      </c>
+      <c r="N8" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" t="s">
         <v>43</v>
       </c>
-      <c r="E6" t="s">
-        <v>56</v>
-      </c>
-      <c r="F6">
-        <v>23.85</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1.48</v>
-      </c>
-      <c r="H6">
-        <v>35.3</v>
-      </c>
-      <c r="I6" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="J6">
-        <v>36.25</v>
-      </c>
-      <c r="K6" t="s">
-        <v>62</v>
-      </c>
-      <c r="L6">
-        <v>242359</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="D9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E9" t="s">
+        <v>86</v>
+      </c>
+      <c r="F9">
+        <v>26</v>
+      </c>
+      <c r="G9" t="s">
+        <v>91</v>
+      </c>
+      <c r="H9">
+        <v>1.45</v>
+      </c>
+      <c r="I9" s="1">
+        <v>37.7</v>
+      </c>
+      <c r="J9">
+        <v>1.49</v>
+      </c>
+      <c r="K9" s="1">
+        <v>38.74</v>
+      </c>
+      <c r="L9" t="s">
+        <v>100</v>
+      </c>
+      <c r="M9">
+        <v>7020</v>
+      </c>
+      <c r="N9" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" t="s">
         <v>44</v>
       </c>
-      <c r="E7" t="s">
-        <v>56</v>
-      </c>
-      <c r="F7">
-        <v>41</v>
-      </c>
-      <c r="G7" s="1">
-        <v>1.48</v>
-      </c>
-      <c r="H7">
-        <v>60.68</v>
-      </c>
-      <c r="I7" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="J7">
-        <v>62.32</v>
-      </c>
-      <c r="K7" t="s">
-        <v>63</v>
-      </c>
-      <c r="L7">
-        <v>285990</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F8">
-        <v>26</v>
-      </c>
-      <c r="G8" s="1">
-        <v>1.45</v>
-      </c>
-      <c r="H8">
-        <v>37.7</v>
-      </c>
-      <c r="I8" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="J8">
-        <v>38.74</v>
-      </c>
-      <c r="K8" t="s">
-        <v>64</v>
-      </c>
-      <c r="L8">
-        <v>7020</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" t="s">
-        <v>46</v>
-      </c>
-      <c r="E9" t="s">
-        <v>55</v>
-      </c>
-      <c r="F9">
-        <v>22</v>
-      </c>
-      <c r="G9" s="1">
-        <v>1.45</v>
-      </c>
-      <c r="H9">
-        <v>31.9</v>
-      </c>
-      <c r="I9" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="J9">
-        <v>32.78</v>
-      </c>
-      <c r="K9" t="s">
-        <v>65</v>
-      </c>
-      <c r="L9">
-        <v>20945</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" t="s">
-        <v>31</v>
-      </c>
       <c r="D10" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="E10" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="F10">
         <v>53.11</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H10">
         <v>1.48</v>
       </c>
-      <c r="H10">
+      <c r="I10" s="1">
         <v>78.59999999999999</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10">
         <v>1.52</v>
       </c>
-      <c r="J10">
+      <c r="K10" s="1">
         <v>80.73</v>
       </c>
-      <c r="K10" t="s">
-        <v>66</v>
-      </c>
-      <c r="L10">
+      <c r="L10" t="s">
+        <v>101</v>
+      </c>
+      <c r="M10">
         <v>284567</v>
       </c>
-    </row>
-    <row r="11" spans="1:12">
+      <c r="N10" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="E11" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="F11">
+        <v>44</v>
+      </c>
+      <c r="G11" t="s">
+        <v>91</v>
+      </c>
+      <c r="H11">
+        <v>1.7</v>
+      </c>
+      <c r="I11" s="1">
+        <v>74.8</v>
+      </c>
+      <c r="J11">
+        <v>1.75</v>
+      </c>
+      <c r="K11" s="1">
+        <v>77</v>
+      </c>
+      <c r="L11" t="s">
+        <v>102</v>
+      </c>
+      <c r="M11">
+        <v>182486</v>
+      </c>
+      <c r="N11" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E12" t="s">
+        <v>87</v>
+      </c>
+      <c r="F12">
         <v>37.62</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G12" t="s">
+        <v>91</v>
+      </c>
+      <c r="H12">
         <v>1.5</v>
       </c>
-      <c r="H11">
+      <c r="I12" s="1">
         <v>56.43</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J12">
         <v>1.54</v>
       </c>
-      <c r="J11">
+      <c r="K12" s="1">
         <v>57.93</v>
       </c>
-      <c r="K11" t="s">
-        <v>67</v>
-      </c>
-      <c r="L11">
+      <c r="L12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M12">
         <v>255470</v>
       </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12" t="s">
-        <v>49</v>
-      </c>
-      <c r="E12" t="s">
-        <v>56</v>
-      </c>
-      <c r="F12">
+      <c r="N12" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" t="s">
+        <v>87</v>
+      </c>
+      <c r="F13">
         <v>35.07</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G13" t="s">
+        <v>91</v>
+      </c>
+      <c r="H13">
         <v>1.5</v>
       </c>
-      <c r="H12">
+      <c r="I13" s="1">
         <v>52.6</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J13">
         <v>1.54</v>
       </c>
-      <c r="J12">
+      <c r="K13" s="1">
         <v>54.01</v>
       </c>
-      <c r="K12" t="s">
-        <v>68</v>
-      </c>
-      <c r="L12">
+      <c r="L13" t="s">
+        <v>104</v>
+      </c>
+      <c r="M13">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="A13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F13">
-        <v>44</v>
-      </c>
-      <c r="G13" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="H13">
-        <v>74.8</v>
-      </c>
-      <c r="I13" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="J13">
-        <v>77</v>
-      </c>
-      <c r="K13" t="s">
-        <v>69</v>
-      </c>
-      <c r="L13">
-        <v>182486</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
+      <c r="N13" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="D14" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="E14" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="F14">
         <v>53</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14" t="s">
+        <v>91</v>
+      </c>
+      <c r="H14">
         <v>1.5</v>
       </c>
-      <c r="H14">
+      <c r="I14" s="1">
         <v>79.5</v>
       </c>
-      <c r="I14" s="1">
+      <c r="J14">
         <v>1.54</v>
       </c>
-      <c r="J14">
+      <c r="K14" s="1">
         <v>81.62</v>
       </c>
-      <c r="K14" t="s">
-        <v>70</v>
-      </c>
-      <c r="L14">
+      <c r="L14" t="s">
+        <v>105</v>
+      </c>
+      <c r="M14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:12">
+      <c r="N14" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="E15" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="F15">
         <v>22</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G15" t="s">
+        <v>91</v>
+      </c>
+      <c r="H15">
         <v>1.52</v>
       </c>
-      <c r="H15">
+      <c r="I15" s="1">
         <v>33.44</v>
       </c>
-      <c r="I15" s="1">
+      <c r="J15">
         <v>1.56</v>
       </c>
-      <c r="J15">
+      <c r="K15" s="1">
         <v>34.32</v>
       </c>
-      <c r="K15" t="s">
-        <v>71</v>
-      </c>
-      <c r="L15">
+      <c r="L15" t="s">
+        <v>106</v>
+      </c>
+      <c r="M15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:12">
+      <c r="N15" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D16" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="E16" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="F16">
         <v>51.01</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G16" t="s">
+        <v>91</v>
+      </c>
+      <c r="H16">
         <v>1.45</v>
       </c>
-      <c r="H16">
+      <c r="I16" s="1">
         <v>73.95999999999999</v>
       </c>
-      <c r="I16" s="1">
+      <c r="J16">
         <v>1.49</v>
       </c>
-      <c r="J16">
+      <c r="K16" s="1">
         <v>76</v>
       </c>
-      <c r="K16" t="s">
-        <v>72</v>
-      </c>
-      <c r="L16">
+      <c r="L16" t="s">
+        <v>107</v>
+      </c>
+      <c r="M16">
         <v>300520</v>
       </c>
-    </row>
-    <row r="17" spans="1:12">
+      <c r="N16" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" t="s">
+        <v>73</v>
+      </c>
+      <c r="E17" t="s">
+        <v>87</v>
+      </c>
+      <c r="F17">
+        <v>45.87</v>
+      </c>
+      <c r="G17" t="s">
+        <v>91</v>
+      </c>
+      <c r="H17">
+        <v>1.51</v>
+      </c>
+      <c r="I17" s="1">
+        <v>69.26000000000001</v>
+      </c>
+      <c r="J17">
+        <v>1.55</v>
+      </c>
+      <c r="K17" s="1">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="L17" t="s">
+        <v>108</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" t="s">
         <v>21</v>
       </c>
-      <c r="C17" t="s">
-        <v>37</v>
-      </c>
-      <c r="D17" t="s">
-        <v>53</v>
-      </c>
-      <c r="E17" t="s">
-        <v>56</v>
-      </c>
-      <c r="F17">
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" t="s">
+        <v>75</v>
+      </c>
+      <c r="E18" t="s">
+        <v>87</v>
+      </c>
+      <c r="F18">
         <v>46.8</v>
       </c>
-      <c r="G17" s="1">
+      <c r="G18" t="s">
+        <v>91</v>
+      </c>
+      <c r="H18">
         <v>1.52</v>
       </c>
-      <c r="H17">
+      <c r="I18" s="1">
         <v>71.14</v>
       </c>
-      <c r="I17" s="1">
+      <c r="J18">
         <v>1.56</v>
       </c>
-      <c r="J17">
+      <c r="K18" s="1">
         <v>73.01000000000001</v>
       </c>
-      <c r="K17" t="s">
-        <v>73</v>
-      </c>
-      <c r="L17">
+      <c r="L18" t="s">
+        <v>109</v>
+      </c>
+      <c r="M18">
         <v>290630</v>
       </c>
-    </row>
-    <row r="18" spans="1:12">
-      <c r="A18" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="N18" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" t="s">
         <v>22</v>
       </c>
-      <c r="C18" t="s">
-        <v>35</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="B19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" t="s">
         <v>51</v>
       </c>
-      <c r="E18" t="s">
-        <v>56</v>
-      </c>
-      <c r="F18">
-        <v>45.87</v>
-      </c>
-      <c r="G18" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="H18">
-        <v>69.26000000000001</v>
-      </c>
-      <c r="I18" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="J18">
-        <v>71.09999999999999</v>
-      </c>
-      <c r="K18" t="s">
-        <v>74</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12">
-      <c r="A19" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" t="s">
-        <v>21</v>
-      </c>
-      <c r="C19" t="s">
-        <v>38</v>
-      </c>
       <c r="D19" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="E19" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="F19">
         <v>46.61</v>
       </c>
-      <c r="G19" s="1">
+      <c r="G19" t="s">
+        <v>91</v>
+      </c>
+      <c r="H19">
         <v>1.54</v>
       </c>
-      <c r="H19">
+      <c r="I19" s="1">
         <v>71.78</v>
       </c>
-      <c r="I19" s="1">
+      <c r="J19">
         <v>1.58</v>
       </c>
-      <c r="J19">
+      <c r="K19" s="1">
         <v>73.64</v>
       </c>
-      <c r="K19" t="s">
-        <v>75</v>
-      </c>
-      <c r="L19">
+      <c r="L19" t="s">
+        <v>110</v>
+      </c>
+      <c r="M19">
         <v>264545</v>
       </c>
-    </row>
-    <row r="20" spans="1:12">
+      <c r="N19" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="C20" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D20" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="E20" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="F20">
         <v>51.94</v>
       </c>
-      <c r="G20" s="1">
+      <c r="G20" t="s">
+        <v>91</v>
+      </c>
+      <c r="H20">
         <v>1.54</v>
       </c>
-      <c r="H20">
+      <c r="I20" s="1">
         <v>79.98999999999999</v>
       </c>
-      <c r="I20" s="1">
+      <c r="J20">
         <v>1.58</v>
       </c>
-      <c r="J20">
+      <c r="K20" s="1">
         <v>82.06999999999999</v>
       </c>
-      <c r="K20" t="s">
+      <c r="L20" t="s">
+        <v>111</v>
+      </c>
+      <c r="M20">
+        <v>41492</v>
+      </c>
+      <c r="N20" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" t="s">
+        <v>77</v>
+      </c>
+      <c r="E21" t="s">
+        <v>87</v>
+      </c>
+      <c r="F21">
+        <v>46</v>
+      </c>
+      <c r="G21" t="s">
+        <v>91</v>
+      </c>
+      <c r="H21">
+        <v>1.57</v>
+      </c>
+      <c r="I21" s="1">
+        <v>72.22</v>
+      </c>
+      <c r="J21">
+        <v>1.61</v>
+      </c>
+      <c r="K21" s="1">
+        <v>74.06</v>
+      </c>
+      <c r="L21" t="s">
+        <v>112</v>
+      </c>
+      <c r="M21">
+        <v>259652</v>
+      </c>
+      <c r="N21" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22" t="s">
+        <v>61</v>
+      </c>
+      <c r="E22" t="s">
+        <v>86</v>
+      </c>
+      <c r="F22">
+        <v>43.31</v>
+      </c>
+      <c r="G22" t="s">
+        <v>91</v>
+      </c>
+      <c r="H22">
+        <v>1.46</v>
+      </c>
+      <c r="I22" s="1">
+        <v>63.23</v>
+      </c>
+      <c r="J22">
+        <v>1.5</v>
+      </c>
+      <c r="K22" s="1">
+        <v>64.95999999999999</v>
+      </c>
+      <c r="L22" t="s">
+        <v>113</v>
+      </c>
+      <c r="M22">
+        <v>235382</v>
+      </c>
+      <c r="N22" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" t="s">
+        <v>78</v>
+      </c>
+      <c r="E23" t="s">
+        <v>87</v>
+      </c>
+      <c r="F23">
+        <v>32</v>
+      </c>
+      <c r="G23" t="s">
+        <v>91</v>
+      </c>
+      <c r="H23">
+        <v>1.57</v>
+      </c>
+      <c r="I23" s="1">
+        <v>50.24</v>
+      </c>
+      <c r="J23">
+        <v>1.61</v>
+      </c>
+      <c r="K23" s="1">
+        <v>51.52</v>
+      </c>
+      <c r="L23" t="s">
+        <v>98</v>
+      </c>
+      <c r="M23">
+        <v>235791</v>
+      </c>
+      <c r="N23" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D24" t="s">
+        <v>62</v>
+      </c>
+      <c r="E24" t="s">
+        <v>87</v>
+      </c>
+      <c r="F24">
+        <v>54.59</v>
+      </c>
+      <c r="G24" t="s">
+        <v>91</v>
+      </c>
+      <c r="H24">
+        <v>1.59</v>
+      </c>
+      <c r="I24" s="1">
+        <v>86.8</v>
+      </c>
+      <c r="J24">
+        <v>1.63</v>
+      </c>
+      <c r="K24" s="1">
+        <v>88.98</v>
+      </c>
+      <c r="L24" t="s">
+        <v>114</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" t="s">
+        <v>47</v>
+      </c>
+      <c r="D25" t="s">
+        <v>72</v>
+      </c>
+      <c r="E25" t="s">
+        <v>87</v>
+      </c>
+      <c r="F25">
+        <v>39.39</v>
+      </c>
+      <c r="G25" t="s">
+        <v>91</v>
+      </c>
+      <c r="H25">
+        <v>1.64</v>
+      </c>
+      <c r="I25" s="1">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="J25">
+        <v>1.68</v>
+      </c>
+      <c r="K25" s="1">
+        <v>66.18000000000001</v>
+      </c>
+      <c r="L25" t="s">
+        <v>115</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" t="s">
+        <v>69</v>
+      </c>
+      <c r="E26" t="s">
+        <v>87</v>
+      </c>
+      <c r="F26">
+        <v>54.94</v>
+      </c>
+      <c r="G26" t="s">
+        <v>91</v>
+      </c>
+      <c r="H26">
+        <v>1.64</v>
+      </c>
+      <c r="I26" s="1">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="J26">
+        <v>1.68</v>
+      </c>
+      <c r="K26" s="1">
+        <v>92.3</v>
+      </c>
+      <c r="L26" t="s">
+        <v>116</v>
+      </c>
+      <c r="M26">
+        <v>285274</v>
+      </c>
+      <c r="N26" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>34</v>
+      </c>
+      <c r="C27" t="s">
+        <v>54</v>
+      </c>
+      <c r="D27" t="s">
+        <v>79</v>
+      </c>
+      <c r="E27" t="s">
+        <v>86</v>
+      </c>
+      <c r="F27">
+        <v>19</v>
+      </c>
+      <c r="G27" t="s">
+        <v>91</v>
+      </c>
+      <c r="H27">
+        <v>1.49</v>
+      </c>
+      <c r="I27" s="1">
+        <v>28.31</v>
+      </c>
+      <c r="J27">
+        <v>1.53</v>
+      </c>
+      <c r="K27" s="1">
+        <v>29.07</v>
+      </c>
+      <c r="L27" t="s">
+        <v>117</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" t="s">
+        <v>55</v>
+      </c>
+      <c r="D28" t="s">
+        <v>80</v>
+      </c>
+      <c r="E28" t="s">
+        <v>86</v>
+      </c>
+      <c r="F28">
+        <v>12</v>
+      </c>
+      <c r="G28" t="s">
+        <v>91</v>
+      </c>
+      <c r="H28">
+        <v>1.49</v>
+      </c>
+      <c r="I28" s="1">
+        <v>17.88</v>
+      </c>
+      <c r="J28">
+        <v>1.53</v>
+      </c>
+      <c r="K28" s="1">
+        <v>18.36</v>
+      </c>
+      <c r="L28" t="s">
+        <v>118</v>
+      </c>
+      <c r="M28">
+        <v>10270</v>
+      </c>
+      <c r="N28" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" t="s">
+        <v>34</v>
+      </c>
+      <c r="C29" t="s">
+        <v>38</v>
+      </c>
+      <c r="D29" t="s">
+        <v>63</v>
+      </c>
+      <c r="E29" t="s">
+        <v>86</v>
+      </c>
+      <c r="F29">
+        <v>21.01</v>
+      </c>
+      <c r="G29" t="s">
+        <v>91</v>
+      </c>
+      <c r="H29">
+        <v>1.49</v>
+      </c>
+      <c r="I29" s="1">
+        <v>31.3</v>
+      </c>
+      <c r="J29">
+        <v>1.53</v>
+      </c>
+      <c r="K29" s="1">
+        <v>32.15</v>
+      </c>
+      <c r="L29" t="s">
+        <v>119</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" t="s">
+        <v>25</v>
+      </c>
+      <c r="B30" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" t="s">
+        <v>48</v>
+      </c>
+      <c r="D30" t="s">
+        <v>73</v>
+      </c>
+      <c r="E30" t="s">
+        <v>87</v>
+      </c>
+      <c r="F30">
+        <v>37</v>
+      </c>
+      <c r="G30" t="s">
+        <v>91</v>
+      </c>
+      <c r="H30">
+        <v>1.64</v>
+      </c>
+      <c r="I30" s="1">
+        <v>60.68</v>
+      </c>
+      <c r="J30">
+        <v>1.68</v>
+      </c>
+      <c r="K30" s="1">
+        <v>62.16</v>
+      </c>
+      <c r="L30" t="s">
+        <v>120</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" t="s">
+        <v>34</v>
+      </c>
+      <c r="C31" t="s">
+        <v>46</v>
+      </c>
+      <c r="D31" t="s">
+        <v>71</v>
+      </c>
+      <c r="E31" t="s">
+        <v>87</v>
+      </c>
+      <c r="F31">
+        <v>34</v>
+      </c>
+      <c r="G31" t="s">
+        <v>91</v>
+      </c>
+      <c r="H31">
+        <v>1.64</v>
+      </c>
+      <c r="I31" s="1">
+        <v>55.76</v>
+      </c>
+      <c r="J31">
+        <v>1.68</v>
+      </c>
+      <c r="K31" s="1">
+        <v>57.12</v>
+      </c>
+      <c r="L31" t="s">
+        <v>121</v>
+      </c>
+      <c r="M31">
+        <v>255860</v>
+      </c>
+      <c r="N31" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" t="s">
+        <v>25</v>
+      </c>
+      <c r="B32" t="s">
+        <v>34</v>
+      </c>
+      <c r="C32" t="s">
+        <v>56</v>
+      </c>
+      <c r="D32" t="s">
+        <v>81</v>
+      </c>
+      <c r="E32" t="s">
+        <v>87</v>
+      </c>
+      <c r="F32">
+        <v>48</v>
+      </c>
+      <c r="G32" t="s">
+        <v>91</v>
+      </c>
+      <c r="H32">
+        <v>1.64</v>
+      </c>
+      <c r="I32" s="1">
+        <v>78.72</v>
+      </c>
+      <c r="J32">
+        <v>1.68</v>
+      </c>
+      <c r="K32" s="1">
+        <v>80.64</v>
+      </c>
+      <c r="L32" t="s">
+        <v>122</v>
+      </c>
+      <c r="M32">
+        <v>27032</v>
+      </c>
+      <c r="N32" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
+      <c r="A33" t="s">
+        <v>26</v>
+      </c>
+      <c r="B33" t="s">
+        <v>34</v>
+      </c>
+      <c r="C33" t="s">
+        <v>57</v>
+      </c>
+      <c r="D33" t="s">
+        <v>82</v>
+      </c>
+      <c r="E33" t="s">
+        <v>87</v>
+      </c>
+      <c r="F33">
+        <v>69</v>
+      </c>
+      <c r="G33" t="s">
+        <v>91</v>
+      </c>
+      <c r="H33">
+        <v>1.62</v>
+      </c>
+      <c r="I33" s="1">
+        <v>111.78</v>
+      </c>
+      <c r="J33">
+        <v>1.66</v>
+      </c>
+      <c r="K33" s="1">
+        <v>114.54</v>
+      </c>
+      <c r="L33" t="s">
+        <v>99</v>
+      </c>
+      <c r="M33">
+        <v>111100</v>
+      </c>
+      <c r="N33" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="A34" t="s">
+        <v>27</v>
+      </c>
+      <c r="B34" t="s">
+        <v>34</v>
+      </c>
+      <c r="C34" t="s">
+        <v>39</v>
+      </c>
+      <c r="D34" t="s">
+        <v>64</v>
+      </c>
+      <c r="E34" t="s">
+        <v>87</v>
+      </c>
+      <c r="F34">
+        <v>48.45</v>
+      </c>
+      <c r="G34" t="s">
+        <v>91</v>
+      </c>
+      <c r="H34">
+        <v>1.64</v>
+      </c>
+      <c r="I34" s="1">
+        <v>79.45999999999999</v>
+      </c>
+      <c r="J34">
+        <v>1.68</v>
+      </c>
+      <c r="K34" s="1">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="L34" t="s">
+        <v>123</v>
+      </c>
+      <c r="M34">
+        <v>41867</v>
+      </c>
+      <c r="N34" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
+      <c r="A35" t="s">
+        <v>27</v>
+      </c>
+      <c r="B35" t="s">
+        <v>34</v>
+      </c>
+      <c r="C35" t="s">
+        <v>58</v>
+      </c>
+      <c r="D35" t="s">
+        <v>83</v>
+      </c>
+      <c r="E35" t="s">
+        <v>86</v>
+      </c>
+      <c r="F35">
+        <v>17</v>
+      </c>
+      <c r="G35" t="s">
+        <v>91</v>
+      </c>
+      <c r="H35">
+        <v>1.48</v>
+      </c>
+      <c r="I35" s="1">
+        <v>25.16</v>
+      </c>
+      <c r="J35">
+        <v>1.52</v>
+      </c>
+      <c r="K35" s="1">
+        <v>25.84</v>
+      </c>
+      <c r="L35" t="s">
+        <v>124</v>
+      </c>
+      <c r="M35">
+        <v>75620</v>
+      </c>
+      <c r="N35" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
+      <c r="A36" t="s">
+        <v>28</v>
+      </c>
+      <c r="B36" t="s">
+        <v>34</v>
+      </c>
+      <c r="C36" t="s">
+        <v>55</v>
+      </c>
+      <c r="D36" t="s">
+        <v>80</v>
+      </c>
+      <c r="E36" t="s">
+        <v>86</v>
+      </c>
+      <c r="F36">
+        <v>25</v>
+      </c>
+      <c r="G36" t="s">
+        <v>91</v>
+      </c>
+      <c r="H36">
+        <v>1.48</v>
+      </c>
+      <c r="I36" s="1">
+        <v>37</v>
+      </c>
+      <c r="J36">
+        <v>1.52</v>
+      </c>
+      <c r="K36" s="1">
+        <v>38</v>
+      </c>
+      <c r="L36" t="s">
+        <v>125</v>
+      </c>
+      <c r="M36">
+        <v>10450</v>
+      </c>
+      <c r="N36" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" t="s">
+        <v>28</v>
+      </c>
+      <c r="B37" t="s">
+        <v>34</v>
+      </c>
+      <c r="C37" t="s">
+        <v>37</v>
+      </c>
+      <c r="D37" t="s">
+        <v>62</v>
+      </c>
+      <c r="E37" t="s">
+        <v>87</v>
+      </c>
+      <c r="F37">
+        <v>49.6</v>
+      </c>
+      <c r="G37" t="s">
+        <v>91</v>
+      </c>
+      <c r="H37">
+        <v>1.64</v>
+      </c>
+      <c r="I37" s="1">
+        <v>81.34</v>
+      </c>
+      <c r="J37">
+        <v>1.68</v>
+      </c>
+      <c r="K37" s="1">
+        <v>83.33</v>
+      </c>
+      <c r="L37" t="s">
+        <v>126</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
+      <c r="A38" t="s">
+        <v>28</v>
+      </c>
+      <c r="B38" t="s">
+        <v>34</v>
+      </c>
+      <c r="C38" t="s">
+        <v>59</v>
+      </c>
+      <c r="D38" t="s">
+        <v>84</v>
+      </c>
+      <c r="E38" t="s">
+        <v>86</v>
+      </c>
+      <c r="F38">
+        <v>16.01</v>
+      </c>
+      <c r="G38" t="s">
+        <v>91</v>
+      </c>
+      <c r="H38">
+        <v>1.48</v>
+      </c>
+      <c r="I38" s="1">
+        <v>23.69</v>
+      </c>
+      <c r="J38">
+        <v>1.52</v>
+      </c>
+      <c r="K38" s="1">
+        <v>24.34</v>
+      </c>
+      <c r="L38" t="s">
+        <v>127</v>
+      </c>
+      <c r="M38">
+        <v>133320</v>
+      </c>
+      <c r="N38" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39" t="s">
+        <v>28</v>
+      </c>
+      <c r="B39" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" t="s">
+        <v>60</v>
+      </c>
+      <c r="D39" t="s">
+        <v>85</v>
+      </c>
+      <c r="E39" t="s">
+        <v>87</v>
+      </c>
+      <c r="F39">
+        <v>49</v>
+      </c>
+      <c r="G39" t="s">
+        <v>91</v>
+      </c>
+      <c r="H39">
+        <v>1.64</v>
+      </c>
+      <c r="I39" s="1">
+        <v>80.36</v>
+      </c>
+      <c r="J39">
+        <v>1.68</v>
+      </c>
+      <c r="K39" s="1">
+        <v>82.31999999999999</v>
+      </c>
+      <c r="L39" t="s">
+        <v>128</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
+      <c r="A40" t="s">
+        <v>29</v>
+      </c>
+      <c r="B40" t="s">
+        <v>34</v>
+      </c>
+      <c r="C40" t="s">
+        <v>43</v>
+      </c>
+      <c r="D40" t="s">
+        <v>68</v>
+      </c>
+      <c r="E40" t="s">
+        <v>86</v>
+      </c>
+      <c r="F40">
+        <v>31</v>
+      </c>
+      <c r="G40" t="s">
+        <v>91</v>
+      </c>
+      <c r="H40">
+        <v>1.49</v>
+      </c>
+      <c r="I40" s="1">
+        <v>46.19</v>
+      </c>
+      <c r="J40">
+        <v>1.53</v>
+      </c>
+      <c r="K40" s="1">
+        <v>47.43</v>
+      </c>
+      <c r="L40" t="s">
+        <v>129</v>
+      </c>
+      <c r="M40">
+        <v>7535</v>
+      </c>
+      <c r="N40" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="A41" t="s">
+        <v>29</v>
+      </c>
+      <c r="B41" t="s">
+        <v>34</v>
+      </c>
+      <c r="C41" t="s">
+        <v>45</v>
+      </c>
+      <c r="D41" t="s">
+        <v>70</v>
+      </c>
+      <c r="E41" t="s">
+        <v>88</v>
+      </c>
+      <c r="F41">
+        <v>43</v>
+      </c>
+      <c r="G41" t="s">
+        <v>91</v>
+      </c>
+      <c r="H41">
+        <v>1.74</v>
+      </c>
+      <c r="I41" s="1">
+        <v>74.81999999999999</v>
+      </c>
+      <c r="J41">
+        <v>1.79</v>
+      </c>
+      <c r="K41" s="1">
+        <v>76.97</v>
+      </c>
+      <c r="L41" t="s">
+        <v>130</v>
+      </c>
+      <c r="M41">
+        <v>182918</v>
+      </c>
+      <c r="N41" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
+      <c r="A42" t="s">
+        <v>29</v>
+      </c>
+      <c r="B42" t="s">
+        <v>34</v>
+      </c>
+      <c r="C42" t="s">
+        <v>40</v>
+      </c>
+      <c r="D42" t="s">
+        <v>65</v>
+      </c>
+      <c r="E42" t="s">
+        <v>87</v>
+      </c>
+      <c r="F42">
+        <v>65</v>
+      </c>
+      <c r="G42" t="s">
+        <v>91</v>
+      </c>
+      <c r="H42">
+        <v>1.66</v>
+      </c>
+      <c r="I42" s="1">
+        <v>107.9</v>
+      </c>
+      <c r="J42">
+        <v>1.7</v>
+      </c>
+      <c r="K42" s="1">
+        <v>110.5</v>
+      </c>
+      <c r="L42" t="s">
+        <v>107</v>
+      </c>
+      <c r="M42">
+        <v>286990</v>
+      </c>
+      <c r="N42" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
+      <c r="A43" t="s">
+        <v>30</v>
+      </c>
+      <c r="B43" t="s">
+        <v>34</v>
+      </c>
+      <c r="C43" t="s">
+        <v>46</v>
+      </c>
+      <c r="D43" t="s">
+        <v>71</v>
+      </c>
+      <c r="E43" t="s">
+        <v>87</v>
+      </c>
+      <c r="F43">
+        <v>29.07</v>
+      </c>
+      <c r="G43" t="s">
+        <v>91</v>
+      </c>
+      <c r="H43">
+        <v>1.7</v>
+      </c>
+      <c r="I43" s="1">
+        <v>49.42</v>
+      </c>
+      <c r="J43">
+        <v>1.74</v>
+      </c>
+      <c r="K43" s="1">
+        <v>50.58</v>
+      </c>
+      <c r="L43" t="s">
+        <v>131</v>
+      </c>
+      <c r="M43">
+        <v>256160</v>
+      </c>
+      <c r="N43" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
+      <c r="A44" t="s">
+        <v>30</v>
+      </c>
+      <c r="B44" t="s">
+        <v>34</v>
+      </c>
+      <c r="C44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D44" t="s">
+        <v>61</v>
+      </c>
+      <c r="E44" t="s">
+        <v>86</v>
+      </c>
+      <c r="F44">
+        <v>31.51</v>
+      </c>
+      <c r="G44" t="s">
+        <v>91</v>
+      </c>
+      <c r="H44">
+        <v>1.51</v>
+      </c>
+      <c r="I44" s="1">
+        <v>47.58</v>
+      </c>
+      <c r="J44">
+        <v>1.55</v>
+      </c>
+      <c r="K44" s="1">
+        <v>48.84</v>
+      </c>
+      <c r="L44" t="s">
+        <v>132</v>
+      </c>
+      <c r="M44">
+        <v>235832</v>
+      </c>
+      <c r="N44" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
+      <c r="A45" t="s">
+        <v>31</v>
+      </c>
+      <c r="B45" t="s">
+        <v>34</v>
+      </c>
+      <c r="C45" t="s">
+        <v>49</v>
+      </c>
+      <c r="D45" t="s">
+        <v>74</v>
+      </c>
+      <c r="E45" t="s">
+        <v>86</v>
+      </c>
+      <c r="F45">
+        <v>40</v>
+      </c>
+      <c r="G45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H45">
+        <v>1.51</v>
+      </c>
+      <c r="I45" s="1">
+        <v>60.4</v>
+      </c>
+      <c r="J45">
+        <v>1.55</v>
+      </c>
+      <c r="K45" s="1">
+        <v>62</v>
+      </c>
+      <c r="L45" t="s">
+        <v>133</v>
+      </c>
+      <c r="M45">
+        <v>300950</v>
+      </c>
+      <c r="N45" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
+      <c r="A46" t="s">
+        <v>31</v>
+      </c>
+      <c r="B46" t="s">
+        <v>34</v>
+      </c>
+      <c r="C46" t="s">
+        <v>44</v>
+      </c>
+      <c r="D46" t="s">
+        <v>69</v>
+      </c>
+      <c r="E46" t="s">
+        <v>87</v>
+      </c>
+      <c r="F46">
+        <v>48.1</v>
+      </c>
+      <c r="G46" t="s">
+        <v>91</v>
+      </c>
+      <c r="H46">
+        <v>1.7</v>
+      </c>
+      <c r="I46" s="1">
+        <v>81.77</v>
+      </c>
+      <c r="J46">
+        <v>1.74</v>
+      </c>
+      <c r="K46" s="1">
+        <v>83.69</v>
+      </c>
+      <c r="L46" t="s">
+        <v>134</v>
+      </c>
+      <c r="M46">
+        <v>285933</v>
+      </c>
+      <c r="N46" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
+      <c r="A47" t="s">
+        <v>31</v>
+      </c>
+      <c r="B47" t="s">
+        <v>34</v>
+      </c>
+      <c r="C47" t="s">
+        <v>37</v>
+      </c>
+      <c r="D47" t="s">
+        <v>62</v>
+      </c>
+      <c r="E47" t="s">
+        <v>87</v>
+      </c>
+      <c r="F47">
+        <v>55</v>
+      </c>
+      <c r="G47" t="s">
+        <v>91</v>
+      </c>
+      <c r="H47">
+        <v>1.7</v>
+      </c>
+      <c r="I47" s="1">
+        <v>93.5</v>
+      </c>
+      <c r="J47">
+        <v>1.74</v>
+      </c>
+      <c r="K47" s="1">
+        <v>95.7</v>
+      </c>
+      <c r="L47" t="s">
+        <v>135</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
+      <c r="A48" t="s">
+        <v>32</v>
+      </c>
+      <c r="B48" t="s">
+        <v>34</v>
+      </c>
+      <c r="C48" t="s">
+        <v>50</v>
+      </c>
+      <c r="D48" t="s">
+        <v>75</v>
+      </c>
+      <c r="E48" t="s">
+        <v>87</v>
+      </c>
+      <c r="F48">
+        <v>46.15</v>
+      </c>
+      <c r="G48" t="s">
+        <v>91</v>
+      </c>
+      <c r="H48">
+        <v>1.7</v>
+      </c>
+      <c r="I48" s="1">
+        <v>78.45999999999999</v>
+      </c>
+      <c r="J48">
+        <v>1.74</v>
+      </c>
+      <c r="K48" s="1">
+        <v>80.3</v>
+      </c>
+      <c r="L48" t="s">
+        <v>136</v>
+      </c>
+      <c r="M48">
+        <v>291490</v>
+      </c>
+      <c r="N48" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14">
+      <c r="A49" t="s">
+        <v>32</v>
+      </c>
+      <c r="B49" t="s">
+        <v>34</v>
+      </c>
+      <c r="C49" t="s">
+        <v>54</v>
+      </c>
+      <c r="D49" t="s">
+        <v>79</v>
+      </c>
+      <c r="E49" t="s">
+        <v>86</v>
+      </c>
+      <c r="F49">
+        <v>25.01</v>
+      </c>
+      <c r="G49" t="s">
+        <v>91</v>
+      </c>
+      <c r="H49">
+        <v>1.5</v>
+      </c>
+      <c r="I49" s="1">
+        <v>37.52</v>
+      </c>
+      <c r="J49">
+        <v>1.54</v>
+      </c>
+      <c r="K49" s="1">
+        <v>38.52</v>
+      </c>
+      <c r="L49" t="s">
+        <v>137</v>
+      </c>
+      <c r="M49">
+        <v>327070</v>
+      </c>
+      <c r="N49" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14">
+      <c r="A50" t="s">
+        <v>32</v>
+      </c>
+      <c r="B50" t="s">
+        <v>34</v>
+      </c>
+      <c r="C50" t="s">
+        <v>39</v>
+      </c>
+      <c r="D50" t="s">
+        <v>64</v>
+      </c>
+      <c r="E50" t="s">
+        <v>87</v>
+      </c>
+      <c r="F50">
+        <v>51.85</v>
+      </c>
+      <c r="G50" t="s">
+        <v>91</v>
+      </c>
+      <c r="H50">
+        <v>1.7</v>
+      </c>
+      <c r="I50" s="1">
+        <v>88.14</v>
+      </c>
+      <c r="J50">
+        <v>1.74</v>
+      </c>
+      <c r="K50" s="1">
+        <v>90.22</v>
+      </c>
+      <c r="L50" t="s">
+        <v>138</v>
+      </c>
+      <c r="M50">
+        <v>42235</v>
+      </c>
+      <c r="N50" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14">
+      <c r="A51" t="s">
+        <v>33</v>
+      </c>
+      <c r="B51" t="s">
+        <v>34</v>
+      </c>
+      <c r="C51" t="s">
+        <v>40</v>
+      </c>
+      <c r="D51" t="s">
+        <v>65</v>
+      </c>
+      <c r="E51" t="s">
+        <v>87</v>
+      </c>
+      <c r="F51">
+        <v>30</v>
+      </c>
+      <c r="G51" t="s">
+        <v>91</v>
+      </c>
+      <c r="H51">
+        <v>1.73</v>
+      </c>
+      <c r="I51" s="1">
+        <v>51.9</v>
+      </c>
+      <c r="J51">
+        <v>1.77</v>
+      </c>
+      <c r="K51" s="1">
+        <v>53.1</v>
+      </c>
+      <c r="L51" t="s">
+        <v>139</v>
+      </c>
+      <c r="M51">
+        <v>287420</v>
+      </c>
+      <c r="N51" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14">
+      <c r="A52" t="s">
+        <v>33</v>
+      </c>
+      <c r="B52" t="s">
+        <v>34</v>
+      </c>
+      <c r="C52" t="s">
+        <v>51</v>
+      </c>
+      <c r="D52" t="s">
         <v>76</v>
       </c>
-      <c r="L20">
-        <v>41492</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12">
-      <c r="A23" s="3" t="s">
+      <c r="E52" t="s">
+        <v>87</v>
+      </c>
+      <c r="F52">
+        <v>54.83</v>
+      </c>
+      <c r="G52" t="s">
+        <v>91</v>
+      </c>
+      <c r="H52">
+        <v>1.73</v>
+      </c>
+      <c r="I52" s="1">
+        <v>94.86</v>
+      </c>
+      <c r="J52">
+        <v>1.77</v>
+      </c>
+      <c r="K52" s="1">
+        <v>97.05</v>
+      </c>
+      <c r="L52" t="s">
+        <v>140</v>
+      </c>
+      <c r="M52">
+        <v>265247</v>
+      </c>
+      <c r="N52" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14">
+      <c r="A53" t="s">
+        <v>33</v>
+      </c>
+      <c r="B53" t="s">
+        <v>34</v>
+      </c>
+      <c r="C53" t="s">
+        <v>52</v>
+      </c>
+      <c r="D53" t="s">
         <v>77</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-    </row>
-    <row r="24" spans="1:12">
-      <c r="A24" s="4" t="s">
+      <c r="E53" t="s">
+        <v>87</v>
+      </c>
+      <c r="F53">
+        <v>39</v>
+      </c>
+      <c r="G53" t="s">
+        <v>91</v>
+      </c>
+      <c r="H53">
+        <v>1.73</v>
+      </c>
+      <c r="I53" s="1">
+        <v>67.47</v>
+      </c>
+      <c r="J53">
+        <v>1.77</v>
+      </c>
+      <c r="K53" s="1">
+        <v>69.03</v>
+      </c>
+      <c r="L53" t="s">
+        <v>141</v>
+      </c>
+      <c r="M53">
+        <v>260190</v>
+      </c>
+      <c r="N53" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14">
+      <c r="A54" t="s">
+        <v>33</v>
+      </c>
+      <c r="B54" t="s">
+        <v>34</v>
+      </c>
+      <c r="C54" t="s">
+        <v>54</v>
+      </c>
+      <c r="D54" t="s">
+        <v>79</v>
+      </c>
+      <c r="E54" t="s">
+        <v>86</v>
+      </c>
+      <c r="F54">
+        <v>27</v>
+      </c>
+      <c r="G54" t="s">
+        <v>91</v>
+      </c>
+      <c r="H54">
+        <v>1.5</v>
+      </c>
+      <c r="I54" s="1">
+        <v>40.5</v>
+      </c>
+      <c r="J54">
+        <v>1.54</v>
+      </c>
+      <c r="K54" s="1">
+        <v>41.58</v>
+      </c>
+      <c r="L54" t="s">
+        <v>126</v>
+      </c>
+      <c r="M54">
+        <v>327405</v>
+      </c>
+      <c r="N54" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14">
+      <c r="A55" t="s">
+        <v>33</v>
+      </c>
+      <c r="B55" t="s">
+        <v>34</v>
+      </c>
+      <c r="C55" t="s">
+        <v>50</v>
+      </c>
+      <c r="D55" t="s">
+        <v>75</v>
+      </c>
+      <c r="E55" t="s">
+        <v>87</v>
+      </c>
+      <c r="F55">
+        <v>14</v>
+      </c>
+      <c r="G55" t="s">
+        <v>91</v>
+      </c>
+      <c r="H55">
+        <v>1.73</v>
+      </c>
+      <c r="I55" s="1">
+        <v>24.22</v>
+      </c>
+      <c r="J55">
+        <v>1.77</v>
+      </c>
+      <c r="K55" s="1">
+        <v>24.78</v>
+      </c>
+      <c r="L55" t="s">
+        <v>142</v>
+      </c>
+      <c r="M55">
+        <v>291780</v>
+      </c>
+      <c r="N55" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14">
+      <c r="A56" t="s">
+        <v>33</v>
+      </c>
+      <c r="B56" t="s">
+        <v>34</v>
+      </c>
+      <c r="C56" t="s">
+        <v>42</v>
+      </c>
+      <c r="D56" t="s">
+        <v>67</v>
+      </c>
+      <c r="E56" t="s">
+        <v>86</v>
+      </c>
+      <c r="F56">
+        <v>22</v>
+      </c>
+      <c r="G56" t="s">
+        <v>91</v>
+      </c>
+      <c r="H56">
+        <v>1.5</v>
+      </c>
+      <c r="I56" s="1">
+        <v>33</v>
+      </c>
+      <c r="J56">
+        <v>1.54</v>
+      </c>
+      <c r="K56" s="1">
+        <v>33.88</v>
+      </c>
+      <c r="L56" t="s">
+        <v>143</v>
+      </c>
+      <c r="M56">
+        <v>21275</v>
+      </c>
+      <c r="N56" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14">
+      <c r="A57" t="s">
+        <v>33</v>
+      </c>
+      <c r="B57" t="s">
+        <v>34</v>
+      </c>
+      <c r="C57" t="s">
+        <v>47</v>
+      </c>
+      <c r="D57" t="s">
+        <v>72</v>
+      </c>
+      <c r="E57" t="s">
+        <v>87</v>
+      </c>
+      <c r="F57">
+        <v>38.56</v>
+      </c>
+      <c r="G57" t="s">
+        <v>91</v>
+      </c>
+      <c r="H57">
+        <v>1.73</v>
+      </c>
+      <c r="I57" s="1">
+        <v>66.70999999999999</v>
+      </c>
+      <c r="J57">
+        <v>1.77</v>
+      </c>
+      <c r="K57" s="1">
+        <v>68.25</v>
+      </c>
+      <c r="L57" t="s">
+        <v>144</v>
+      </c>
+      <c r="M57">
+        <v>0</v>
+      </c>
+      <c r="N57" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14">
+      <c r="A58" t="s">
+        <v>33</v>
+      </c>
+      <c r="B58" t="s">
+        <v>34</v>
+      </c>
+      <c r="C58" t="s">
+        <v>48</v>
+      </c>
+      <c r="D58" t="s">
+        <v>73</v>
+      </c>
+      <c r="E58" t="s">
+        <v>87</v>
+      </c>
+      <c r="F58">
+        <v>24.36</v>
+      </c>
+      <c r="G58" t="s">
+        <v>91</v>
+      </c>
+      <c r="H58">
+        <v>1.73</v>
+      </c>
+      <c r="I58" s="1">
+        <v>42.14</v>
+      </c>
+      <c r="J58">
+        <v>1.77</v>
+      </c>
+      <c r="K58" s="1">
+        <v>43.12</v>
+      </c>
+      <c r="L58" t="s">
+        <v>145</v>
+      </c>
+      <c r="M58">
+        <v>0</v>
+      </c>
+      <c r="N58" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14">
+      <c r="A59" t="s">
+        <v>33</v>
+      </c>
+      <c r="B59" t="s">
+        <v>34</v>
+      </c>
+      <c r="C59" t="s">
+        <v>46</v>
+      </c>
+      <c r="D59" t="s">
+        <v>71</v>
+      </c>
+      <c r="E59" t="s">
+        <v>87</v>
+      </c>
+      <c r="F59">
+        <v>16</v>
+      </c>
+      <c r="G59" t="s">
+        <v>91</v>
+      </c>
+      <c r="H59">
+        <v>1.73</v>
+      </c>
+      <c r="I59" s="1">
+        <v>27.68</v>
+      </c>
+      <c r="J59">
+        <v>1.77</v>
+      </c>
+      <c r="K59" s="1">
+        <v>28.32</v>
+      </c>
+      <c r="L59" t="s">
+        <v>146</v>
+      </c>
+      <c r="M59">
+        <v>256400</v>
+      </c>
+      <c r="N59" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14">
+      <c r="A60" t="s">
+        <v>33</v>
+      </c>
+      <c r="B60" t="s">
+        <v>34</v>
+      </c>
+      <c r="C60" t="s">
+        <v>44</v>
+      </c>
+      <c r="D60" t="s">
+        <v>69</v>
+      </c>
+      <c r="E60" t="s">
+        <v>87</v>
+      </c>
+      <c r="F60">
+        <v>27.01</v>
+      </c>
+      <c r="G60" t="s">
+        <v>91</v>
+      </c>
+      <c r="H60">
+        <v>1.73</v>
+      </c>
+      <c r="I60" s="1">
+        <v>46.73</v>
+      </c>
+      <c r="J60">
+        <v>1.77</v>
+      </c>
+      <c r="K60" s="1">
+        <v>47.81</v>
+      </c>
+      <c r="L60" t="s">
+        <v>115</v>
+      </c>
+      <c r="M60">
+        <v>268295</v>
+      </c>
+      <c r="N60" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14">
+      <c r="A61" t="s">
+        <v>33</v>
+      </c>
+      <c r="B61" t="s">
+        <v>34</v>
+      </c>
+      <c r="C61" t="s">
+        <v>60</v>
+      </c>
+      <c r="D61" t="s">
+        <v>85</v>
+      </c>
+      <c r="E61" t="s">
+        <v>87</v>
+      </c>
+      <c r="F61">
+        <v>29.01</v>
+      </c>
+      <c r="G61" t="s">
+        <v>91</v>
+      </c>
+      <c r="H61">
+        <v>1.73</v>
+      </c>
+      <c r="I61" s="1">
+        <v>50.19</v>
+      </c>
+      <c r="J61">
+        <v>1.77</v>
+      </c>
+      <c r="K61" s="1">
+        <v>51.35</v>
+      </c>
+      <c r="L61" t="s">
+        <v>147</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+      <c r="N61" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14">
+      <c r="A62" t="s">
+        <v>33</v>
+      </c>
+      <c r="B62" t="s">
+        <v>34</v>
+      </c>
+      <c r="C62" t="s">
+        <v>57</v>
+      </c>
+      <c r="D62" t="s">
+        <v>82</v>
+      </c>
+      <c r="E62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F62">
+        <v>37.01</v>
+      </c>
+      <c r="G62" t="s">
+        <v>91</v>
+      </c>
+      <c r="H62">
+        <v>1.73</v>
+      </c>
+      <c r="I62" s="1">
+        <v>64.03</v>
+      </c>
+      <c r="J62">
+        <v>1.77</v>
+      </c>
+      <c r="K62" s="1">
+        <v>65.51000000000001</v>
+      </c>
+      <c r="L62" t="s">
+        <v>132</v>
+      </c>
+      <c r="M62">
+        <v>111500</v>
+      </c>
+      <c r="N62" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14">
+      <c r="A63" t="s">
+        <v>33</v>
+      </c>
+      <c r="B63" t="s">
+        <v>34</v>
+      </c>
+      <c r="C63" t="s">
+        <v>39</v>
+      </c>
+      <c r="D63" t="s">
+        <v>64</v>
+      </c>
+      <c r="E63" t="s">
+        <v>87</v>
+      </c>
+      <c r="F63">
+        <v>22.01</v>
+      </c>
+      <c r="G63" t="s">
+        <v>91</v>
+      </c>
+      <c r="H63">
+        <v>1.73</v>
+      </c>
+      <c r="I63" s="1">
+        <v>38.08</v>
+      </c>
+      <c r="J63">
+        <v>1.77</v>
+      </c>
+      <c r="K63" s="1">
+        <v>38.96</v>
+      </c>
+      <c r="L63" t="s">
+        <v>104</v>
+      </c>
+      <c r="M63">
+        <v>42399</v>
+      </c>
+      <c r="N63" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14">
+      <c r="A64" t="s">
+        <v>33</v>
+      </c>
+      <c r="B64" t="s">
+        <v>34</v>
+      </c>
+      <c r="C64" t="s">
+        <v>39</v>
+      </c>
+      <c r="D64" t="s">
+        <v>64</v>
+      </c>
+      <c r="E64" t="s">
+        <v>89</v>
+      </c>
+      <c r="F64">
+        <v>1</v>
+      </c>
+      <c r="G64" t="s">
+        <v>92</v>
+      </c>
+      <c r="H64">
+        <v>24.99</v>
+      </c>
+      <c r="I64" s="1">
+        <v>24.99</v>
+      </c>
+      <c r="J64">
+        <v>24.99</v>
+      </c>
+      <c r="K64" s="1">
+        <v>24.99</v>
+      </c>
+      <c r="L64" t="s">
+        <v>104</v>
+      </c>
+      <c r="M64">
+        <v>42399</v>
+      </c>
+      <c r="N64" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14">
+      <c r="A65" t="s">
+        <v>33</v>
+      </c>
+      <c r="B65" t="s">
+        <v>34</v>
+      </c>
+      <c r="C65" t="s">
+        <v>58</v>
+      </c>
+      <c r="D65" t="s">
+        <v>83</v>
+      </c>
+      <c r="E65" t="s">
+        <v>86</v>
+      </c>
+      <c r="F65">
+        <v>6</v>
+      </c>
+      <c r="G65" t="s">
+        <v>91</v>
+      </c>
+      <c r="H65">
+        <v>1.5</v>
+      </c>
+      <c r="I65" s="1">
+        <v>9</v>
+      </c>
+      <c r="J65">
+        <v>1.54</v>
+      </c>
+      <c r="K65" s="1">
+        <v>9.24</v>
+      </c>
+      <c r="L65" t="s">
+        <v>148</v>
+      </c>
+      <c r="M65">
+        <v>75676</v>
+      </c>
+      <c r="N65" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14">
+      <c r="A66" t="s">
+        <v>33</v>
+      </c>
+      <c r="B66" t="s">
+        <v>34</v>
+      </c>
+      <c r="C66" t="s">
+        <v>49</v>
+      </c>
+      <c r="D66" t="s">
+        <v>74</v>
+      </c>
+      <c r="E66" t="s">
+        <v>86</v>
+      </c>
+      <c r="F66">
+        <v>18</v>
+      </c>
+      <c r="G66" t="s">
+        <v>91</v>
+      </c>
+      <c r="H66">
+        <v>1.5</v>
+      </c>
+      <c r="I66" s="1">
+        <v>27</v>
+      </c>
+      <c r="J66">
+        <v>1.54</v>
+      </c>
+      <c r="K66" s="1">
+        <v>27.72</v>
+      </c>
+      <c r="L66" t="s">
+        <v>149</v>
+      </c>
+      <c r="M66">
+        <v>301160</v>
+      </c>
+      <c r="N66" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14">
+      <c r="A67" t="s">
+        <v>33</v>
+      </c>
+      <c r="B67" t="s">
+        <v>34</v>
+      </c>
+      <c r="C67" t="s">
+        <v>43</v>
+      </c>
+      <c r="D67" t="s">
+        <v>68</v>
+      </c>
+      <c r="E67" t="s">
+        <v>86</v>
+      </c>
+      <c r="F67">
+        <v>15</v>
+      </c>
+      <c r="G67" t="s">
+        <v>91</v>
+      </c>
+      <c r="H67">
+        <v>1.5</v>
+      </c>
+      <c r="I67" s="1">
+        <v>22.5</v>
+      </c>
+      <c r="J67">
+        <v>1.54</v>
+      </c>
+      <c r="K67" s="1">
+        <v>23.1</v>
+      </c>
+      <c r="L67" t="s">
+        <v>150</v>
+      </c>
+      <c r="M67">
+        <v>7755</v>
+      </c>
+      <c r="N67" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14">
+      <c r="A68" t="s">
+        <v>33</v>
+      </c>
+      <c r="B68" t="s">
+        <v>34</v>
+      </c>
+      <c r="C68" t="s">
+        <v>53</v>
+      </c>
+      <c r="D68" t="s">
         <v>78</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D24" s="4" t="s">
+      <c r="E68" t="s">
+        <v>87</v>
+      </c>
+      <c r="F68">
+        <v>29.77</v>
+      </c>
+      <c r="G68" t="s">
+        <v>91</v>
+      </c>
+      <c r="H68">
+        <v>1.73</v>
+      </c>
+      <c r="I68" s="1">
+        <v>51.5</v>
+      </c>
+      <c r="J68">
+        <v>1.77</v>
+      </c>
+      <c r="K68" s="1">
+        <v>52.69</v>
+      </c>
+      <c r="L68" t="s">
+        <v>111</v>
+      </c>
+      <c r="M68">
+        <v>236251</v>
+      </c>
+      <c r="N68" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14">
+      <c r="A69" t="s">
+        <v>33</v>
+      </c>
+      <c r="B69" t="s">
+        <v>34</v>
+      </c>
+      <c r="C69" t="s">
+        <v>56</v>
+      </c>
+      <c r="D69" t="s">
         <v>81</v>
       </c>
-      <c r="E24" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12">
-      <c r="A25" s="5" t="s">
+      <c r="E69" t="s">
+        <v>87</v>
+      </c>
+      <c r="F69">
+        <v>29</v>
+      </c>
+      <c r="G69" t="s">
+        <v>91</v>
+      </c>
+      <c r="H69">
+        <v>1.73</v>
+      </c>
+      <c r="I69" s="1">
+        <v>50.17</v>
+      </c>
+      <c r="J69">
+        <v>1.77</v>
+      </c>
+      <c r="K69" s="1">
+        <v>51.33</v>
+      </c>
+      <c r="L69" t="s">
+        <v>151</v>
+      </c>
+      <c r="M69">
+        <v>27540</v>
+      </c>
+      <c r="N69" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14">
+      <c r="A70" t="s">
+        <v>33</v>
+      </c>
+      <c r="B70" t="s">
+        <v>34</v>
+      </c>
+      <c r="C70" t="s">
         <v>56</v>
       </c>
-      <c r="B25" s="6">
-        <v>551.6799999999999</v>
-      </c>
-      <c r="C25" s="6">
-        <v>13</v>
-      </c>
-      <c r="D25" s="7">
-        <v>1.5028</v>
-      </c>
-      <c r="E25" s="6">
-        <v>829.04</v>
-      </c>
-      <c r="F25" s="6">
-        <v>851.11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12">
-      <c r="A26" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B26" s="6">
-        <v>149.72</v>
-      </c>
-      <c r="C26" s="6">
-        <v>5</v>
-      </c>
-      <c r="D26" s="7">
-        <v>1.4534</v>
-      </c>
-      <c r="E26" s="6">
-        <v>217.6</v>
-      </c>
-      <c r="F26" s="6">
-        <v>223.59</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12">
-      <c r="A27" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B27" s="6">
-        <v>44</v>
-      </c>
-      <c r="C27" s="6">
+      <c r="D70" t="s">
+        <v>81</v>
+      </c>
+      <c r="E70" t="s">
+        <v>90</v>
+      </c>
+      <c r="F70">
         <v>1</v>
       </c>
-      <c r="D27" s="7">
-        <v>1.7</v>
-      </c>
-      <c r="E27" s="6">
-        <v>74.8</v>
-      </c>
-      <c r="F27" s="6">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12">
-      <c r="A28" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B28" s="9">
-        <v>745.4</v>
-      </c>
-      <c r="C28" s="9">
-        <v>19</v>
-      </c>
-      <c r="D28" s="7"/>
-      <c r="E28" s="9">
-        <v>1121.44</v>
-      </c>
-      <c r="F28" s="9">
-        <v>1151.7</v>
+      <c r="G70" t="s">
+        <v>92</v>
+      </c>
+      <c r="H70">
+        <v>14.99</v>
+      </c>
+      <c r="I70" s="1">
+        <v>14.99</v>
+      </c>
+      <c r="J70">
+        <v>14.99</v>
+      </c>
+      <c r="K70" s="1">
+        <v>14.99</v>
+      </c>
+      <c r="L70" t="s">
+        <v>151</v>
+      </c>
+      <c r="M70">
+        <v>27540</v>
+      </c>
+      <c r="N70" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14">
+      <c r="A71" t="s">
+        <v>33</v>
+      </c>
+      <c r="B71" t="s">
+        <v>34</v>
+      </c>
+      <c r="C71" t="s">
+        <v>37</v>
+      </c>
+      <c r="D71" t="s">
+        <v>62</v>
+      </c>
+      <c r="E71" t="s">
+        <v>87</v>
+      </c>
+      <c r="F71">
+        <v>17.63</v>
+      </c>
+      <c r="G71" t="s">
+        <v>91</v>
+      </c>
+      <c r="H71">
+        <v>1.73</v>
+      </c>
+      <c r="I71" s="1">
+        <v>30.5</v>
+      </c>
+      <c r="J71">
+        <v>1.77</v>
+      </c>
+      <c r="K71" s="1">
+        <v>31.21</v>
+      </c>
+      <c r="L71" t="s">
+        <v>152</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+      <c r="N71" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14">
+      <c r="A74" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B74" s="3"/>
+      <c r="C74" s="3"/>
+      <c r="D74" s="3"/>
+      <c r="E74" s="3"/>
+      <c r="F74" s="3"/>
+    </row>
+    <row r="75" spans="1:14">
+      <c r="A75" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14">
+      <c r="A76" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B76" s="6">
+        <v>1817.01</v>
+      </c>
+      <c r="C76" s="6">
+        <v>45</v>
+      </c>
+      <c r="D76" s="7">
+        <v>1.6216</v>
+      </c>
+      <c r="E76" s="6">
+        <v>2946.47</v>
+      </c>
+      <c r="F76" s="6">
+        <v>3019.16</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14">
+      <c r="A77" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B77" s="6">
+        <v>518.5700000000001</v>
+      </c>
+      <c r="C77" s="6">
+        <v>21</v>
+      </c>
+      <c r="D77" s="7">
+        <v>1.4807</v>
+      </c>
+      <c r="E77" s="6">
+        <v>767.86</v>
+      </c>
+      <c r="F77" s="6">
+        <v>788.62</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14">
+      <c r="A78" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B78" s="6">
+        <v>87</v>
+      </c>
+      <c r="C78" s="6">
+        <v>2</v>
+      </c>
+      <c r="D78" s="7">
+        <v>1.7198</v>
+      </c>
+      <c r="E78" s="6">
+        <v>149.62</v>
+      </c>
+      <c r="F78" s="6">
+        <v>153.97</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14">
+      <c r="A79" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B79" s="6">
+        <v>1</v>
+      </c>
+      <c r="C79" s="6">
+        <v>1</v>
+      </c>
+      <c r="D79" s="7">
+        <v>24.99</v>
+      </c>
+      <c r="E79" s="6">
+        <v>24.99</v>
+      </c>
+      <c r="F79" s="6">
+        <v>24.99</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14">
+      <c r="A80" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B80" s="6">
+        <v>1</v>
+      </c>
+      <c r="C80" s="6">
+        <v>1</v>
+      </c>
+      <c r="D80" s="7">
+        <v>14.99</v>
+      </c>
+      <c r="E80" s="6">
+        <v>14.99</v>
+      </c>
+      <c r="F80" s="6">
+        <v>14.99</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="A81" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="B81" s="9">
+        <v>2424.58</v>
+      </c>
+      <c r="C81" s="9">
+        <v>70</v>
+      </c>
+      <c r="D81" s="7"/>
+      <c r="E81" s="9">
+        <v>3903.93</v>
+      </c>
+      <c r="F81" s="9">
+        <v>4001.73</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A74:F74"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ДОБРИЧКА/ОБЩИНА ДОБРИЧКА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ДОБРИЧКА/ОБЩИНА ДОБРИЧКА.xlsx
@@ -703,7 +703,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -4278,7 +4278,7 @@
         <v>45</v>
       </c>
       <c r="D76" s="7">
-        <v>1.6216</v>
+        <v>1.621604</v>
       </c>
       <c r="E76" s="6">
         <v>2946.47</v>
@@ -4298,7 +4298,7 @@
         <v>21</v>
       </c>
       <c r="D77" s="7">
-        <v>1.4807</v>
+        <v>1.480726</v>
       </c>
       <c r="E77" s="6">
         <v>767.86</v>
@@ -4318,7 +4318,7 @@
         <v>2</v>
       </c>
       <c r="D78" s="7">
-        <v>1.7198</v>
+        <v>1.71977</v>
       </c>
       <c r="E78" s="6">
         <v>149.62</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ДОБРИЧКА/ОБЩИНА ДОБРИЧКА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ДОБРИЧКА/ОБЩИНА ДОБРИЧКА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="228">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -1094,7 +1097,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N81"/>
+  <dimension ref="A1:O81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -1107,13 +1110,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1156,2756 +1159,2945 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F2">
         <v>33.82</v>
       </c>
       <c r="G2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H2">
+        <v>1.359</v>
+      </c>
+      <c r="I2" s="1">
         <v>1.46</v>
       </c>
-      <c r="I2" s="1">
-        <v>49.38</v>
-      </c>
       <c r="J2">
+        <v>49.3772</v>
+      </c>
+      <c r="K2" s="1">
         <v>1.5</v>
       </c>
-      <c r="K2" s="1">
+      <c r="L2" s="1">
         <v>50.73</v>
       </c>
-      <c r="L2" t="s">
-        <v>93</v>
-      </c>
-      <c r="M2">
+      <c r="M2" t="s">
+        <v>94</v>
+      </c>
+      <c r="N2">
         <v>234743</v>
       </c>
-      <c r="N2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F3">
+        <v>49.349</v>
+      </c>
+      <c r="G3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H3">
+        <v>1.406</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.48</v>
+      </c>
+      <c r="J3">
+        <v>73.03652</v>
+      </c>
+      <c r="K3" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="L3" s="1">
+        <v>75.01048</v>
+      </c>
+      <c r="M3" t="s">
+        <v>95</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" t="s">
         <v>87</v>
       </c>
-      <c r="F3">
-        <v>49.35</v>
-      </c>
-      <c r="G3" t="s">
-        <v>91</v>
-      </c>
-      <c r="H3">
+      <c r="F4">
+        <v>16.887</v>
+      </c>
+      <c r="G4" t="s">
+        <v>92</v>
+      </c>
+      <c r="H4">
+        <v>1.359</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.46</v>
+      </c>
+      <c r="J4">
+        <v>24.65502</v>
+      </c>
+      <c r="K4" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="L4" s="1">
+        <v>25.3305</v>
+      </c>
+      <c r="M4" t="s">
+        <v>96</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F5">
+        <v>45.461</v>
+      </c>
+      <c r="G5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H5">
+        <v>1.406</v>
+      </c>
+      <c r="I5" s="1">
         <v>1.48</v>
       </c>
-      <c r="I3" s="1">
-        <v>73.04000000000001</v>
-      </c>
-      <c r="J3">
+      <c r="J5">
+        <v>67.28228</v>
+      </c>
+      <c r="K5" s="1">
         <v>1.52</v>
       </c>
-      <c r="K3" s="1">
-        <v>75.01000000000001</v>
-      </c>
-      <c r="L3" t="s">
-        <v>94</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E4" t="s">
-        <v>86</v>
-      </c>
-      <c r="F4">
-        <v>16.89</v>
-      </c>
-      <c r="G4" t="s">
-        <v>91</v>
-      </c>
-      <c r="H4">
-        <v>1.46</v>
-      </c>
-      <c r="I4" s="1">
-        <v>24.66</v>
-      </c>
-      <c r="J4">
-        <v>1.5</v>
-      </c>
-      <c r="K4" s="1">
-        <v>25.34</v>
-      </c>
-      <c r="L4" t="s">
-        <v>95</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E5" t="s">
-        <v>87</v>
-      </c>
-      <c r="F5">
-        <v>45.46</v>
-      </c>
-      <c r="G5" t="s">
-        <v>91</v>
-      </c>
-      <c r="H5">
-        <v>1.48</v>
-      </c>
-      <c r="I5" s="1">
-        <v>67.28</v>
-      </c>
-      <c r="J5">
-        <v>1.52</v>
-      </c>
-      <c r="K5" s="1">
-        <v>69.09999999999999</v>
-      </c>
-      <c r="L5" t="s">
-        <v>96</v>
-      </c>
-      <c r="M5">
+      <c r="L5" s="1">
+        <v>69.10072</v>
+      </c>
+      <c r="M5" t="s">
+        <v>97</v>
+      </c>
+      <c r="N5">
         <v>41143</v>
       </c>
-      <c r="N5" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="O5" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F6">
         <v>41</v>
       </c>
       <c r="G6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H6">
+        <v>1.406</v>
+      </c>
+      <c r="I6" s="1">
         <v>1.48</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>60.68</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>1.52</v>
       </c>
-      <c r="K6" s="1">
+      <c r="L6" s="1">
         <v>62.32</v>
       </c>
-      <c r="L6" t="s">
-        <v>97</v>
-      </c>
-      <c r="M6">
+      <c r="M6" t="s">
+        <v>98</v>
+      </c>
+      <c r="N6">
         <v>285990</v>
       </c>
-      <c r="N6" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="O6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E7" t="s">
+        <v>88</v>
+      </c>
+      <c r="F7">
+        <v>23.849</v>
+      </c>
+      <c r="G7" t="s">
+        <v>92</v>
+      </c>
+      <c r="H7">
+        <v>1.406</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1.48</v>
+      </c>
+      <c r="J7">
+        <v>35.29652</v>
+      </c>
+      <c r="K7" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="L7" s="1">
+        <v>36.25048</v>
+      </c>
+      <c r="M7" t="s">
+        <v>99</v>
+      </c>
+      <c r="N7">
+        <v>242359</v>
+      </c>
+      <c r="O7" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E8" t="s">
         <v>87</v>
-      </c>
-      <c r="F7">
-        <v>23.85</v>
-      </c>
-      <c r="G7" t="s">
-        <v>91</v>
-      </c>
-      <c r="H7">
-        <v>1.48</v>
-      </c>
-      <c r="I7" s="1">
-        <v>35.3</v>
-      </c>
-      <c r="J7">
-        <v>1.52</v>
-      </c>
-      <c r="K7" s="1">
-        <v>36.25</v>
-      </c>
-      <c r="L7" t="s">
-        <v>98</v>
-      </c>
-      <c r="M7">
-        <v>242359</v>
-      </c>
-      <c r="N7" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" t="s">
-        <v>67</v>
-      </c>
-      <c r="E8" t="s">
-        <v>86</v>
       </c>
       <c r="F8">
         <v>22</v>
       </c>
       <c r="G8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H8">
+        <v>1.359</v>
+      </c>
+      <c r="I8" s="1">
         <v>1.45</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>31.9</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>1.49</v>
       </c>
-      <c r="K8" s="1">
+      <c r="L8" s="1">
         <v>32.78</v>
       </c>
-      <c r="L8" t="s">
-        <v>99</v>
-      </c>
-      <c r="M8">
+      <c r="M8" t="s">
+        <v>100</v>
+      </c>
+      <c r="N8">
         <v>20945</v>
       </c>
-      <c r="N8" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="O8" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F9">
         <v>26</v>
       </c>
       <c r="G9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H9">
+        <v>1.359</v>
+      </c>
+      <c r="I9" s="1">
         <v>1.45</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9">
         <v>37.7</v>
       </c>
-      <c r="J9">
+      <c r="K9" s="1">
         <v>1.49</v>
       </c>
-      <c r="K9" s="1">
+      <c r="L9" s="1">
         <v>38.74</v>
       </c>
-      <c r="L9" t="s">
-        <v>100</v>
-      </c>
-      <c r="M9">
+      <c r="M9" t="s">
+        <v>101</v>
+      </c>
+      <c r="N9">
         <v>7020</v>
       </c>
-      <c r="N9" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="O9" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F10">
-        <v>53.11</v>
+        <v>53.112</v>
       </c>
       <c r="G10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H10">
+        <v>1.412</v>
+      </c>
+      <c r="I10" s="1">
         <v>1.48</v>
       </c>
-      <c r="I10" s="1">
-        <v>78.59999999999999</v>
-      </c>
       <c r="J10">
+        <v>78.60576</v>
+      </c>
+      <c r="K10" s="1">
         <v>1.52</v>
       </c>
-      <c r="K10" s="1">
-        <v>80.73</v>
-      </c>
-      <c r="L10" t="s">
-        <v>101</v>
-      </c>
-      <c r="M10">
+      <c r="L10" s="1">
+        <v>80.73023999999999</v>
+      </c>
+      <c r="M10" t="s">
+        <v>102</v>
+      </c>
+      <c r="N10">
         <v>284567</v>
       </c>
-      <c r="N10" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="O10" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F11">
         <v>44</v>
       </c>
       <c r="G11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H11">
+        <v>1.629</v>
+      </c>
+      <c r="I11" s="1">
         <v>1.7</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11">
         <v>74.8</v>
       </c>
-      <c r="J11">
+      <c r="K11" s="1">
         <v>1.75</v>
       </c>
-      <c r="K11" s="1">
+      <c r="L11" s="1">
         <v>77</v>
       </c>
-      <c r="L11" t="s">
-        <v>102</v>
-      </c>
-      <c r="M11">
+      <c r="M11" t="s">
+        <v>103</v>
+      </c>
+      <c r="N11">
         <v>182486</v>
       </c>
-      <c r="N11" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="O11" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F12">
-        <v>37.62</v>
+        <v>37.623</v>
       </c>
       <c r="G12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H12">
+        <v>1.437</v>
+      </c>
+      <c r="I12" s="1">
         <v>1.5</v>
       </c>
-      <c r="I12" s="1">
-        <v>56.43</v>
-      </c>
       <c r="J12">
+        <v>56.4345</v>
+      </c>
+      <c r="K12" s="1">
         <v>1.54</v>
       </c>
-      <c r="K12" s="1">
-        <v>57.93</v>
-      </c>
-      <c r="L12" t="s">
-        <v>103</v>
-      </c>
-      <c r="M12">
+      <c r="L12" s="1">
+        <v>57.93942</v>
+      </c>
+      <c r="M12" t="s">
+        <v>104</v>
+      </c>
+      <c r="N12">
         <v>255470</v>
       </c>
-      <c r="N12" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="O12" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F13">
-        <v>35.07</v>
+        <v>35.071</v>
       </c>
       <c r="G13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H13">
+        <v>1.437</v>
+      </c>
+      <c r="I13" s="1">
         <v>1.5</v>
       </c>
-      <c r="I13" s="1">
-        <v>52.6</v>
-      </c>
       <c r="J13">
+        <v>52.6065</v>
+      </c>
+      <c r="K13" s="1">
         <v>1.54</v>
       </c>
-      <c r="K13" s="1">
-        <v>54.01</v>
-      </c>
-      <c r="L13" t="s">
-        <v>104</v>
-      </c>
-      <c r="M13">
+      <c r="L13" s="1">
+        <v>54.00934</v>
+      </c>
+      <c r="M13" t="s">
+        <v>105</v>
+      </c>
+      <c r="N13">
         <v>0</v>
       </c>
-      <c r="N13" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="O13" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F14">
         <v>53</v>
       </c>
       <c r="G14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H14">
+        <v>1.437</v>
+      </c>
+      <c r="I14" s="1">
         <v>1.5</v>
       </c>
-      <c r="I14" s="1">
+      <c r="J14">
         <v>79.5</v>
       </c>
-      <c r="J14">
+      <c r="K14" s="1">
         <v>1.54</v>
       </c>
-      <c r="K14" s="1">
+      <c r="L14" s="1">
         <v>81.62</v>
       </c>
-      <c r="L14" t="s">
-        <v>105</v>
-      </c>
-      <c r="M14">
+      <c r="M14" t="s">
+        <v>106</v>
+      </c>
+      <c r="N14">
         <v>0</v>
       </c>
-      <c r="N14" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="O14" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F15">
         <v>22</v>
       </c>
       <c r="G15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H15">
+        <v>1.451</v>
+      </c>
+      <c r="I15" s="1">
         <v>1.52</v>
       </c>
-      <c r="I15" s="1">
+      <c r="J15">
         <v>33.44</v>
       </c>
-      <c r="J15">
+      <c r="K15" s="1">
         <v>1.56</v>
       </c>
-      <c r="K15" s="1">
+      <c r="L15" s="1">
         <v>34.32</v>
       </c>
-      <c r="L15" t="s">
-        <v>106</v>
-      </c>
-      <c r="M15">
+      <c r="M15" t="s">
+        <v>107</v>
+      </c>
+      <c r="N15">
         <v>0</v>
       </c>
-      <c r="N15" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="O15" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" t="s">
+        <v>75</v>
+      </c>
+      <c r="E16" t="s">
+        <v>87</v>
+      </c>
+      <c r="F16">
+        <v>51.007</v>
+      </c>
+      <c r="G16" t="s">
+        <v>92</v>
+      </c>
+      <c r="H16">
+        <v>1.359</v>
+      </c>
+      <c r="I16" s="1">
+        <v>1.45</v>
+      </c>
+      <c r="J16">
+        <v>73.96015</v>
+      </c>
+      <c r="K16" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="L16" s="1">
+        <v>76.00042999999999</v>
+      </c>
+      <c r="M16" t="s">
+        <v>108</v>
+      </c>
+      <c r="N16">
+        <v>300520</v>
+      </c>
+      <c r="O16" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" t="s">
         <v>49</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D17" t="s">
         <v>74</v>
       </c>
-      <c r="E16" t="s">
-        <v>86</v>
-      </c>
-      <c r="F16">
-        <v>51.01</v>
-      </c>
-      <c r="G16" t="s">
-        <v>91</v>
-      </c>
-      <c r="H16">
-        <v>1.45</v>
-      </c>
-      <c r="I16" s="1">
-        <v>73.95999999999999</v>
-      </c>
-      <c r="J16">
-        <v>1.49</v>
-      </c>
-      <c r="K16" s="1">
+      <c r="E17" t="s">
+        <v>88</v>
+      </c>
+      <c r="F17">
+        <v>45.871</v>
+      </c>
+      <c r="G17" t="s">
+        <v>92</v>
+      </c>
+      <c r="H17">
+        <v>1.469</v>
+      </c>
+      <c r="I17" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="J17">
+        <v>69.26521</v>
+      </c>
+      <c r="K17" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="L17" s="1">
+        <v>71.10005</v>
+      </c>
+      <c r="M17" t="s">
+        <v>109</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" t="s">
         <v>76</v>
       </c>
-      <c r="L16" t="s">
-        <v>107</v>
-      </c>
-      <c r="M16">
-        <v>300520</v>
-      </c>
-      <c r="N16" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
-      <c r="A17" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" t="s">
-        <v>48</v>
-      </c>
-      <c r="D17" t="s">
-        <v>73</v>
-      </c>
-      <c r="E17" t="s">
-        <v>87</v>
-      </c>
-      <c r="F17">
-        <v>45.87</v>
-      </c>
-      <c r="G17" t="s">
-        <v>91</v>
-      </c>
-      <c r="H17">
-        <v>1.51</v>
-      </c>
-      <c r="I17" s="1">
-        <v>69.26000000000001</v>
-      </c>
-      <c r="J17">
-        <v>1.55</v>
-      </c>
-      <c r="K17" s="1">
-        <v>71.09999999999999</v>
-      </c>
-      <c r="L17" t="s">
-        <v>108</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-      <c r="N17" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
-      <c r="A18" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" t="s">
-        <v>34</v>
-      </c>
-      <c r="C18" t="s">
-        <v>50</v>
-      </c>
-      <c r="D18" t="s">
-        <v>75</v>
-      </c>
       <c r="E18" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F18">
-        <v>46.8</v>
+        <v>46.795</v>
       </c>
       <c r="G18" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H18">
+        <v>1.469</v>
+      </c>
+      <c r="I18" s="1">
         <v>1.52</v>
       </c>
-      <c r="I18" s="1">
-        <v>71.14</v>
-      </c>
       <c r="J18">
+        <v>71.1284</v>
+      </c>
+      <c r="K18" s="1">
         <v>1.56</v>
       </c>
-      <c r="K18" s="1">
-        <v>73.01000000000001</v>
-      </c>
-      <c r="L18" t="s">
-        <v>109</v>
-      </c>
-      <c r="M18">
+      <c r="L18" s="1">
+        <v>73.00020000000001</v>
+      </c>
+      <c r="M18" t="s">
+        <v>110</v>
+      </c>
+      <c r="N18">
         <v>290630</v>
       </c>
-      <c r="N18" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
+      <c r="O18" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D19" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E19" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F19">
-        <v>46.61</v>
+        <v>46.608</v>
       </c>
       <c r="G19" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H19">
+        <v>1.489</v>
+      </c>
+      <c r="I19" s="1">
         <v>1.54</v>
       </c>
-      <c r="I19" s="1">
-        <v>71.78</v>
-      </c>
       <c r="J19">
+        <v>71.77632</v>
+      </c>
+      <c r="K19" s="1">
         <v>1.58</v>
       </c>
-      <c r="K19" s="1">
-        <v>73.64</v>
-      </c>
-      <c r="L19" t="s">
-        <v>110</v>
-      </c>
-      <c r="M19">
+      <c r="L19" s="1">
+        <v>73.64064</v>
+      </c>
+      <c r="M19" t="s">
+        <v>111</v>
+      </c>
+      <c r="N19">
         <v>264545</v>
       </c>
-      <c r="N19" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
+      <c r="O19" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D20" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F20">
-        <v>51.94</v>
+        <v>51.943</v>
       </c>
       <c r="G20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H20">
+        <v>1.489</v>
+      </c>
+      <c r="I20" s="1">
         <v>1.54</v>
       </c>
-      <c r="I20" s="1">
-        <v>79.98999999999999</v>
-      </c>
       <c r="J20">
+        <v>79.99222</v>
+      </c>
+      <c r="K20" s="1">
         <v>1.58</v>
       </c>
-      <c r="K20" s="1">
-        <v>82.06999999999999</v>
-      </c>
-      <c r="L20" t="s">
-        <v>111</v>
-      </c>
-      <c r="M20">
+      <c r="L20" s="1">
+        <v>82.06994</v>
+      </c>
+      <c r="M20" t="s">
+        <v>112</v>
+      </c>
+      <c r="N20">
         <v>41492</v>
       </c>
-      <c r="N20" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="O20" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F21">
         <v>46</v>
       </c>
       <c r="G21" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H21">
+        <v>1.499</v>
+      </c>
+      <c r="I21" s="1">
         <v>1.57</v>
       </c>
-      <c r="I21" s="1">
+      <c r="J21">
         <v>72.22</v>
       </c>
-      <c r="J21">
+      <c r="K21" s="1">
         <v>1.61</v>
       </c>
-      <c r="K21" s="1">
+      <c r="L21" s="1">
         <v>74.06</v>
       </c>
-      <c r="L21" t="s">
-        <v>112</v>
-      </c>
-      <c r="M21">
+      <c r="M21" t="s">
+        <v>113</v>
+      </c>
+      <c r="N21">
         <v>259652</v>
       </c>
-      <c r="N21" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
+      <c r="O21" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B22" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F22">
-        <v>43.31</v>
+        <v>43.307</v>
       </c>
       <c r="G22" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H22">
+        <v>1.369</v>
+      </c>
+      <c r="I22" s="1">
         <v>1.46</v>
       </c>
-      <c r="I22" s="1">
-        <v>63.23</v>
-      </c>
       <c r="J22">
+        <v>63.22822</v>
+      </c>
+      <c r="K22" s="1">
         <v>1.5</v>
       </c>
-      <c r="K22" s="1">
-        <v>64.95999999999999</v>
-      </c>
-      <c r="L22" t="s">
-        <v>113</v>
-      </c>
-      <c r="M22">
+      <c r="L22" s="1">
+        <v>64.9605</v>
+      </c>
+      <c r="M22" t="s">
+        <v>114</v>
+      </c>
+      <c r="N22">
         <v>235382</v>
       </c>
-      <c r="N22" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
+      <c r="O22" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D23" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F23">
         <v>32</v>
       </c>
       <c r="G23" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H23">
+        <v>1.499</v>
+      </c>
+      <c r="I23" s="1">
         <v>1.57</v>
       </c>
-      <c r="I23" s="1">
+      <c r="J23">
         <v>50.24</v>
       </c>
-      <c r="J23">
+      <c r="K23" s="1">
         <v>1.61</v>
       </c>
-      <c r="K23" s="1">
+      <c r="L23" s="1">
         <v>51.52</v>
       </c>
-      <c r="L23" t="s">
-        <v>98</v>
-      </c>
-      <c r="M23">
+      <c r="M23" t="s">
+        <v>99</v>
+      </c>
+      <c r="N23">
         <v>235791</v>
       </c>
-      <c r="N23" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
+      <c r="O23" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
       <c r="A24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D24" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E24" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F24">
-        <v>54.59</v>
+        <v>54.589</v>
       </c>
       <c r="G24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H24">
+        <v>1.499</v>
+      </c>
+      <c r="I24" s="1">
         <v>1.59</v>
       </c>
-      <c r="I24" s="1">
-        <v>86.8</v>
-      </c>
       <c r="J24">
+        <v>86.79651</v>
+      </c>
+      <c r="K24" s="1">
         <v>1.63</v>
       </c>
-      <c r="K24" s="1">
-        <v>88.98</v>
-      </c>
-      <c r="L24" t="s">
-        <v>114</v>
-      </c>
-      <c r="M24">
+      <c r="L24" s="1">
+        <v>88.98007</v>
+      </c>
+      <c r="M24" t="s">
+        <v>115</v>
+      </c>
+      <c r="N24">
         <v>0</v>
       </c>
-      <c r="N24" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
+      <c r="O24" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C25" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D25" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F25">
-        <v>39.39</v>
+        <v>39.393</v>
       </c>
       <c r="G25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H25">
+        <v>1.546</v>
+      </c>
+      <c r="I25" s="1">
         <v>1.64</v>
       </c>
-      <c r="I25" s="1">
-        <v>64.59999999999999</v>
-      </c>
       <c r="J25">
+        <v>64.60451999999999</v>
+      </c>
+      <c r="K25" s="1">
         <v>1.68</v>
       </c>
-      <c r="K25" s="1">
-        <v>66.18000000000001</v>
-      </c>
-      <c r="L25" t="s">
-        <v>115</v>
-      </c>
-      <c r="M25">
+      <c r="L25" s="1">
+        <v>66.18024</v>
+      </c>
+      <c r="M25" t="s">
+        <v>116</v>
+      </c>
+      <c r="N25">
         <v>0</v>
       </c>
-      <c r="N25" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
+      <c r="O25" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D26" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E26" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F26">
         <v>54.94</v>
       </c>
       <c r="G26" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H26">
+        <v>1.546</v>
+      </c>
+      <c r="I26" s="1">
         <v>1.64</v>
       </c>
-      <c r="I26" s="1">
-        <v>90.09999999999999</v>
-      </c>
       <c r="J26">
+        <v>90.1016</v>
+      </c>
+      <c r="K26" s="1">
         <v>1.68</v>
       </c>
-      <c r="K26" s="1">
-        <v>92.3</v>
-      </c>
-      <c r="L26" t="s">
-        <v>116</v>
-      </c>
-      <c r="M26">
+      <c r="L26" s="1">
+        <v>92.2992</v>
+      </c>
+      <c r="M26" t="s">
+        <v>117</v>
+      </c>
+      <c r="N26">
         <v>285274</v>
       </c>
-      <c r="N26" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14">
+      <c r="O26" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15">
       <c r="A27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C27" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E27" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F27">
         <v>19</v>
       </c>
       <c r="G27" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H27">
+        <v>1.389</v>
+      </c>
+      <c r="I27" s="1">
         <v>1.49</v>
       </c>
-      <c r="I27" s="1">
+      <c r="J27">
         <v>28.31</v>
       </c>
-      <c r="J27">
+      <c r="K27" s="1">
         <v>1.53</v>
       </c>
-      <c r="K27" s="1">
+      <c r="L27" s="1">
         <v>29.07</v>
       </c>
-      <c r="L27" t="s">
-        <v>117</v>
-      </c>
-      <c r="M27">
+      <c r="M27" t="s">
+        <v>118</v>
+      </c>
+      <c r="N27">
         <v>0</v>
       </c>
-      <c r="N27" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14">
+      <c r="O27" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15">
       <c r="A28" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C28" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D28" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E28" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F28">
         <v>12</v>
       </c>
       <c r="G28" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H28">
+        <v>1.389</v>
+      </c>
+      <c r="I28" s="1">
         <v>1.49</v>
       </c>
-      <c r="I28" s="1">
+      <c r="J28">
         <v>17.88</v>
       </c>
-      <c r="J28">
+      <c r="K28" s="1">
         <v>1.53</v>
       </c>
-      <c r="K28" s="1">
+      <c r="L28" s="1">
         <v>18.36</v>
       </c>
-      <c r="L28" t="s">
-        <v>118</v>
-      </c>
-      <c r="M28">
+      <c r="M28" t="s">
+        <v>119</v>
+      </c>
+      <c r="N28">
         <v>10270</v>
       </c>
-      <c r="N28" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14">
+      <c r="O28" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15">
       <c r="A29" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C29" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D29" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E29" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F29">
-        <v>21.01</v>
+        <v>21.013</v>
       </c>
       <c r="G29" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H29">
+        <v>1.389</v>
+      </c>
+      <c r="I29" s="1">
         <v>1.49</v>
       </c>
-      <c r="I29" s="1">
-        <v>31.3</v>
-      </c>
       <c r="J29">
+        <v>31.30937</v>
+      </c>
+      <c r="K29" s="1">
         <v>1.53</v>
       </c>
-      <c r="K29" s="1">
-        <v>32.15</v>
-      </c>
-      <c r="L29" t="s">
-        <v>119</v>
-      </c>
-      <c r="M29">
+      <c r="L29" s="1">
+        <v>32.14989</v>
+      </c>
+      <c r="M29" t="s">
+        <v>120</v>
+      </c>
+      <c r="N29">
         <v>0</v>
       </c>
-      <c r="N29" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14">
+      <c r="O29" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15">
       <c r="A30" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B30" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C30" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D30" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E30" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F30">
         <v>37</v>
       </c>
       <c r="G30" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H30">
+        <v>1.546</v>
+      </c>
+      <c r="I30" s="1">
         <v>1.64</v>
       </c>
-      <c r="I30" s="1">
+      <c r="J30">
         <v>60.68</v>
       </c>
-      <c r="J30">
+      <c r="K30" s="1">
         <v>1.68</v>
       </c>
-      <c r="K30" s="1">
+      <c r="L30" s="1">
         <v>62.16</v>
       </c>
-      <c r="L30" t="s">
-        <v>120</v>
-      </c>
-      <c r="M30">
+      <c r="M30" t="s">
+        <v>121</v>
+      </c>
+      <c r="N30">
         <v>0</v>
       </c>
-      <c r="N30" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14">
+      <c r="O30" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15">
       <c r="A31" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C31" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D31" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E31" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F31">
         <v>34</v>
       </c>
       <c r="G31" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H31">
+        <v>1.546</v>
+      </c>
+      <c r="I31" s="1">
         <v>1.64</v>
       </c>
-      <c r="I31" s="1">
+      <c r="J31">
         <v>55.76</v>
       </c>
-      <c r="J31">
+      <c r="K31" s="1">
         <v>1.68</v>
       </c>
-      <c r="K31" s="1">
+      <c r="L31" s="1">
         <v>57.12</v>
       </c>
-      <c r="L31" t="s">
-        <v>121</v>
-      </c>
-      <c r="M31">
+      <c r="M31" t="s">
+        <v>122</v>
+      </c>
+      <c r="N31">
         <v>255860</v>
       </c>
-      <c r="N31" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14">
+      <c r="O31" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15">
       <c r="A32" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B32" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D32" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E32" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F32">
         <v>48</v>
       </c>
       <c r="G32" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H32">
+        <v>1.546</v>
+      </c>
+      <c r="I32" s="1">
         <v>1.64</v>
       </c>
-      <c r="I32" s="1">
+      <c r="J32">
         <v>78.72</v>
       </c>
-      <c r="J32">
+      <c r="K32" s="1">
         <v>1.68</v>
       </c>
-      <c r="K32" s="1">
+      <c r="L32" s="1">
         <v>80.64</v>
       </c>
-      <c r="L32" t="s">
-        <v>122</v>
-      </c>
-      <c r="M32">
+      <c r="M32" t="s">
+        <v>123</v>
+      </c>
+      <c r="N32">
         <v>27032</v>
       </c>
-      <c r="N32" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14">
+      <c r="O32" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15">
       <c r="A33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B33" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C33" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D33" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E33" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F33">
         <v>69</v>
       </c>
       <c r="G33" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H33">
+        <v>1.564</v>
+      </c>
+      <c r="I33" s="1">
         <v>1.62</v>
       </c>
-      <c r="I33" s="1">
+      <c r="J33">
         <v>111.78</v>
       </c>
-      <c r="J33">
+      <c r="K33" s="1">
         <v>1.66</v>
       </c>
-      <c r="K33" s="1">
+      <c r="L33" s="1">
         <v>114.54</v>
       </c>
-      <c r="L33" t="s">
-        <v>99</v>
-      </c>
-      <c r="M33">
+      <c r="M33" t="s">
+        <v>100</v>
+      </c>
+      <c r="N33">
         <v>111100</v>
       </c>
-      <c r="N33" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14">
+      <c r="O33" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15">
       <c r="A34" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C34" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D34" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E34" t="s">
+        <v>88</v>
+      </c>
+      <c r="F34">
+        <v>48.452</v>
+      </c>
+      <c r="G34" t="s">
+        <v>92</v>
+      </c>
+      <c r="H34">
+        <v>1.588</v>
+      </c>
+      <c r="I34" s="1">
+        <v>1.64</v>
+      </c>
+      <c r="J34">
+        <v>79.46128</v>
+      </c>
+      <c r="K34" s="1">
+        <v>1.68</v>
+      </c>
+      <c r="L34" s="1">
+        <v>81.39936</v>
+      </c>
+      <c r="M34" t="s">
+        <v>124</v>
+      </c>
+      <c r="N34">
+        <v>41867</v>
+      </c>
+      <c r="O34" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15">
+      <c r="A35" t="s">
+        <v>28</v>
+      </c>
+      <c r="B35" t="s">
+        <v>35</v>
+      </c>
+      <c r="C35" t="s">
+        <v>59</v>
+      </c>
+      <c r="D35" t="s">
+        <v>84</v>
+      </c>
+      <c r="E35" t="s">
         <v>87</v>
-      </c>
-      <c r="F34">
-        <v>48.45</v>
-      </c>
-      <c r="G34" t="s">
-        <v>91</v>
-      </c>
-      <c r="H34">
-        <v>1.64</v>
-      </c>
-      <c r="I34" s="1">
-        <v>79.45999999999999</v>
-      </c>
-      <c r="J34">
-        <v>1.68</v>
-      </c>
-      <c r="K34" s="1">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="L34" t="s">
-        <v>123</v>
-      </c>
-      <c r="M34">
-        <v>41867</v>
-      </c>
-      <c r="N34" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14">
-      <c r="A35" t="s">
-        <v>27</v>
-      </c>
-      <c r="B35" t="s">
-        <v>34</v>
-      </c>
-      <c r="C35" t="s">
-        <v>58</v>
-      </c>
-      <c r="D35" t="s">
-        <v>83</v>
-      </c>
-      <c r="E35" t="s">
-        <v>86</v>
       </c>
       <c r="F35">
         <v>17</v>
       </c>
       <c r="G35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H35">
+        <v>1.401</v>
+      </c>
+      <c r="I35" s="1">
         <v>1.48</v>
       </c>
-      <c r="I35" s="1">
+      <c r="J35">
         <v>25.16</v>
       </c>
-      <c r="J35">
+      <c r="K35" s="1">
         <v>1.52</v>
       </c>
-      <c r="K35" s="1">
+      <c r="L35" s="1">
         <v>25.84</v>
       </c>
-      <c r="L35" t="s">
-        <v>124</v>
-      </c>
-      <c r="M35">
+      <c r="M35" t="s">
+        <v>125</v>
+      </c>
+      <c r="N35">
         <v>75620</v>
       </c>
-      <c r="N35" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14">
+      <c r="O35" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15">
       <c r="A36" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B36" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C36" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D36" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E36" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F36">
         <v>25</v>
       </c>
       <c r="G36" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H36">
+        <v>1.401</v>
+      </c>
+      <c r="I36" s="1">
         <v>1.48</v>
       </c>
-      <c r="I36" s="1">
+      <c r="J36">
         <v>37</v>
       </c>
-      <c r="J36">
+      <c r="K36" s="1">
         <v>1.52</v>
       </c>
-      <c r="K36" s="1">
+      <c r="L36" s="1">
         <v>38</v>
       </c>
-      <c r="L36" t="s">
-        <v>125</v>
-      </c>
-      <c r="M36">
+      <c r="M36" t="s">
+        <v>126</v>
+      </c>
+      <c r="N36">
         <v>10450</v>
       </c>
-      <c r="N36" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14">
+      <c r="O36" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15">
       <c r="A37" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B37" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C37" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D37" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E37" t="s">
+        <v>88</v>
+      </c>
+      <c r="F37">
+        <v>49.601</v>
+      </c>
+      <c r="G37" t="s">
+        <v>92</v>
+      </c>
+      <c r="H37">
+        <v>1.588</v>
+      </c>
+      <c r="I37" s="1">
+        <v>1.64</v>
+      </c>
+      <c r="J37">
+        <v>81.34564</v>
+      </c>
+      <c r="K37" s="1">
+        <v>1.68</v>
+      </c>
+      <c r="L37" s="1">
+        <v>83.32968</v>
+      </c>
+      <c r="M37" t="s">
+        <v>127</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15">
+      <c r="A38" t="s">
+        <v>29</v>
+      </c>
+      <c r="B38" t="s">
+        <v>35</v>
+      </c>
+      <c r="C38" t="s">
+        <v>60</v>
+      </c>
+      <c r="D38" t="s">
+        <v>85</v>
+      </c>
+      <c r="E38" t="s">
         <v>87</v>
       </c>
-      <c r="F37">
-        <v>49.6</v>
-      </c>
-      <c r="G37" t="s">
-        <v>91</v>
-      </c>
-      <c r="H37">
-        <v>1.64</v>
-      </c>
-      <c r="I37" s="1">
-        <v>81.34</v>
-      </c>
-      <c r="J37">
-        <v>1.68</v>
-      </c>
-      <c r="K37" s="1">
-        <v>83.33</v>
-      </c>
-      <c r="L37" t="s">
-        <v>126</v>
-      </c>
-      <c r="M37">
-        <v>0</v>
-      </c>
-      <c r="N37" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14">
-      <c r="A38" t="s">
-        <v>28</v>
-      </c>
-      <c r="B38" t="s">
-        <v>34</v>
-      </c>
-      <c r="C38" t="s">
-        <v>59</v>
-      </c>
-      <c r="D38" t="s">
-        <v>84</v>
-      </c>
-      <c r="E38" t="s">
+      <c r="F38">
+        <v>16.013</v>
+      </c>
+      <c r="G38" t="s">
+        <v>92</v>
+      </c>
+      <c r="H38">
+        <v>1.401</v>
+      </c>
+      <c r="I38" s="1">
+        <v>1.48</v>
+      </c>
+      <c r="J38">
+        <v>23.69924</v>
+      </c>
+      <c r="K38" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="L38" s="1">
+        <v>24.33976</v>
+      </c>
+      <c r="M38" t="s">
+        <v>128</v>
+      </c>
+      <c r="N38">
+        <v>133320</v>
+      </c>
+      <c r="O38" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15">
+      <c r="A39" t="s">
+        <v>29</v>
+      </c>
+      <c r="B39" t="s">
+        <v>35</v>
+      </c>
+      <c r="C39" t="s">
+        <v>61</v>
+      </c>
+      <c r="D39" t="s">
         <v>86</v>
       </c>
-      <c r="F38">
-        <v>16.01</v>
-      </c>
-      <c r="G38" t="s">
-        <v>91</v>
-      </c>
-      <c r="H38">
-        <v>1.48</v>
-      </c>
-      <c r="I38" s="1">
-        <v>23.69</v>
-      </c>
-      <c r="J38">
-        <v>1.52</v>
-      </c>
-      <c r="K38" s="1">
-        <v>24.34</v>
-      </c>
-      <c r="L38" t="s">
-        <v>127</v>
-      </c>
-      <c r="M38">
-        <v>133320</v>
-      </c>
-      <c r="N38" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14">
-      <c r="A39" t="s">
-        <v>28</v>
-      </c>
-      <c r="B39" t="s">
-        <v>34</v>
-      </c>
-      <c r="C39" t="s">
-        <v>60</v>
-      </c>
-      <c r="D39" t="s">
-        <v>85</v>
-      </c>
       <c r="E39" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F39">
         <v>49</v>
       </c>
       <c r="G39" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H39">
+        <v>1.588</v>
+      </c>
+      <c r="I39" s="1">
         <v>1.64</v>
       </c>
-      <c r="I39" s="1">
+      <c r="J39">
         <v>80.36</v>
       </c>
-      <c r="J39">
+      <c r="K39" s="1">
         <v>1.68</v>
       </c>
-      <c r="K39" s="1">
+      <c r="L39" s="1">
         <v>82.31999999999999</v>
       </c>
-      <c r="L39" t="s">
-        <v>128</v>
-      </c>
-      <c r="M39">
+      <c r="M39" t="s">
+        <v>129</v>
+      </c>
+      <c r="N39">
         <v>0</v>
       </c>
-      <c r="N39" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14">
+      <c r="O39" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15">
       <c r="A40" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B40" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C40" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D40" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E40" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F40">
         <v>31</v>
       </c>
       <c r="G40" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H40">
+        <v>1.401</v>
+      </c>
+      <c r="I40" s="1">
         <v>1.49</v>
       </c>
-      <c r="I40" s="1">
+      <c r="J40">
         <v>46.19</v>
       </c>
-      <c r="J40">
+      <c r="K40" s="1">
         <v>1.53</v>
       </c>
-      <c r="K40" s="1">
+      <c r="L40" s="1">
         <v>47.43</v>
       </c>
-      <c r="L40" t="s">
-        <v>129</v>
-      </c>
-      <c r="M40">
+      <c r="M40" t="s">
+        <v>130</v>
+      </c>
+      <c r="N40">
         <v>7535</v>
       </c>
-      <c r="N40" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14">
+      <c r="O40" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15">
       <c r="A41" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B41" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C41" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D41" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E41" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F41">
         <v>43</v>
       </c>
       <c r="G41" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H41">
+        <v>1.649</v>
+      </c>
+      <c r="I41" s="1">
         <v>1.74</v>
       </c>
-      <c r="I41" s="1">
+      <c r="J41">
         <v>74.81999999999999</v>
       </c>
-      <c r="J41">
+      <c r="K41" s="1">
         <v>1.79</v>
       </c>
-      <c r="K41" s="1">
+      <c r="L41" s="1">
         <v>76.97</v>
       </c>
-      <c r="L41" t="s">
-        <v>130</v>
-      </c>
-      <c r="M41">
+      <c r="M41" t="s">
+        <v>131</v>
+      </c>
+      <c r="N41">
         <v>182918</v>
       </c>
-      <c r="N41" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14">
+      <c r="O41" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15">
       <c r="A42" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B42" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C42" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D42" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E42" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F42">
         <v>65</v>
       </c>
       <c r="G42" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H42">
+        <v>1.619</v>
+      </c>
+      <c r="I42" s="1">
         <v>1.66</v>
       </c>
-      <c r="I42" s="1">
+      <c r="J42">
         <v>107.9</v>
       </c>
-      <c r="J42">
+      <c r="K42" s="1">
         <v>1.7</v>
       </c>
-      <c r="K42" s="1">
+      <c r="L42" s="1">
         <v>110.5</v>
       </c>
-      <c r="L42" t="s">
-        <v>107</v>
-      </c>
-      <c r="M42">
+      <c r="M42" t="s">
+        <v>108</v>
+      </c>
+      <c r="N42">
         <v>286990</v>
       </c>
-      <c r="N42" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14">
+      <c r="O42" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15">
       <c r="A43" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B43" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C43" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D43" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E43" t="s">
+        <v>88</v>
+      </c>
+      <c r="F43">
+        <v>29.069</v>
+      </c>
+      <c r="G43" t="s">
+        <v>92</v>
+      </c>
+      <c r="H43">
+        <v>1.619</v>
+      </c>
+      <c r="I43" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="J43">
+        <v>49.4173</v>
+      </c>
+      <c r="K43" s="1">
+        <v>1.74</v>
+      </c>
+      <c r="L43" s="1">
+        <v>50.58006</v>
+      </c>
+      <c r="M43" t="s">
+        <v>132</v>
+      </c>
+      <c r="N43">
+        <v>256160</v>
+      </c>
+      <c r="O43" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15">
+      <c r="A44" t="s">
+        <v>31</v>
+      </c>
+      <c r="B44" t="s">
+        <v>35</v>
+      </c>
+      <c r="C44" t="s">
+        <v>37</v>
+      </c>
+      <c r="D44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E44" t="s">
         <v>87</v>
-      </c>
-      <c r="F43">
-        <v>29.07</v>
-      </c>
-      <c r="G43" t="s">
-        <v>91</v>
-      </c>
-      <c r="H43">
-        <v>1.7</v>
-      </c>
-      <c r="I43" s="1">
-        <v>49.42</v>
-      </c>
-      <c r="J43">
-        <v>1.74</v>
-      </c>
-      <c r="K43" s="1">
-        <v>50.58</v>
-      </c>
-      <c r="L43" t="s">
-        <v>131</v>
-      </c>
-      <c r="M43">
-        <v>256160</v>
-      </c>
-      <c r="N43" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14">
-      <c r="A44" t="s">
-        <v>30</v>
-      </c>
-      <c r="B44" t="s">
-        <v>34</v>
-      </c>
-      <c r="C44" t="s">
-        <v>36</v>
-      </c>
-      <c r="D44" t="s">
-        <v>61</v>
-      </c>
-      <c r="E44" t="s">
-        <v>86</v>
       </c>
       <c r="F44">
         <v>31.51</v>
       </c>
       <c r="G44" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H44">
+        <v>1.401</v>
+      </c>
+      <c r="I44" s="1">
         <v>1.51</v>
       </c>
-      <c r="I44" s="1">
-        <v>47.58</v>
-      </c>
       <c r="J44">
+        <v>47.5801</v>
+      </c>
+      <c r="K44" s="1">
         <v>1.55</v>
       </c>
-      <c r="K44" s="1">
-        <v>48.84</v>
-      </c>
-      <c r="L44" t="s">
-        <v>132</v>
-      </c>
-      <c r="M44">
+      <c r="L44" s="1">
+        <v>48.8405</v>
+      </c>
+      <c r="M44" t="s">
+        <v>133</v>
+      </c>
+      <c r="N44">
         <v>235832</v>
       </c>
-      <c r="N44" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14">
+      <c r="O44" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15">
       <c r="A45" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B45" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C45" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D45" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E45" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F45">
         <v>40</v>
       </c>
       <c r="G45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H45">
+        <v>1.441</v>
+      </c>
+      <c r="I45" s="1">
         <v>1.51</v>
       </c>
-      <c r="I45" s="1">
+      <c r="J45">
         <v>60.4</v>
       </c>
-      <c r="J45">
+      <c r="K45" s="1">
         <v>1.55</v>
       </c>
-      <c r="K45" s="1">
+      <c r="L45" s="1">
         <v>62</v>
       </c>
-      <c r="L45" t="s">
-        <v>133</v>
-      </c>
-      <c r="M45">
+      <c r="M45" t="s">
+        <v>134</v>
+      </c>
+      <c r="N45">
         <v>300950</v>
       </c>
-      <c r="N45" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14">
+      <c r="O45" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15">
       <c r="A46" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B46" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C46" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D46" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E46" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F46">
-        <v>48.1</v>
+        <v>48.103</v>
       </c>
       <c r="G46" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H46">
+        <v>1.653</v>
+      </c>
+      <c r="I46" s="1">
         <v>1.7</v>
       </c>
-      <c r="I46" s="1">
-        <v>81.77</v>
-      </c>
       <c r="J46">
+        <v>81.77509999999999</v>
+      </c>
+      <c r="K46" s="1">
         <v>1.74</v>
       </c>
-      <c r="K46" s="1">
-        <v>83.69</v>
-      </c>
-      <c r="L46" t="s">
-        <v>134</v>
-      </c>
-      <c r="M46">
+      <c r="L46" s="1">
+        <v>83.69922</v>
+      </c>
+      <c r="M46" t="s">
+        <v>135</v>
+      </c>
+      <c r="N46">
         <v>285933</v>
       </c>
-      <c r="N46" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14">
+      <c r="O46" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15">
       <c r="A47" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B47" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C47" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D47" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E47" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F47">
         <v>55</v>
       </c>
       <c r="G47" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H47">
+        <v>1.653</v>
+      </c>
+      <c r="I47" s="1">
         <v>1.7</v>
       </c>
-      <c r="I47" s="1">
+      <c r="J47">
         <v>93.5</v>
       </c>
-      <c r="J47">
+      <c r="K47" s="1">
         <v>1.74</v>
       </c>
-      <c r="K47" s="1">
+      <c r="L47" s="1">
         <v>95.7</v>
       </c>
-      <c r="L47" t="s">
-        <v>135</v>
-      </c>
-      <c r="M47">
+      <c r="M47" t="s">
+        <v>136</v>
+      </c>
+      <c r="N47">
         <v>0</v>
       </c>
-      <c r="N47" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14">
+      <c r="O47" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15">
       <c r="A48" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B48" t="s">
+        <v>35</v>
+      </c>
+      <c r="C48" t="s">
+        <v>51</v>
+      </c>
+      <c r="D48" t="s">
+        <v>76</v>
+      </c>
+      <c r="E48" t="s">
+        <v>88</v>
+      </c>
+      <c r="F48">
+        <v>46.149</v>
+      </c>
+      <c r="G48" t="s">
+        <v>92</v>
+      </c>
+      <c r="H48">
+        <v>1.674</v>
+      </c>
+      <c r="I48" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="J48">
+        <v>78.4533</v>
+      </c>
+      <c r="K48" s="1">
+        <v>1.74</v>
+      </c>
+      <c r="L48" s="1">
+        <v>80.29926</v>
+      </c>
+      <c r="M48" t="s">
+        <v>137</v>
+      </c>
+      <c r="N48">
+        <v>291490</v>
+      </c>
+      <c r="O48" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15">
+      <c r="A49" t="s">
+        <v>33</v>
+      </c>
+      <c r="B49" t="s">
+        <v>35</v>
+      </c>
+      <c r="C49" t="s">
+        <v>55</v>
+      </c>
+      <c r="D49" t="s">
+        <v>80</v>
+      </c>
+      <c r="E49" t="s">
+        <v>87</v>
+      </c>
+      <c r="F49">
+        <v>25.013</v>
+      </c>
+      <c r="G49" t="s">
+        <v>92</v>
+      </c>
+      <c r="H49">
+        <v>1.449</v>
+      </c>
+      <c r="I49" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="J49">
+        <v>37.5195</v>
+      </c>
+      <c r="K49" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="L49" s="1">
+        <v>38.52002</v>
+      </c>
+      <c r="M49" t="s">
+        <v>138</v>
+      </c>
+      <c r="N49">
+        <v>327070</v>
+      </c>
+      <c r="O49" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15">
+      <c r="A50" t="s">
+        <v>33</v>
+      </c>
+      <c r="B50" t="s">
+        <v>35</v>
+      </c>
+      <c r="C50" t="s">
+        <v>40</v>
+      </c>
+      <c r="D50" t="s">
+        <v>65</v>
+      </c>
+      <c r="E50" t="s">
+        <v>88</v>
+      </c>
+      <c r="F50">
+        <v>51.851</v>
+      </c>
+      <c r="G50" t="s">
+        <v>92</v>
+      </c>
+      <c r="H50">
+        <v>1.674</v>
+      </c>
+      <c r="I50" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="J50">
+        <v>88.1467</v>
+      </c>
+      <c r="K50" s="1">
+        <v>1.74</v>
+      </c>
+      <c r="L50" s="1">
+        <v>90.22074000000001</v>
+      </c>
+      <c r="M50" t="s">
+        <v>139</v>
+      </c>
+      <c r="N50">
+        <v>42235</v>
+      </c>
+      <c r="O50" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15">
+      <c r="A51" t="s">
         <v>34</v>
       </c>
-      <c r="C48" t="s">
-        <v>50</v>
-      </c>
-      <c r="D48" t="s">
-        <v>75</v>
-      </c>
-      <c r="E48" t="s">
-        <v>87</v>
-      </c>
-      <c r="F48">
-        <v>46.15</v>
-      </c>
-      <c r="G48" t="s">
-        <v>91</v>
-      </c>
-      <c r="H48">
-        <v>1.7</v>
-      </c>
-      <c r="I48" s="1">
-        <v>78.45999999999999</v>
-      </c>
-      <c r="J48">
-        <v>1.74</v>
-      </c>
-      <c r="K48" s="1">
-        <v>80.3</v>
-      </c>
-      <c r="L48" t="s">
-        <v>136</v>
-      </c>
-      <c r="M48">
-        <v>291490</v>
-      </c>
-      <c r="N48" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14">
-      <c r="A49" t="s">
-        <v>32</v>
-      </c>
-      <c r="B49" t="s">
-        <v>34</v>
-      </c>
-      <c r="C49" t="s">
-        <v>54</v>
-      </c>
-      <c r="D49" t="s">
-        <v>79</v>
-      </c>
-      <c r="E49" t="s">
-        <v>86</v>
-      </c>
-      <c r="F49">
-        <v>25.01</v>
-      </c>
-      <c r="G49" t="s">
-        <v>91</v>
-      </c>
-      <c r="H49">
-        <v>1.5</v>
-      </c>
-      <c r="I49" s="1">
-        <v>37.52</v>
-      </c>
-      <c r="J49">
-        <v>1.54</v>
-      </c>
-      <c r="K49" s="1">
-        <v>38.52</v>
-      </c>
-      <c r="L49" t="s">
-        <v>137</v>
-      </c>
-      <c r="M49">
-        <v>327070</v>
-      </c>
-      <c r="N49" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14">
-      <c r="A50" t="s">
-        <v>32</v>
-      </c>
-      <c r="B50" t="s">
-        <v>34</v>
-      </c>
-      <c r="C50" t="s">
-        <v>39</v>
-      </c>
-      <c r="D50" t="s">
-        <v>64</v>
-      </c>
-      <c r="E50" t="s">
-        <v>87</v>
-      </c>
-      <c r="F50">
-        <v>51.85</v>
-      </c>
-      <c r="G50" t="s">
-        <v>91</v>
-      </c>
-      <c r="H50">
-        <v>1.7</v>
-      </c>
-      <c r="I50" s="1">
-        <v>88.14</v>
-      </c>
-      <c r="J50">
-        <v>1.74</v>
-      </c>
-      <c r="K50" s="1">
-        <v>90.22</v>
-      </c>
-      <c r="L50" t="s">
-        <v>138</v>
-      </c>
-      <c r="M50">
-        <v>42235</v>
-      </c>
-      <c r="N50" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14">
-      <c r="A51" t="s">
-        <v>33</v>
-      </c>
       <c r="B51" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C51" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D51" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E51" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F51">
         <v>30</v>
       </c>
       <c r="G51" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H51">
+        <v>1.689</v>
+      </c>
+      <c r="I51" s="1">
         <v>1.73</v>
       </c>
-      <c r="I51" s="1">
+      <c r="J51">
         <v>51.9</v>
       </c>
-      <c r="J51">
+      <c r="K51" s="1">
         <v>1.77</v>
       </c>
-      <c r="K51" s="1">
+      <c r="L51" s="1">
         <v>53.1</v>
       </c>
-      <c r="L51" t="s">
-        <v>139</v>
-      </c>
-      <c r="M51">
+      <c r="M51" t="s">
+        <v>140</v>
+      </c>
+      <c r="N51">
         <v>287420</v>
       </c>
-      <c r="N51" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14">
+      <c r="O51" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15">
       <c r="A52" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B52" t="s">
+        <v>35</v>
+      </c>
+      <c r="C52" t="s">
+        <v>52</v>
+      </c>
+      <c r="D52" t="s">
+        <v>77</v>
+      </c>
+      <c r="E52" t="s">
+        <v>88</v>
+      </c>
+      <c r="F52">
+        <v>54.831</v>
+      </c>
+      <c r="G52" t="s">
+        <v>92</v>
+      </c>
+      <c r="H52">
+        <v>1.689</v>
+      </c>
+      <c r="I52" s="1">
+        <v>1.73</v>
+      </c>
+      <c r="J52">
+        <v>94.85763</v>
+      </c>
+      <c r="K52" s="1">
+        <v>1.77</v>
+      </c>
+      <c r="L52" s="1">
+        <v>97.05087</v>
+      </c>
+      <c r="M52" t="s">
+        <v>141</v>
+      </c>
+      <c r="N52">
+        <v>265247</v>
+      </c>
+      <c r="O52" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15">
+      <c r="A53" t="s">
         <v>34</v>
       </c>
-      <c r="C52" t="s">
-        <v>51</v>
-      </c>
-      <c r="D52" t="s">
-        <v>76</v>
-      </c>
-      <c r="E52" t="s">
-        <v>87</v>
-      </c>
-      <c r="F52">
-        <v>54.83</v>
-      </c>
-      <c r="G52" t="s">
-        <v>91</v>
-      </c>
-      <c r="H52">
-        <v>1.73</v>
-      </c>
-      <c r="I52" s="1">
-        <v>94.86</v>
-      </c>
-      <c r="J52">
-        <v>1.77</v>
-      </c>
-      <c r="K52" s="1">
-        <v>97.05</v>
-      </c>
-      <c r="L52" t="s">
-        <v>140</v>
-      </c>
-      <c r="M52">
-        <v>265247</v>
-      </c>
-      <c r="N52" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14">
-      <c r="A53" t="s">
-        <v>33</v>
-      </c>
       <c r="B53" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C53" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D53" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E53" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F53">
         <v>39</v>
       </c>
       <c r="G53" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H53">
+        <v>1.689</v>
+      </c>
+      <c r="I53" s="1">
         <v>1.73</v>
       </c>
-      <c r="I53" s="1">
+      <c r="J53">
         <v>67.47</v>
       </c>
-      <c r="J53">
+      <c r="K53" s="1">
         <v>1.77</v>
       </c>
-      <c r="K53" s="1">
+      <c r="L53" s="1">
         <v>69.03</v>
       </c>
-      <c r="L53" t="s">
-        <v>141</v>
-      </c>
-      <c r="M53">
+      <c r="M53" t="s">
+        <v>142</v>
+      </c>
+      <c r="N53">
         <v>260190</v>
       </c>
-      <c r="N53" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14">
+      <c r="O53" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15">
       <c r="A54" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B54" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C54" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D54" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E54" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F54">
         <v>27</v>
       </c>
       <c r="G54" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H54">
+        <v>1.459</v>
+      </c>
+      <c r="I54" s="1">
         <v>1.5</v>
       </c>
-      <c r="I54" s="1">
+      <c r="J54">
         <v>40.5</v>
       </c>
-      <c r="J54">
+      <c r="K54" s="1">
         <v>1.54</v>
       </c>
-      <c r="K54" s="1">
+      <c r="L54" s="1">
         <v>41.58</v>
       </c>
-      <c r="L54" t="s">
-        <v>126</v>
-      </c>
-      <c r="M54">
+      <c r="M54" t="s">
+        <v>127</v>
+      </c>
+      <c r="N54">
         <v>327405</v>
       </c>
-      <c r="N54" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14">
+      <c r="O54" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15">
       <c r="A55" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B55" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C55" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D55" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E55" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F55">
         <v>14</v>
       </c>
       <c r="G55" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H55">
+        <v>1.689</v>
+      </c>
+      <c r="I55" s="1">
         <v>1.73</v>
       </c>
-      <c r="I55" s="1">
+      <c r="J55">
         <v>24.22</v>
       </c>
-      <c r="J55">
+      <c r="K55" s="1">
         <v>1.77</v>
       </c>
-      <c r="K55" s="1">
+      <c r="L55" s="1">
         <v>24.78</v>
       </c>
-      <c r="L55" t="s">
-        <v>142</v>
-      </c>
-      <c r="M55">
+      <c r="M55" t="s">
+        <v>143</v>
+      </c>
+      <c r="N55">
         <v>291780</v>
       </c>
-      <c r="N55" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14">
+      <c r="O55" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15">
       <c r="A56" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B56" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C56" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D56" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E56" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F56">
         <v>22</v>
       </c>
       <c r="G56" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H56">
+        <v>1.459</v>
+      </c>
+      <c r="I56" s="1">
         <v>1.5</v>
       </c>
-      <c r="I56" s="1">
+      <c r="J56">
         <v>33</v>
       </c>
-      <c r="J56">
+      <c r="K56" s="1">
         <v>1.54</v>
       </c>
-      <c r="K56" s="1">
+      <c r="L56" s="1">
         <v>33.88</v>
       </c>
-      <c r="L56" t="s">
-        <v>143</v>
-      </c>
-      <c r="M56">
+      <c r="M56" t="s">
+        <v>144</v>
+      </c>
+      <c r="N56">
         <v>21275</v>
       </c>
-      <c r="N56" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14">
+      <c r="O56" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15">
       <c r="A57" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B57" t="s">
+        <v>35</v>
+      </c>
+      <c r="C57" t="s">
+        <v>48</v>
+      </c>
+      <c r="D57" t="s">
+        <v>73</v>
+      </c>
+      <c r="E57" t="s">
+        <v>88</v>
+      </c>
+      <c r="F57">
+        <v>38.559</v>
+      </c>
+      <c r="G57" t="s">
+        <v>92</v>
+      </c>
+      <c r="H57">
+        <v>1.689</v>
+      </c>
+      <c r="I57" s="1">
+        <v>1.73</v>
+      </c>
+      <c r="J57">
+        <v>66.70707</v>
+      </c>
+      <c r="K57" s="1">
+        <v>1.77</v>
+      </c>
+      <c r="L57" s="1">
+        <v>68.24943</v>
+      </c>
+      <c r="M57" t="s">
+        <v>145</v>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+      <c r="O57" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15">
+      <c r="A58" t="s">
         <v>34</v>
       </c>
-      <c r="C57" t="s">
+      <c r="B58" t="s">
+        <v>35</v>
+      </c>
+      <c r="C58" t="s">
+        <v>49</v>
+      </c>
+      <c r="D58" t="s">
+        <v>74</v>
+      </c>
+      <c r="E58" t="s">
+        <v>88</v>
+      </c>
+      <c r="F58">
+        <v>24.362</v>
+      </c>
+      <c r="G58" t="s">
+        <v>92</v>
+      </c>
+      <c r="H58">
+        <v>1.689</v>
+      </c>
+      <c r="I58" s="1">
+        <v>1.73</v>
+      </c>
+      <c r="J58">
+        <v>42.14626</v>
+      </c>
+      <c r="K58" s="1">
+        <v>1.77</v>
+      </c>
+      <c r="L58" s="1">
+        <v>43.12074</v>
+      </c>
+      <c r="M58" t="s">
+        <v>146</v>
+      </c>
+      <c r="N58">
+        <v>0</v>
+      </c>
+      <c r="O58" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15">
+      <c r="A59" t="s">
+        <v>34</v>
+      </c>
+      <c r="B59" t="s">
+        <v>35</v>
+      </c>
+      <c r="C59" t="s">
         <v>47</v>
       </c>
-      <c r="D57" t="s">
+      <c r="D59" t="s">
         <v>72</v>
       </c>
-      <c r="E57" t="s">
-        <v>87</v>
-      </c>
-      <c r="F57">
-        <v>38.56</v>
-      </c>
-      <c r="G57" t="s">
-        <v>91</v>
-      </c>
-      <c r="H57">
-        <v>1.73</v>
-      </c>
-      <c r="I57" s="1">
-        <v>66.70999999999999</v>
-      </c>
-      <c r="J57">
-        <v>1.77</v>
-      </c>
-      <c r="K57" s="1">
-        <v>68.25</v>
-      </c>
-      <c r="L57" t="s">
-        <v>144</v>
-      </c>
-      <c r="M57">
-        <v>0</v>
-      </c>
-      <c r="N57" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14">
-      <c r="A58" t="s">
-        <v>33</v>
-      </c>
-      <c r="B58" t="s">
-        <v>34</v>
-      </c>
-      <c r="C58" t="s">
-        <v>48</v>
-      </c>
-      <c r="D58" t="s">
-        <v>73</v>
-      </c>
-      <c r="E58" t="s">
-        <v>87</v>
-      </c>
-      <c r="F58">
-        <v>24.36</v>
-      </c>
-      <c r="G58" t="s">
-        <v>91</v>
-      </c>
-      <c r="H58">
-        <v>1.73</v>
-      </c>
-      <c r="I58" s="1">
-        <v>42.14</v>
-      </c>
-      <c r="J58">
-        <v>1.77</v>
-      </c>
-      <c r="K58" s="1">
-        <v>43.12</v>
-      </c>
-      <c r="L58" t="s">
-        <v>145</v>
-      </c>
-      <c r="M58">
-        <v>0</v>
-      </c>
-      <c r="N58" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14">
-      <c r="A59" t="s">
-        <v>33</v>
-      </c>
-      <c r="B59" t="s">
-        <v>34</v>
-      </c>
-      <c r="C59" t="s">
-        <v>46</v>
-      </c>
-      <c r="D59" t="s">
-        <v>71</v>
-      </c>
       <c r="E59" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F59">
         <v>16</v>
       </c>
       <c r="G59" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H59">
+        <v>1.689</v>
+      </c>
+      <c r="I59" s="1">
         <v>1.73</v>
       </c>
-      <c r="I59" s="1">
+      <c r="J59">
         <v>27.68</v>
       </c>
-      <c r="J59">
+      <c r="K59" s="1">
         <v>1.77</v>
       </c>
-      <c r="K59" s="1">
+      <c r="L59" s="1">
         <v>28.32</v>
       </c>
-      <c r="L59" t="s">
-        <v>146</v>
-      </c>
-      <c r="M59">
+      <c r="M59" t="s">
+        <v>147</v>
+      </c>
+      <c r="N59">
         <v>256400</v>
       </c>
-      <c r="N59" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="60" spans="1:14">
+      <c r="O59" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15">
       <c r="A60" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B60" t="s">
+        <v>35</v>
+      </c>
+      <c r="C60" t="s">
+        <v>45</v>
+      </c>
+      <c r="D60" t="s">
+        <v>70</v>
+      </c>
+      <c r="E60" t="s">
+        <v>88</v>
+      </c>
+      <c r="F60">
+        <v>27.006</v>
+      </c>
+      <c r="G60" t="s">
+        <v>92</v>
+      </c>
+      <c r="H60">
+        <v>1.689</v>
+      </c>
+      <c r="I60" s="1">
+        <v>1.73</v>
+      </c>
+      <c r="J60">
+        <v>46.72038</v>
+      </c>
+      <c r="K60" s="1">
+        <v>1.77</v>
+      </c>
+      <c r="L60" s="1">
+        <v>47.80062</v>
+      </c>
+      <c r="M60" t="s">
+        <v>116</v>
+      </c>
+      <c r="N60">
+        <v>268295</v>
+      </c>
+      <c r="O60" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15">
+      <c r="A61" t="s">
         <v>34</v>
       </c>
-      <c r="C60" t="s">
-        <v>44</v>
-      </c>
-      <c r="D60" t="s">
-        <v>69</v>
-      </c>
-      <c r="E60" t="s">
-        <v>87</v>
-      </c>
-      <c r="F60">
-        <v>27.01</v>
-      </c>
-      <c r="G60" t="s">
-        <v>91</v>
-      </c>
-      <c r="H60">
+      <c r="B61" t="s">
+        <v>35</v>
+      </c>
+      <c r="C61" t="s">
+        <v>61</v>
+      </c>
+      <c r="D61" t="s">
+        <v>86</v>
+      </c>
+      <c r="E61" t="s">
+        <v>88</v>
+      </c>
+      <c r="F61">
+        <v>29.011</v>
+      </c>
+      <c r="G61" t="s">
+        <v>92</v>
+      </c>
+      <c r="H61">
+        <v>1.689</v>
+      </c>
+      <c r="I61" s="1">
         <v>1.73</v>
       </c>
-      <c r="I60" s="1">
-        <v>46.73</v>
-      </c>
-      <c r="J60">
+      <c r="J61">
+        <v>50.18903</v>
+      </c>
+      <c r="K61" s="1">
         <v>1.77</v>
       </c>
-      <c r="K60" s="1">
-        <v>47.81</v>
-      </c>
-      <c r="L60" t="s">
-        <v>115</v>
-      </c>
-      <c r="M60">
-        <v>268295</v>
-      </c>
-      <c r="N60" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="61" spans="1:14">
-      <c r="A61" t="s">
-        <v>33</v>
-      </c>
-      <c r="B61" t="s">
+      <c r="L61" s="1">
+        <v>51.34947</v>
+      </c>
+      <c r="M61" t="s">
+        <v>148</v>
+      </c>
+      <c r="N61">
+        <v>0</v>
+      </c>
+      <c r="O61" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15">
+      <c r="A62" t="s">
         <v>34</v>
       </c>
-      <c r="C61" t="s">
-        <v>60</v>
-      </c>
-      <c r="D61" t="s">
-        <v>85</v>
-      </c>
-      <c r="E61" t="s">
-        <v>87</v>
-      </c>
-      <c r="F61">
-        <v>29.01</v>
-      </c>
-      <c r="G61" t="s">
-        <v>91</v>
-      </c>
-      <c r="H61">
+      <c r="B62" t="s">
+        <v>35</v>
+      </c>
+      <c r="C62" t="s">
+        <v>58</v>
+      </c>
+      <c r="D62" t="s">
+        <v>83</v>
+      </c>
+      <c r="E62" t="s">
+        <v>88</v>
+      </c>
+      <c r="F62">
+        <v>37.006</v>
+      </c>
+      <c r="G62" t="s">
+        <v>92</v>
+      </c>
+      <c r="H62">
+        <v>1.689</v>
+      </c>
+      <c r="I62" s="1">
         <v>1.73</v>
       </c>
-      <c r="I61" s="1">
-        <v>50.19</v>
-      </c>
-      <c r="J61">
+      <c r="J62">
+        <v>64.02038</v>
+      </c>
+      <c r="K62" s="1">
         <v>1.77</v>
       </c>
-      <c r="K61" s="1">
-        <v>51.35</v>
-      </c>
-      <c r="L61" t="s">
-        <v>147</v>
-      </c>
-      <c r="M61">
-        <v>0</v>
-      </c>
-      <c r="N61" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="62" spans="1:14">
-      <c r="A62" t="s">
-        <v>33</v>
-      </c>
-      <c r="B62" t="s">
+      <c r="L62" s="1">
+        <v>65.50062</v>
+      </c>
+      <c r="M62" t="s">
+        <v>133</v>
+      </c>
+      <c r="N62">
+        <v>111500</v>
+      </c>
+      <c r="O62" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15">
+      <c r="A63" t="s">
         <v>34</v>
       </c>
-      <c r="C62" t="s">
-        <v>57</v>
-      </c>
-      <c r="D62" t="s">
-        <v>82</v>
-      </c>
-      <c r="E62" t="s">
-        <v>87</v>
-      </c>
-      <c r="F62">
-        <v>37.01</v>
-      </c>
-      <c r="G62" t="s">
-        <v>91</v>
-      </c>
-      <c r="H62">
+      <c r="B63" t="s">
+        <v>35</v>
+      </c>
+      <c r="C63" t="s">
+        <v>40</v>
+      </c>
+      <c r="D63" t="s">
+        <v>65</v>
+      </c>
+      <c r="E63" t="s">
+        <v>88</v>
+      </c>
+      <c r="F63">
+        <v>22.011</v>
+      </c>
+      <c r="G63" t="s">
+        <v>92</v>
+      </c>
+      <c r="H63">
+        <v>1.689</v>
+      </c>
+      <c r="I63" s="1">
         <v>1.73</v>
       </c>
-      <c r="I62" s="1">
-        <v>64.03</v>
-      </c>
-      <c r="J62">
+      <c r="J63">
+        <v>38.07903</v>
+      </c>
+      <c r="K63" s="1">
         <v>1.77</v>
       </c>
-      <c r="K62" s="1">
-        <v>65.51000000000001</v>
-      </c>
-      <c r="L62" t="s">
-        <v>132</v>
-      </c>
-      <c r="M62">
-        <v>111500</v>
-      </c>
-      <c r="N62" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14">
-      <c r="A63" t="s">
-        <v>33</v>
-      </c>
-      <c r="B63" t="s">
+      <c r="L63" s="1">
+        <v>38.95947</v>
+      </c>
+      <c r="M63" t="s">
+        <v>105</v>
+      </c>
+      <c r="N63">
+        <v>42399</v>
+      </c>
+      <c r="O63" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15">
+      <c r="A64" t="s">
         <v>34</v>
       </c>
-      <c r="C63" t="s">
-        <v>39</v>
-      </c>
-      <c r="D63" t="s">
-        <v>64</v>
-      </c>
-      <c r="E63" t="s">
-        <v>87</v>
-      </c>
-      <c r="F63">
-        <v>22.01</v>
-      </c>
-      <c r="G63" t="s">
-        <v>91</v>
-      </c>
-      <c r="H63">
-        <v>1.73</v>
-      </c>
-      <c r="I63" s="1">
-        <v>38.08</v>
-      </c>
-      <c r="J63">
-        <v>1.77</v>
-      </c>
-      <c r="K63" s="1">
-        <v>38.96</v>
-      </c>
-      <c r="L63" t="s">
-        <v>104</v>
-      </c>
-      <c r="M63">
-        <v>42399</v>
-      </c>
-      <c r="N63" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="64" spans="1:14">
-      <c r="A64" t="s">
-        <v>33</v>
-      </c>
       <c r="B64" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C64" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D64" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E64" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F64">
         <v>1</v>
       </c>
       <c r="G64" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H64">
         <v>24.99</v>
@@ -3919,257 +4111,275 @@
       <c r="K64" s="1">
         <v>24.99</v>
       </c>
-      <c r="L64" t="s">
-        <v>104</v>
-      </c>
-      <c r="M64">
+      <c r="L64" s="1">
+        <v>24.99</v>
+      </c>
+      <c r="M64" t="s">
+        <v>105</v>
+      </c>
+      <c r="N64">
         <v>42399</v>
       </c>
-      <c r="N64" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="65" spans="1:14">
+      <c r="O64" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15">
       <c r="A65" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B65" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C65" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D65" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E65" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F65">
         <v>6</v>
       </c>
       <c r="G65" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H65">
+        <v>1.459</v>
+      </c>
+      <c r="I65" s="1">
         <v>1.5</v>
       </c>
-      <c r="I65" s="1">
+      <c r="J65">
         <v>9</v>
       </c>
-      <c r="J65">
+      <c r="K65" s="1">
         <v>1.54</v>
       </c>
-      <c r="K65" s="1">
+      <c r="L65" s="1">
         <v>9.24</v>
       </c>
-      <c r="L65" t="s">
-        <v>148</v>
-      </c>
-      <c r="M65">
+      <c r="M65" t="s">
+        <v>149</v>
+      </c>
+      <c r="N65">
         <v>75676</v>
       </c>
-      <c r="N65" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="66" spans="1:14">
+      <c r="O65" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15">
       <c r="A66" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B66" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C66" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D66" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E66" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F66">
         <v>18</v>
       </c>
       <c r="G66" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H66">
+        <v>1.459</v>
+      </c>
+      <c r="I66" s="1">
         <v>1.5</v>
       </c>
-      <c r="I66" s="1">
+      <c r="J66">
         <v>27</v>
       </c>
-      <c r="J66">
+      <c r="K66" s="1">
         <v>1.54</v>
       </c>
-      <c r="K66" s="1">
+      <c r="L66" s="1">
         <v>27.72</v>
       </c>
-      <c r="L66" t="s">
-        <v>149</v>
-      </c>
-      <c r="M66">
+      <c r="M66" t="s">
+        <v>150</v>
+      </c>
+      <c r="N66">
         <v>301160</v>
       </c>
-      <c r="N66" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="67" spans="1:14">
+      <c r="O66" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15">
       <c r="A67" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B67" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C67" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D67" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E67" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F67">
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H67">
+        <v>1.459</v>
+      </c>
+      <c r="I67" s="1">
         <v>1.5</v>
       </c>
-      <c r="I67" s="1">
+      <c r="J67">
         <v>22.5</v>
       </c>
-      <c r="J67">
+      <c r="K67" s="1">
         <v>1.54</v>
       </c>
-      <c r="K67" s="1">
+      <c r="L67" s="1">
         <v>23.1</v>
       </c>
-      <c r="L67" t="s">
-        <v>150</v>
-      </c>
-      <c r="M67">
+      <c r="M67" t="s">
+        <v>151</v>
+      </c>
+      <c r="N67">
         <v>7755</v>
       </c>
-      <c r="N67" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="68" spans="1:14">
+      <c r="O67" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15">
       <c r="A68" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B68" t="s">
+        <v>35</v>
+      </c>
+      <c r="C68" t="s">
+        <v>54</v>
+      </c>
+      <c r="D68" t="s">
+        <v>79</v>
+      </c>
+      <c r="E68" t="s">
+        <v>88</v>
+      </c>
+      <c r="F68">
+        <v>29.774</v>
+      </c>
+      <c r="G68" t="s">
+        <v>92</v>
+      </c>
+      <c r="H68">
+        <v>1.689</v>
+      </c>
+      <c r="I68" s="1">
+        <v>1.73</v>
+      </c>
+      <c r="J68">
+        <v>51.50902</v>
+      </c>
+      <c r="K68" s="1">
+        <v>1.77</v>
+      </c>
+      <c r="L68" s="1">
+        <v>52.69998</v>
+      </c>
+      <c r="M68" t="s">
+        <v>112</v>
+      </c>
+      <c r="N68">
+        <v>236251</v>
+      </c>
+      <c r="O68" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15">
+      <c r="A69" t="s">
         <v>34</v>
       </c>
-      <c r="C68" t="s">
-        <v>53</v>
-      </c>
-      <c r="D68" t="s">
-        <v>78</v>
-      </c>
-      <c r="E68" t="s">
-        <v>87</v>
-      </c>
-      <c r="F68">
-        <v>29.77</v>
-      </c>
-      <c r="G68" t="s">
-        <v>91</v>
-      </c>
-      <c r="H68">
-        <v>1.73</v>
-      </c>
-      <c r="I68" s="1">
-        <v>51.5</v>
-      </c>
-      <c r="J68">
-        <v>1.77</v>
-      </c>
-      <c r="K68" s="1">
-        <v>52.69</v>
-      </c>
-      <c r="L68" t="s">
-        <v>111</v>
-      </c>
-      <c r="M68">
-        <v>236251</v>
-      </c>
-      <c r="N68" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="69" spans="1:14">
-      <c r="A69" t="s">
-        <v>33</v>
-      </c>
       <c r="B69" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C69" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D69" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E69" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F69">
         <v>29</v>
       </c>
       <c r="G69" t="s">
+        <v>92</v>
+      </c>
+      <c r="H69">
+        <v>1.689</v>
+      </c>
+      <c r="I69" s="1">
+        <v>1.73</v>
+      </c>
+      <c r="J69">
+        <v>50.17</v>
+      </c>
+      <c r="K69" s="1">
+        <v>1.77</v>
+      </c>
+      <c r="L69" s="1">
+        <v>51.33</v>
+      </c>
+      <c r="M69" t="s">
+        <v>152</v>
+      </c>
+      <c r="N69">
+        <v>27540</v>
+      </c>
+      <c r="O69" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15">
+      <c r="A70" t="s">
+        <v>34</v>
+      </c>
+      <c r="B70" t="s">
+        <v>35</v>
+      </c>
+      <c r="C70" t="s">
+        <v>57</v>
+      </c>
+      <c r="D70" t="s">
+        <v>82</v>
+      </c>
+      <c r="E70" t="s">
         <v>91</v>
-      </c>
-      <c r="H69">
-        <v>1.73</v>
-      </c>
-      <c r="I69" s="1">
-        <v>50.17</v>
-      </c>
-      <c r="J69">
-        <v>1.77</v>
-      </c>
-      <c r="K69" s="1">
-        <v>51.33</v>
-      </c>
-      <c r="L69" t="s">
-        <v>151</v>
-      </c>
-      <c r="M69">
-        <v>27540</v>
-      </c>
-      <c r="N69" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="70" spans="1:14">
-      <c r="A70" t="s">
-        <v>33</v>
-      </c>
-      <c r="B70" t="s">
-        <v>34</v>
-      </c>
-      <c r="C70" t="s">
-        <v>56</v>
-      </c>
-      <c r="D70" t="s">
-        <v>81</v>
-      </c>
-      <c r="E70" t="s">
-        <v>90</v>
       </c>
       <c r="F70">
         <v>1</v>
       </c>
       <c r="G70" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H70">
         <v>14.99</v>
@@ -4183,63 +4393,69 @@
       <c r="K70" s="1">
         <v>14.99</v>
       </c>
-      <c r="L70" t="s">
-        <v>151</v>
-      </c>
-      <c r="M70">
+      <c r="L70" s="1">
+        <v>14.99</v>
+      </c>
+      <c r="M70" t="s">
+        <v>152</v>
+      </c>
+      <c r="N70">
         <v>27540</v>
       </c>
-      <c r="N70" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="71" spans="1:14">
+      <c r="O70" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15">
       <c r="A71" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B71" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C71" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D71" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E71" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F71">
-        <v>17.63</v>
+        <v>17.633</v>
       </c>
       <c r="G71" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H71">
+        <v>1.689</v>
+      </c>
+      <c r="I71" s="1">
         <v>1.73</v>
       </c>
-      <c r="I71" s="1">
-        <v>30.5</v>
-      </c>
       <c r="J71">
+        <v>30.50509</v>
+      </c>
+      <c r="K71" s="1">
         <v>1.77</v>
       </c>
-      <c r="K71" s="1">
-        <v>31.21</v>
-      </c>
-      <c r="L71" t="s">
-        <v>152</v>
-      </c>
-      <c r="M71">
+      <c r="L71" s="1">
+        <v>31.21041</v>
+      </c>
+      <c r="M71" t="s">
+        <v>153</v>
+      </c>
+      <c r="N71">
         <v>0</v>
       </c>
-      <c r="N71" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="74" spans="1:14">
+      <c r="O71" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15">
       <c r="A74" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
@@ -4247,49 +4463,49 @@
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
     </row>
-    <row r="75" spans="1:14">
+    <row r="75" spans="1:15">
       <c r="A75" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="76" spans="1:14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15">
       <c r="A76" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B76" s="6">
-        <v>1817.01</v>
+        <v>1817.022</v>
       </c>
       <c r="C76" s="6">
         <v>45</v>
       </c>
       <c r="D76" s="7">
-        <v>1.621604</v>
+        <v>1.621598</v>
       </c>
       <c r="E76" s="6">
-        <v>2946.47</v>
+        <v>2946.48</v>
       </c>
       <c r="F76" s="6">
         <v>3019.16</v>
       </c>
     </row>
-    <row r="77" spans="1:14">
+    <row r="77" spans="1:15">
       <c r="A77" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B77" s="6">
         <v>518.5700000000001</v>
@@ -4298,18 +4514,18 @@
         <v>21</v>
       </c>
       <c r="D77" s="7">
-        <v>1.480726</v>
+        <v>1.480743</v>
       </c>
       <c r="E77" s="6">
-        <v>767.86</v>
+        <v>767.87</v>
       </c>
       <c r="F77" s="6">
-        <v>788.62</v>
-      </c>
-    </row>
-    <row r="78" spans="1:14">
+        <v>788.61</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15">
       <c r="A78" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B78" s="6">
         <v>87</v>
@@ -4327,9 +4543,9 @@
         <v>153.97</v>
       </c>
     </row>
-    <row r="79" spans="1:14">
+    <row r="79" spans="1:15">
       <c r="A79" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B79" s="6">
         <v>1</v>
@@ -4347,9 +4563,9 @@
         <v>24.99</v>
       </c>
     </row>
-    <row r="80" spans="1:14">
+    <row r="80" spans="1:15">
       <c r="A80" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B80" s="6">
         <v>1</v>
@@ -4369,20 +4585,20 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B81" s="9">
-        <v>2424.58</v>
+        <v>2424.592</v>
       </c>
       <c r="C81" s="9">
         <v>70</v>
       </c>
       <c r="D81" s="7"/>
       <c r="E81" s="9">
-        <v>3903.93</v>
+        <v>3903.95</v>
       </c>
       <c r="F81" s="9">
-        <v>4001.73</v>
+        <v>4001.72</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ДОБРИЧКА/ОБЩИНА ДОБРИЧКА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ДОБРИЧКА/ОБЩИНА ДОБРИЧКА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="227">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -705,8 +702,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -799,10 +796,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1097,7 +1094,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O81"/>
+  <dimension ref="A1:N81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -1110,13 +1107,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1159,2945 +1156,2756 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F2">
         <v>33.82</v>
       </c>
       <c r="G2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H2">
-        <v>1.359</v>
+        <v>1.46</v>
       </c>
       <c r="I2" s="1">
-        <v>1.46</v>
+        <v>49.377</v>
       </c>
       <c r="J2">
-        <v>49.3772</v>
+        <v>1.5</v>
       </c>
       <c r="K2" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L2" s="1">
         <v>50.73</v>
       </c>
-      <c r="M2" t="s">
-        <v>94</v>
-      </c>
-      <c r="N2">
+      <c r="L2" t="s">
+        <v>93</v>
+      </c>
+      <c r="M2">
         <v>234743</v>
       </c>
-      <c r="O2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="N2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F3">
         <v>49.349</v>
       </c>
       <c r="G3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H3">
-        <v>1.406</v>
+        <v>1.48</v>
       </c>
       <c r="I3" s="1">
-        <v>1.48</v>
+        <v>73.03700000000001</v>
       </c>
       <c r="J3">
-        <v>73.03652</v>
+        <v>1.52</v>
       </c>
       <c r="K3" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L3" s="1">
-        <v>75.01048</v>
-      </c>
-      <c r="M3" t="s">
-        <v>95</v>
-      </c>
-      <c r="N3">
+        <v>75.01000000000001</v>
+      </c>
+      <c r="L3" t="s">
+        <v>94</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-      <c r="O3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="N3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F4">
         <v>16.887</v>
       </c>
       <c r="G4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H4">
-        <v>1.359</v>
+        <v>1.46</v>
       </c>
       <c r="I4" s="1">
-        <v>1.46</v>
+        <v>24.655</v>
       </c>
       <c r="J4">
-        <v>24.65502</v>
+        <v>1.5</v>
       </c>
       <c r="K4" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L4" s="1">
-        <v>25.3305</v>
-      </c>
-      <c r="M4" t="s">
-        <v>96</v>
-      </c>
-      <c r="N4">
+        <v>25.33</v>
+      </c>
+      <c r="L4" t="s">
+        <v>95</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
-      <c r="O4" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="N4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F5">
         <v>45.461</v>
       </c>
       <c r="G5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H5">
-        <v>1.406</v>
+        <v>1.48</v>
       </c>
       <c r="I5" s="1">
-        <v>1.48</v>
+        <v>67.282</v>
       </c>
       <c r="J5">
-        <v>67.28228</v>
+        <v>1.52</v>
       </c>
       <c r="K5" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L5" s="1">
-        <v>69.10072</v>
-      </c>
-      <c r="M5" t="s">
-        <v>97</v>
-      </c>
-      <c r="N5">
+        <v>69.101</v>
+      </c>
+      <c r="L5" t="s">
+        <v>96</v>
+      </c>
+      <c r="M5">
         <v>41143</v>
       </c>
-      <c r="O5" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="N5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F6">
         <v>41</v>
       </c>
       <c r="G6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H6">
-        <v>1.406</v>
+        <v>1.48</v>
       </c>
       <c r="I6" s="1">
-        <v>1.48</v>
+        <v>60.68</v>
       </c>
       <c r="J6">
-        <v>60.68</v>
+        <v>1.52</v>
       </c>
       <c r="K6" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L6" s="1">
         <v>62.32</v>
       </c>
-      <c r="M6" t="s">
-        <v>98</v>
-      </c>
-      <c r="N6">
+      <c r="L6" t="s">
+        <v>97</v>
+      </c>
+      <c r="M6">
         <v>285990</v>
       </c>
-      <c r="O6" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="N6" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F7">
         <v>23.849</v>
       </c>
       <c r="G7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H7">
-        <v>1.406</v>
+        <v>1.48</v>
       </c>
       <c r="I7" s="1">
-        <v>1.48</v>
+        <v>35.297</v>
       </c>
       <c r="J7">
-        <v>35.29652</v>
+        <v>1.52</v>
       </c>
       <c r="K7" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L7" s="1">
-        <v>36.25048</v>
-      </c>
-      <c r="M7" t="s">
-        <v>99</v>
-      </c>
-      <c r="N7">
+        <v>36.25</v>
+      </c>
+      <c r="L7" t="s">
+        <v>98</v>
+      </c>
+      <c r="M7">
         <v>242359</v>
       </c>
-      <c r="O7" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="N7" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F8">
         <v>22</v>
       </c>
       <c r="G8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H8">
-        <v>1.359</v>
+        <v>1.45</v>
       </c>
       <c r="I8" s="1">
-        <v>1.45</v>
+        <v>31.9</v>
       </c>
       <c r="J8">
-        <v>31.9</v>
+        <v>1.49</v>
       </c>
       <c r="K8" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="L8" s="1">
         <v>32.78</v>
       </c>
-      <c r="M8" t="s">
-        <v>100</v>
-      </c>
-      <c r="N8">
+      <c r="L8" t="s">
+        <v>99</v>
+      </c>
+      <c r="M8">
         <v>20945</v>
       </c>
-      <c r="O8" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="N8" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F9">
         <v>26</v>
       </c>
       <c r="G9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H9">
-        <v>1.359</v>
+        <v>1.45</v>
       </c>
       <c r="I9" s="1">
-        <v>1.45</v>
+        <v>37.7</v>
       </c>
       <c r="J9">
-        <v>37.7</v>
+        <v>1.49</v>
       </c>
       <c r="K9" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="L9" s="1">
         <v>38.74</v>
       </c>
-      <c r="M9" t="s">
-        <v>101</v>
-      </c>
-      <c r="N9">
+      <c r="L9" t="s">
+        <v>100</v>
+      </c>
+      <c r="M9">
         <v>7020</v>
       </c>
-      <c r="O9" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="N9" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F10">
         <v>53.112</v>
       </c>
       <c r="G10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H10">
-        <v>1.412</v>
+        <v>1.48</v>
       </c>
       <c r="I10" s="1">
-        <v>1.48</v>
+        <v>78.60599999999999</v>
       </c>
       <c r="J10">
-        <v>78.60576</v>
+        <v>1.52</v>
       </c>
       <c r="K10" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L10" s="1">
-        <v>80.73023999999999</v>
-      </c>
-      <c r="M10" t="s">
-        <v>102</v>
-      </c>
-      <c r="N10">
+        <v>80.73</v>
+      </c>
+      <c r="L10" t="s">
+        <v>101</v>
+      </c>
+      <c r="M10">
         <v>284567</v>
       </c>
-      <c r="O10" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="N10" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F11">
         <v>44</v>
       </c>
       <c r="G11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H11">
-        <v>1.629</v>
+        <v>1.7</v>
       </c>
       <c r="I11" s="1">
-        <v>1.7</v>
+        <v>74.8</v>
       </c>
       <c r="J11">
-        <v>74.8</v>
+        <v>1.75</v>
       </c>
       <c r="K11" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L11" s="1">
         <v>77</v>
       </c>
-      <c r="M11" t="s">
-        <v>103</v>
-      </c>
-      <c r="N11">
+      <c r="L11" t="s">
+        <v>102</v>
+      </c>
+      <c r="M11">
         <v>182486</v>
       </c>
-      <c r="O11" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+      <c r="N11" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F12">
         <v>37.623</v>
       </c>
       <c r="G12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H12">
-        <v>1.437</v>
+        <v>1.5</v>
       </c>
       <c r="I12" s="1">
-        <v>1.5</v>
+        <v>56.434</v>
       </c>
       <c r="J12">
-        <v>56.4345</v>
+        <v>1.54</v>
       </c>
       <c r="K12" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L12" s="1">
-        <v>57.93942</v>
-      </c>
-      <c r="M12" t="s">
-        <v>104</v>
-      </c>
-      <c r="N12">
+        <v>57.939</v>
+      </c>
+      <c r="L12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M12">
         <v>255470</v>
       </c>
-      <c r="O12" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+      <c r="N12" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F13">
         <v>35.071</v>
       </c>
       <c r="G13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H13">
-        <v>1.437</v>
+        <v>1.5</v>
       </c>
       <c r="I13" s="1">
-        <v>1.5</v>
+        <v>52.606</v>
       </c>
       <c r="J13">
-        <v>52.6065</v>
+        <v>1.54</v>
       </c>
       <c r="K13" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L13" s="1">
-        <v>54.00934</v>
-      </c>
-      <c r="M13" t="s">
-        <v>105</v>
-      </c>
-      <c r="N13">
+        <v>54.009</v>
+      </c>
+      <c r="L13" t="s">
+        <v>104</v>
+      </c>
+      <c r="M13">
         <v>0</v>
       </c>
-      <c r="O13" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+      <c r="N13" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F14">
         <v>53</v>
       </c>
       <c r="G14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H14">
-        <v>1.437</v>
+        <v>1.5</v>
       </c>
       <c r="I14" s="1">
-        <v>1.5</v>
+        <v>79.5</v>
       </c>
       <c r="J14">
-        <v>79.5</v>
+        <v>1.54</v>
       </c>
       <c r="K14" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L14" s="1">
         <v>81.62</v>
       </c>
-      <c r="M14" t="s">
-        <v>106</v>
-      </c>
-      <c r="N14">
+      <c r="L14" t="s">
+        <v>105</v>
+      </c>
+      <c r="M14">
         <v>0</v>
       </c>
-      <c r="O14" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+      <c r="N14" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F15">
         <v>22</v>
       </c>
       <c r="G15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H15">
-        <v>1.451</v>
+        <v>1.52</v>
       </c>
       <c r="I15" s="1">
-        <v>1.52</v>
+        <v>33.44</v>
       </c>
       <c r="J15">
-        <v>33.44</v>
+        <v>1.56</v>
       </c>
       <c r="K15" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L15" s="1">
         <v>34.32</v>
       </c>
-      <c r="M15" t="s">
-        <v>107</v>
-      </c>
-      <c r="N15">
+      <c r="L15" t="s">
+        <v>106</v>
+      </c>
+      <c r="M15">
         <v>0</v>
       </c>
-      <c r="O15" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+      <c r="N15" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F16">
         <v>51.007</v>
       </c>
       <c r="G16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H16">
-        <v>1.359</v>
+        <v>1.45</v>
       </c>
       <c r="I16" s="1">
-        <v>1.45</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="J16">
-        <v>73.96015</v>
+        <v>1.49</v>
       </c>
       <c r="K16" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="L16" s="1">
-        <v>76.00042999999999</v>
-      </c>
-      <c r="M16" t="s">
-        <v>108</v>
-      </c>
-      <c r="N16">
+        <v>76</v>
+      </c>
+      <c r="L16" t="s">
+        <v>107</v>
+      </c>
+      <c r="M16">
         <v>300520</v>
       </c>
-      <c r="O16" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15">
+      <c r="N16" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F17">
         <v>45.871</v>
       </c>
       <c r="G17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H17">
-        <v>1.469</v>
+        <v>1.51</v>
       </c>
       <c r="I17" s="1">
-        <v>1.51</v>
+        <v>69.265</v>
       </c>
       <c r="J17">
-        <v>69.26521</v>
+        <v>1.55</v>
       </c>
       <c r="K17" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L17" s="1">
-        <v>71.10005</v>
-      </c>
-      <c r="M17" t="s">
-        <v>109</v>
-      </c>
-      <c r="N17">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="L17" t="s">
+        <v>108</v>
+      </c>
+      <c r="M17">
         <v>0</v>
       </c>
-      <c r="O17" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15">
+      <c r="N17" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F18">
         <v>46.795</v>
       </c>
       <c r="G18" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H18">
-        <v>1.469</v>
+        <v>1.52</v>
       </c>
       <c r="I18" s="1">
-        <v>1.52</v>
+        <v>71.128</v>
       </c>
       <c r="J18">
-        <v>71.1284</v>
+        <v>1.56</v>
       </c>
       <c r="K18" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L18" s="1">
-        <v>73.00020000000001</v>
-      </c>
-      <c r="M18" t="s">
-        <v>110</v>
-      </c>
-      <c r="N18">
+        <v>73</v>
+      </c>
+      <c r="L18" t="s">
+        <v>109</v>
+      </c>
+      <c r="M18">
         <v>290630</v>
       </c>
-      <c r="O18" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15">
+      <c r="N18" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F19">
         <v>46.608</v>
       </c>
       <c r="G19" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H19">
-        <v>1.489</v>
+        <v>1.54</v>
       </c>
       <c r="I19" s="1">
-        <v>1.54</v>
+        <v>71.776</v>
       </c>
       <c r="J19">
-        <v>71.77632</v>
+        <v>1.58</v>
       </c>
       <c r="K19" s="1">
-        <v>1.58</v>
-      </c>
-      <c r="L19" s="1">
-        <v>73.64064</v>
-      </c>
-      <c r="M19" t="s">
-        <v>111</v>
-      </c>
-      <c r="N19">
+        <v>73.64100000000001</v>
+      </c>
+      <c r="L19" t="s">
+        <v>110</v>
+      </c>
+      <c r="M19">
         <v>264545</v>
       </c>
-      <c r="O19" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15">
+      <c r="N19" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D20" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F20">
         <v>51.943</v>
       </c>
       <c r="G20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H20">
-        <v>1.489</v>
+        <v>1.54</v>
       </c>
       <c r="I20" s="1">
-        <v>1.54</v>
+        <v>79.992</v>
       </c>
       <c r="J20">
-        <v>79.99222</v>
+        <v>1.58</v>
       </c>
       <c r="K20" s="1">
-        <v>1.58</v>
-      </c>
-      <c r="L20" s="1">
-        <v>82.06994</v>
-      </c>
-      <c r="M20" t="s">
-        <v>112</v>
-      </c>
-      <c r="N20">
+        <v>82.06999999999999</v>
+      </c>
+      <c r="L20" t="s">
+        <v>111</v>
+      </c>
+      <c r="M20">
         <v>41492</v>
       </c>
-      <c r="O20" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15">
+      <c r="N20" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C21" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E21" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F21">
         <v>46</v>
       </c>
       <c r="G21" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H21">
-        <v>1.499</v>
+        <v>1.57</v>
       </c>
       <c r="I21" s="1">
-        <v>1.57</v>
+        <v>72.22</v>
       </c>
       <c r="J21">
-        <v>72.22</v>
+        <v>1.61</v>
       </c>
       <c r="K21" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="L21" s="1">
         <v>74.06</v>
       </c>
-      <c r="M21" t="s">
-        <v>113</v>
-      </c>
-      <c r="N21">
+      <c r="L21" t="s">
+        <v>112</v>
+      </c>
+      <c r="M21">
         <v>259652</v>
       </c>
-      <c r="O21" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15">
+      <c r="N21" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D22" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E22" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F22">
         <v>43.307</v>
       </c>
       <c r="G22" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H22">
-        <v>1.369</v>
+        <v>1.46</v>
       </c>
       <c r="I22" s="1">
-        <v>1.46</v>
+        <v>63.228</v>
       </c>
       <c r="J22">
-        <v>63.22822</v>
+        <v>1.5</v>
       </c>
       <c r="K22" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L22" s="1">
-        <v>64.9605</v>
-      </c>
-      <c r="M22" t="s">
-        <v>114</v>
-      </c>
-      <c r="N22">
+        <v>64.95999999999999</v>
+      </c>
+      <c r="L22" t="s">
+        <v>113</v>
+      </c>
+      <c r="M22">
         <v>235382</v>
       </c>
-      <c r="O22" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15">
+      <c r="N22" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C23" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D23" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E23" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F23">
         <v>32</v>
       </c>
       <c r="G23" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H23">
-        <v>1.499</v>
+        <v>1.57</v>
       </c>
       <c r="I23" s="1">
-        <v>1.57</v>
+        <v>50.24</v>
       </c>
       <c r="J23">
-        <v>50.24</v>
+        <v>1.61</v>
       </c>
       <c r="K23" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="L23" s="1">
         <v>51.52</v>
       </c>
-      <c r="M23" t="s">
-        <v>99</v>
-      </c>
-      <c r="N23">
+      <c r="L23" t="s">
+        <v>98</v>
+      </c>
+      <c r="M23">
         <v>235791</v>
       </c>
-      <c r="O23" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15">
+      <c r="N23" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D24" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E24" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F24">
         <v>54.589</v>
       </c>
       <c r="G24" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H24">
-        <v>1.499</v>
+        <v>1.59</v>
       </c>
       <c r="I24" s="1">
-        <v>1.59</v>
+        <v>86.797</v>
       </c>
       <c r="J24">
-        <v>86.79651</v>
+        <v>1.63</v>
       </c>
       <c r="K24" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="L24" s="1">
-        <v>88.98007</v>
-      </c>
-      <c r="M24" t="s">
-        <v>115</v>
-      </c>
-      <c r="N24">
+        <v>88.98</v>
+      </c>
+      <c r="L24" t="s">
+        <v>114</v>
+      </c>
+      <c r="M24">
         <v>0</v>
       </c>
-      <c r="O24" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15">
+      <c r="N24" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C25" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F25">
         <v>39.393</v>
       </c>
       <c r="G25" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H25">
-        <v>1.546</v>
+        <v>1.64</v>
       </c>
       <c r="I25" s="1">
-        <v>1.64</v>
+        <v>64.605</v>
       </c>
       <c r="J25">
-        <v>64.60451999999999</v>
+        <v>1.68</v>
       </c>
       <c r="K25" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L25" s="1">
-        <v>66.18024</v>
-      </c>
-      <c r="M25" t="s">
-        <v>116</v>
-      </c>
-      <c r="N25">
+        <v>66.18000000000001</v>
+      </c>
+      <c r="L25" t="s">
+        <v>115</v>
+      </c>
+      <c r="M25">
         <v>0</v>
       </c>
-      <c r="O25" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15">
+      <c r="N25" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E26" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F26">
         <v>54.94</v>
       </c>
       <c r="G26" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H26">
-        <v>1.546</v>
+        <v>1.64</v>
       </c>
       <c r="I26" s="1">
-        <v>1.64</v>
+        <v>90.102</v>
       </c>
       <c r="J26">
-        <v>90.1016</v>
+        <v>1.68</v>
       </c>
       <c r="K26" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L26" s="1">
-        <v>92.2992</v>
-      </c>
-      <c r="M26" t="s">
-        <v>117</v>
-      </c>
-      <c r="N26">
+        <v>92.29900000000001</v>
+      </c>
+      <c r="L26" t="s">
+        <v>116</v>
+      </c>
+      <c r="M26">
         <v>285274</v>
       </c>
-      <c r="O26" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15">
+      <c r="N26" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E27" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F27">
         <v>19</v>
       </c>
       <c r="G27" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H27">
-        <v>1.389</v>
+        <v>1.49</v>
       </c>
       <c r="I27" s="1">
-        <v>1.49</v>
+        <v>28.31</v>
       </c>
       <c r="J27">
-        <v>28.31</v>
+        <v>1.53</v>
       </c>
       <c r="K27" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="L27" s="1">
         <v>29.07</v>
       </c>
-      <c r="M27" t="s">
-        <v>118</v>
-      </c>
-      <c r="N27">
+      <c r="L27" t="s">
+        <v>117</v>
+      </c>
+      <c r="M27">
         <v>0</v>
       </c>
-      <c r="O27" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15">
+      <c r="N27" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C28" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D28" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E28" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F28">
         <v>12</v>
       </c>
       <c r="G28" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H28">
-        <v>1.389</v>
+        <v>1.49</v>
       </c>
       <c r="I28" s="1">
-        <v>1.49</v>
+        <v>17.88</v>
       </c>
       <c r="J28">
-        <v>17.88</v>
+        <v>1.53</v>
       </c>
       <c r="K28" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="L28" s="1">
         <v>18.36</v>
       </c>
-      <c r="M28" t="s">
-        <v>119</v>
-      </c>
-      <c r="N28">
+      <c r="L28" t="s">
+        <v>118</v>
+      </c>
+      <c r="M28">
         <v>10270</v>
       </c>
-      <c r="O28" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15">
+      <c r="N28" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C29" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D29" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E29" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F29">
         <v>21.013</v>
       </c>
       <c r="G29" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H29">
-        <v>1.389</v>
+        <v>1.49</v>
       </c>
       <c r="I29" s="1">
-        <v>1.49</v>
+        <v>31.309</v>
       </c>
       <c r="J29">
-        <v>31.30937</v>
+        <v>1.53</v>
       </c>
       <c r="K29" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="L29" s="1">
-        <v>32.14989</v>
-      </c>
-      <c r="M29" t="s">
-        <v>120</v>
-      </c>
-      <c r="N29">
+        <v>32.15</v>
+      </c>
+      <c r="L29" t="s">
+        <v>119</v>
+      </c>
+      <c r="M29">
         <v>0</v>
       </c>
-      <c r="O29" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15">
+      <c r="N29" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
       <c r="A30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D30" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F30">
         <v>37</v>
       </c>
       <c r="G30" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H30">
-        <v>1.546</v>
+        <v>1.64</v>
       </c>
       <c r="I30" s="1">
+        <v>60.68</v>
+      </c>
+      <c r="J30">
+        <v>1.68</v>
+      </c>
+      <c r="K30" s="1">
+        <v>62.16</v>
+      </c>
+      <c r="L30" t="s">
+        <v>120</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" t="s">
+        <v>34</v>
+      </c>
+      <c r="C31" t="s">
+        <v>46</v>
+      </c>
+      <c r="D31" t="s">
+        <v>71</v>
+      </c>
+      <c r="E31" t="s">
+        <v>87</v>
+      </c>
+      <c r="F31">
+        <v>34</v>
+      </c>
+      <c r="G31" t="s">
+        <v>91</v>
+      </c>
+      <c r="H31">
         <v>1.64</v>
       </c>
-      <c r="J30">
-        <v>60.68</v>
-      </c>
-      <c r="K30" s="1">
+      <c r="I31" s="1">
+        <v>55.76</v>
+      </c>
+      <c r="J31">
         <v>1.68</v>
       </c>
-      <c r="L30" s="1">
-        <v>62.16</v>
-      </c>
-      <c r="M30" t="s">
+      <c r="K31" s="1">
+        <v>57.12</v>
+      </c>
+      <c r="L31" t="s">
         <v>121</v>
       </c>
-      <c r="N30">
-        <v>0</v>
-      </c>
-      <c r="O30" t="s">
+      <c r="M31">
+        <v>255860</v>
+      </c>
+      <c r="N31" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="31" spans="1:15">
-      <c r="A31" t="s">
-        <v>26</v>
-      </c>
-      <c r="B31" t="s">
-        <v>35</v>
-      </c>
-      <c r="C31" t="s">
-        <v>47</v>
-      </c>
-      <c r="D31" t="s">
-        <v>72</v>
-      </c>
-      <c r="E31" t="s">
-        <v>88</v>
-      </c>
-      <c r="F31">
-        <v>34</v>
-      </c>
-      <c r="G31" t="s">
-        <v>92</v>
-      </c>
-      <c r="H31">
-        <v>1.546</v>
-      </c>
-      <c r="I31" s="1">
-        <v>1.64</v>
-      </c>
-      <c r="J31">
-        <v>55.76</v>
-      </c>
-      <c r="K31" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L31" s="1">
-        <v>57.12</v>
-      </c>
-      <c r="M31" t="s">
-        <v>122</v>
-      </c>
-      <c r="N31">
-        <v>255860</v>
-      </c>
-      <c r="O31" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15">
+    <row r="32" spans="1:14">
       <c r="A32" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C32" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D32" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E32" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F32">
         <v>48</v>
       </c>
       <c r="G32" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H32">
-        <v>1.546</v>
+        <v>1.64</v>
       </c>
       <c r="I32" s="1">
-        <v>1.64</v>
+        <v>78.72</v>
       </c>
       <c r="J32">
-        <v>78.72</v>
+        <v>1.68</v>
       </c>
       <c r="K32" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L32" s="1">
         <v>80.64</v>
       </c>
-      <c r="M32" t="s">
-        <v>123</v>
-      </c>
-      <c r="N32">
+      <c r="L32" t="s">
+        <v>122</v>
+      </c>
+      <c r="M32">
         <v>27032</v>
       </c>
-      <c r="O32" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15">
+      <c r="N32" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B33" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C33" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D33" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E33" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F33">
         <v>69</v>
       </c>
       <c r="G33" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H33">
-        <v>1.564</v>
+        <v>1.62</v>
       </c>
       <c r="I33" s="1">
-        <v>1.62</v>
+        <v>111.78</v>
       </c>
       <c r="J33">
-        <v>111.78</v>
+        <v>1.66</v>
       </c>
       <c r="K33" s="1">
-        <v>1.66</v>
-      </c>
-      <c r="L33" s="1">
         <v>114.54</v>
       </c>
-      <c r="M33" t="s">
-        <v>100</v>
-      </c>
-      <c r="N33">
+      <c r="L33" t="s">
+        <v>99</v>
+      </c>
+      <c r="M33">
         <v>111100</v>
       </c>
-      <c r="O33" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15">
+      <c r="N33" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D34" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E34" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F34">
         <v>48.452</v>
       </c>
       <c r="G34" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H34">
-        <v>1.588</v>
+        <v>1.64</v>
       </c>
       <c r="I34" s="1">
-        <v>1.64</v>
+        <v>79.461</v>
       </c>
       <c r="J34">
-        <v>79.46128</v>
+        <v>1.68</v>
       </c>
       <c r="K34" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L34" s="1">
-        <v>81.39936</v>
-      </c>
-      <c r="M34" t="s">
-        <v>124</v>
-      </c>
-      <c r="N34">
+        <v>81.399</v>
+      </c>
+      <c r="L34" t="s">
+        <v>123</v>
+      </c>
+      <c r="M34">
         <v>41867</v>
       </c>
-      <c r="O34" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15">
+      <c r="N34" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
       <c r="A35" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C35" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D35" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E35" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F35">
         <v>17</v>
       </c>
       <c r="G35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H35">
-        <v>1.401</v>
+        <v>1.48</v>
       </c>
       <c r="I35" s="1">
-        <v>1.48</v>
+        <v>25.16</v>
       </c>
       <c r="J35">
-        <v>25.16</v>
+        <v>1.52</v>
       </c>
       <c r="K35" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L35" s="1">
         <v>25.84</v>
       </c>
-      <c r="M35" t="s">
-        <v>125</v>
-      </c>
-      <c r="N35">
+      <c r="L35" t="s">
+        <v>124</v>
+      </c>
+      <c r="M35">
         <v>75620</v>
       </c>
-      <c r="O35" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15">
+      <c r="N35" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
       <c r="A36" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B36" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C36" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E36" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F36">
         <v>25</v>
       </c>
       <c r="G36" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H36">
-        <v>1.401</v>
+        <v>1.48</v>
       </c>
       <c r="I36" s="1">
-        <v>1.48</v>
+        <v>37</v>
       </c>
       <c r="J36">
+        <v>1.52</v>
+      </c>
+      <c r="K36" s="1">
+        <v>38</v>
+      </c>
+      <c r="L36" t="s">
+        <v>125</v>
+      </c>
+      <c r="M36">
+        <v>10450</v>
+      </c>
+      <c r="N36" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" t="s">
+        <v>28</v>
+      </c>
+      <c r="B37" t="s">
+        <v>34</v>
+      </c>
+      <c r="C37" t="s">
         <v>37</v>
       </c>
-      <c r="K36" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L36" s="1">
-        <v>38</v>
-      </c>
-      <c r="M36" t="s">
-        <v>126</v>
-      </c>
-      <c r="N36">
-        <v>10450</v>
-      </c>
-      <c r="O36" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15">
-      <c r="A37" t="s">
-        <v>29</v>
-      </c>
-      <c r="B37" t="s">
-        <v>35</v>
-      </c>
-      <c r="C37" t="s">
-        <v>38</v>
-      </c>
       <c r="D37" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E37" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F37">
         <v>49.601</v>
       </c>
       <c r="G37" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H37">
-        <v>1.588</v>
+        <v>1.64</v>
       </c>
       <c r="I37" s="1">
-        <v>1.64</v>
+        <v>81.346</v>
       </c>
       <c r="J37">
-        <v>81.34564</v>
+        <v>1.68</v>
       </c>
       <c r="K37" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L37" s="1">
-        <v>83.32968</v>
-      </c>
-      <c r="M37" t="s">
-        <v>127</v>
-      </c>
-      <c r="N37">
+        <v>83.33</v>
+      </c>
+      <c r="L37" t="s">
+        <v>126</v>
+      </c>
+      <c r="M37">
         <v>0</v>
       </c>
-      <c r="O37" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15">
+      <c r="N37" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
       <c r="A38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C38" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D38" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E38" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F38">
         <v>16.013</v>
       </c>
       <c r="G38" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H38">
-        <v>1.401</v>
+        <v>1.48</v>
       </c>
       <c r="I38" s="1">
-        <v>1.48</v>
+        <v>23.699</v>
       </c>
       <c r="J38">
-        <v>23.69924</v>
+        <v>1.52</v>
       </c>
       <c r="K38" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L38" s="1">
-        <v>24.33976</v>
-      </c>
-      <c r="M38" t="s">
-        <v>128</v>
-      </c>
-      <c r="N38">
+        <v>24.34</v>
+      </c>
+      <c r="L38" t="s">
+        <v>127</v>
+      </c>
+      <c r="M38">
         <v>133320</v>
       </c>
-      <c r="O38" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15">
+      <c r="N38" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
       <c r="A39" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C39" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D39" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E39" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F39">
         <v>49</v>
       </c>
       <c r="G39" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H39">
-        <v>1.588</v>
+        <v>1.64</v>
       </c>
       <c r="I39" s="1">
-        <v>1.64</v>
+        <v>80.36</v>
       </c>
       <c r="J39">
-        <v>80.36</v>
+        <v>1.68</v>
       </c>
       <c r="K39" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L39" s="1">
         <v>82.31999999999999</v>
       </c>
-      <c r="M39" t="s">
-        <v>129</v>
-      </c>
-      <c r="N39">
+      <c r="L39" t="s">
+        <v>128</v>
+      </c>
+      <c r="M39">
         <v>0</v>
       </c>
-      <c r="O39" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15">
+      <c r="N39" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
       <c r="A40" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B40" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D40" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E40" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F40">
         <v>31</v>
       </c>
       <c r="G40" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H40">
-        <v>1.401</v>
+        <v>1.49</v>
       </c>
       <c r="I40" s="1">
-        <v>1.49</v>
+        <v>46.19</v>
       </c>
       <c r="J40">
-        <v>46.19</v>
+        <v>1.53</v>
       </c>
       <c r="K40" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="L40" s="1">
         <v>47.43</v>
       </c>
-      <c r="M40" t="s">
-        <v>130</v>
-      </c>
-      <c r="N40">
+      <c r="L40" t="s">
+        <v>129</v>
+      </c>
+      <c r="M40">
         <v>7535</v>
       </c>
-      <c r="O40" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15">
+      <c r="N40" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
       <c r="A41" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B41" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C41" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D41" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E41" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F41">
         <v>43</v>
       </c>
       <c r="G41" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H41">
-        <v>1.649</v>
+        <v>1.74</v>
       </c>
       <c r="I41" s="1">
-        <v>1.74</v>
+        <v>74.81999999999999</v>
       </c>
       <c r="J41">
-        <v>74.81999999999999</v>
+        <v>1.79</v>
       </c>
       <c r="K41" s="1">
-        <v>1.79</v>
-      </c>
-      <c r="L41" s="1">
         <v>76.97</v>
       </c>
-      <c r="M41" t="s">
-        <v>131</v>
-      </c>
-      <c r="N41">
+      <c r="L41" t="s">
+        <v>130</v>
+      </c>
+      <c r="M41">
         <v>182918</v>
       </c>
-      <c r="O41" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15">
+      <c r="N41" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
       <c r="A42" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D42" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E42" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F42">
         <v>65</v>
       </c>
       <c r="G42" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H42">
-        <v>1.619</v>
+        <v>1.66</v>
       </c>
       <c r="I42" s="1">
-        <v>1.66</v>
+        <v>107.9</v>
       </c>
       <c r="J42">
-        <v>107.9</v>
+        <v>1.7</v>
       </c>
       <c r="K42" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="L42" s="1">
         <v>110.5</v>
       </c>
-      <c r="M42" t="s">
-        <v>108</v>
-      </c>
-      <c r="N42">
+      <c r="L42" t="s">
+        <v>107</v>
+      </c>
+      <c r="M42">
         <v>286990</v>
       </c>
-      <c r="O42" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15">
+      <c r="N42" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
       <c r="A43" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B43" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D43" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E43" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F43">
         <v>29.069</v>
       </c>
       <c r="G43" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H43">
-        <v>1.619</v>
+        <v>1.7</v>
       </c>
       <c r="I43" s="1">
-        <v>1.7</v>
+        <v>49.417</v>
       </c>
       <c r="J43">
-        <v>49.4173</v>
+        <v>1.74</v>
       </c>
       <c r="K43" s="1">
-        <v>1.74</v>
-      </c>
-      <c r="L43" s="1">
-        <v>50.58006</v>
-      </c>
-      <c r="M43" t="s">
-        <v>132</v>
-      </c>
-      <c r="N43">
+        <v>50.58</v>
+      </c>
+      <c r="L43" t="s">
+        <v>131</v>
+      </c>
+      <c r="M43">
         <v>256160</v>
       </c>
-      <c r="O43" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15">
+      <c r="N43" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
       <c r="A44" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C44" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D44" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E44" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F44">
         <v>31.51</v>
       </c>
       <c r="G44" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H44">
-        <v>1.401</v>
+        <v>1.51</v>
       </c>
       <c r="I44" s="1">
-        <v>1.51</v>
+        <v>47.58</v>
       </c>
       <c r="J44">
-        <v>47.5801</v>
+        <v>1.55</v>
       </c>
       <c r="K44" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L44" s="1">
-        <v>48.8405</v>
-      </c>
-      <c r="M44" t="s">
-        <v>133</v>
-      </c>
-      <c r="N44">
+        <v>48.841</v>
+      </c>
+      <c r="L44" t="s">
+        <v>132</v>
+      </c>
+      <c r="M44">
         <v>235832</v>
       </c>
-      <c r="O44" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15">
+      <c r="N44" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
       <c r="A45" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B45" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C45" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D45" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E45" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F45">
         <v>40</v>
       </c>
       <c r="G45" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H45">
-        <v>1.441</v>
+        <v>1.51</v>
       </c>
       <c r="I45" s="1">
-        <v>1.51</v>
+        <v>60.4</v>
       </c>
       <c r="J45">
-        <v>60.4</v>
+        <v>1.55</v>
       </c>
       <c r="K45" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L45" s="1">
         <v>62</v>
       </c>
-      <c r="M45" t="s">
-        <v>134</v>
-      </c>
-      <c r="N45">
+      <c r="L45" t="s">
+        <v>133</v>
+      </c>
+      <c r="M45">
         <v>300950</v>
       </c>
-      <c r="O45" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15">
+      <c r="N45" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
       <c r="A46" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B46" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C46" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D46" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E46" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F46">
         <v>48.103</v>
       </c>
       <c r="G46" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H46">
-        <v>1.653</v>
+        <v>1.7</v>
       </c>
       <c r="I46" s="1">
-        <v>1.7</v>
+        <v>81.77500000000001</v>
       </c>
       <c r="J46">
-        <v>81.77509999999999</v>
+        <v>1.74</v>
       </c>
       <c r="K46" s="1">
-        <v>1.74</v>
-      </c>
-      <c r="L46" s="1">
-        <v>83.69922</v>
-      </c>
-      <c r="M46" t="s">
-        <v>135</v>
-      </c>
-      <c r="N46">
+        <v>83.699</v>
+      </c>
+      <c r="L46" t="s">
+        <v>134</v>
+      </c>
+      <c r="M46">
         <v>285933</v>
       </c>
-      <c r="O46" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15">
+      <c r="N46" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
       <c r="A47" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C47" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D47" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E47" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F47">
         <v>55</v>
       </c>
       <c r="G47" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H47">
-        <v>1.653</v>
+        <v>1.7</v>
       </c>
       <c r="I47" s="1">
-        <v>1.7</v>
+        <v>93.5</v>
       </c>
       <c r="J47">
-        <v>93.5</v>
+        <v>1.74</v>
       </c>
       <c r="K47" s="1">
-        <v>1.74</v>
-      </c>
-      <c r="L47" s="1">
         <v>95.7</v>
       </c>
-      <c r="M47" t="s">
-        <v>136</v>
-      </c>
-      <c r="N47">
+      <c r="L47" t="s">
+        <v>135</v>
+      </c>
+      <c r="M47">
         <v>0</v>
       </c>
-      <c r="O47" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15">
+      <c r="N47" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
       <c r="A48" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B48" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C48" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D48" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E48" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F48">
         <v>46.149</v>
       </c>
       <c r="G48" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H48">
-        <v>1.674</v>
+        <v>1.7</v>
       </c>
       <c r="I48" s="1">
-        <v>1.7</v>
+        <v>78.453</v>
       </c>
       <c r="J48">
-        <v>78.4533</v>
+        <v>1.74</v>
       </c>
       <c r="K48" s="1">
-        <v>1.74</v>
-      </c>
-      <c r="L48" s="1">
-        <v>80.29926</v>
-      </c>
-      <c r="M48" t="s">
-        <v>137</v>
-      </c>
-      <c r="N48">
+        <v>80.29900000000001</v>
+      </c>
+      <c r="L48" t="s">
+        <v>136</v>
+      </c>
+      <c r="M48">
         <v>291490</v>
       </c>
-      <c r="O48" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15">
+      <c r="N48" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14">
       <c r="A49" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B49" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C49" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D49" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E49" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F49">
         <v>25.013</v>
       </c>
       <c r="G49" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H49">
-        <v>1.449</v>
+        <v>1.5</v>
       </c>
       <c r="I49" s="1">
-        <v>1.5</v>
+        <v>37.52</v>
       </c>
       <c r="J49">
-        <v>37.5195</v>
+        <v>1.54</v>
       </c>
       <c r="K49" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L49" s="1">
-        <v>38.52002</v>
-      </c>
-      <c r="M49" t="s">
-        <v>138</v>
-      </c>
-      <c r="N49">
+        <v>38.52</v>
+      </c>
+      <c r="L49" t="s">
+        <v>137</v>
+      </c>
+      <c r="M49">
         <v>327070</v>
       </c>
-      <c r="O49" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15">
+      <c r="N49" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14">
       <c r="A50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C50" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D50" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E50" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F50">
         <v>51.851</v>
       </c>
       <c r="G50" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H50">
-        <v>1.674</v>
+        <v>1.7</v>
       </c>
       <c r="I50" s="1">
-        <v>1.7</v>
+        <v>88.14700000000001</v>
       </c>
       <c r="J50">
-        <v>88.1467</v>
+        <v>1.74</v>
       </c>
       <c r="K50" s="1">
-        <v>1.74</v>
-      </c>
-      <c r="L50" s="1">
-        <v>90.22074000000001</v>
-      </c>
-      <c r="M50" t="s">
-        <v>139</v>
-      </c>
-      <c r="N50">
+        <v>90.221</v>
+      </c>
+      <c r="L50" t="s">
+        <v>138</v>
+      </c>
+      <c r="M50">
         <v>42235</v>
       </c>
-      <c r="O50" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15">
+      <c r="N50" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14">
       <c r="A51" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B51" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C51" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D51" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E51" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F51">
         <v>30</v>
       </c>
       <c r="G51" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H51">
-        <v>1.689</v>
+        <v>1.73</v>
       </c>
       <c r="I51" s="1">
-        <v>1.73</v>
+        <v>51.9</v>
       </c>
       <c r="J51">
-        <v>51.9</v>
+        <v>1.77</v>
       </c>
       <c r="K51" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L51" s="1">
         <v>53.1</v>
       </c>
-      <c r="M51" t="s">
-        <v>140</v>
-      </c>
-      <c r="N51">
+      <c r="L51" t="s">
+        <v>139</v>
+      </c>
+      <c r="M51">
         <v>287420</v>
       </c>
-      <c r="O51" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15">
+      <c r="N51" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14">
       <c r="A52" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C52" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D52" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E52" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F52">
         <v>54.831</v>
       </c>
       <c r="G52" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H52">
-        <v>1.689</v>
+        <v>1.73</v>
       </c>
       <c r="I52" s="1">
-        <v>1.73</v>
+        <v>94.858</v>
       </c>
       <c r="J52">
-        <v>94.85763</v>
+        <v>1.77</v>
       </c>
       <c r="K52" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L52" s="1">
-        <v>97.05087</v>
-      </c>
-      <c r="M52" t="s">
-        <v>141</v>
-      </c>
-      <c r="N52">
+        <v>97.051</v>
+      </c>
+      <c r="L52" t="s">
+        <v>140</v>
+      </c>
+      <c r="M52">
         <v>265247</v>
       </c>
-      <c r="O52" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15">
+      <c r="N52" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14">
       <c r="A53" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C53" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D53" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E53" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F53">
         <v>39</v>
       </c>
       <c r="G53" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H53">
-        <v>1.689</v>
+        <v>1.73</v>
       </c>
       <c r="I53" s="1">
-        <v>1.73</v>
+        <v>67.47</v>
       </c>
       <c r="J53">
-        <v>67.47</v>
+        <v>1.77</v>
       </c>
       <c r="K53" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L53" s="1">
         <v>69.03</v>
       </c>
-      <c r="M53" t="s">
-        <v>142</v>
-      </c>
-      <c r="N53">
+      <c r="L53" t="s">
+        <v>141</v>
+      </c>
+      <c r="M53">
         <v>260190</v>
       </c>
-      <c r="O53" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15">
+      <c r="N53" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14">
       <c r="A54" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B54" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C54" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D54" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E54" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F54">
         <v>27</v>
       </c>
       <c r="G54" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H54">
-        <v>1.459</v>
+        <v>1.5</v>
       </c>
       <c r="I54" s="1">
-        <v>1.5</v>
+        <v>40.5</v>
       </c>
       <c r="J54">
-        <v>40.5</v>
+        <v>1.54</v>
       </c>
       <c r="K54" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L54" s="1">
         <v>41.58</v>
       </c>
-      <c r="M54" t="s">
-        <v>127</v>
-      </c>
-      <c r="N54">
+      <c r="L54" t="s">
+        <v>126</v>
+      </c>
+      <c r="M54">
         <v>327405</v>
       </c>
-      <c r="O54" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15">
+      <c r="N54" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14">
       <c r="A55" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B55" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C55" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D55" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E55" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F55">
         <v>14</v>
       </c>
       <c r="G55" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H55">
-        <v>1.689</v>
+        <v>1.73</v>
       </c>
       <c r="I55" s="1">
-        <v>1.73</v>
+        <v>24.22</v>
       </c>
       <c r="J55">
-        <v>24.22</v>
+        <v>1.77</v>
       </c>
       <c r="K55" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L55" s="1">
         <v>24.78</v>
       </c>
-      <c r="M55" t="s">
-        <v>143</v>
-      </c>
-      <c r="N55">
+      <c r="L55" t="s">
+        <v>142</v>
+      </c>
+      <c r="M55">
         <v>291780</v>
       </c>
-      <c r="O55" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15">
+      <c r="N55" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14">
       <c r="A56" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B56" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C56" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D56" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E56" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F56">
         <v>22</v>
       </c>
       <c r="G56" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H56">
-        <v>1.459</v>
+        <v>1.5</v>
       </c>
       <c r="I56" s="1">
-        <v>1.5</v>
+        <v>33</v>
       </c>
       <c r="J56">
+        <v>1.54</v>
+      </c>
+      <c r="K56" s="1">
+        <v>33.88</v>
+      </c>
+      <c r="L56" t="s">
+        <v>143</v>
+      </c>
+      <c r="M56">
+        <v>21275</v>
+      </c>
+      <c r="N56" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14">
+      <c r="A57" t="s">
         <v>33</v>
       </c>
-      <c r="K56" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L56" s="1">
-        <v>33.88</v>
-      </c>
-      <c r="M56" t="s">
-        <v>144</v>
-      </c>
-      <c r="N56">
-        <v>21275</v>
-      </c>
-      <c r="O56" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15">
-      <c r="A57" t="s">
-        <v>34</v>
-      </c>
       <c r="B57" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C57" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D57" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E57" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F57">
         <v>38.559</v>
       </c>
       <c r="G57" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H57">
-        <v>1.689</v>
+        <v>1.73</v>
       </c>
       <c r="I57" s="1">
-        <v>1.73</v>
+        <v>66.70699999999999</v>
       </c>
       <c r="J57">
-        <v>66.70707</v>
+        <v>1.77</v>
       </c>
       <c r="K57" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L57" s="1">
-        <v>68.24943</v>
-      </c>
-      <c r="M57" t="s">
-        <v>145</v>
-      </c>
-      <c r="N57">
+        <v>68.249</v>
+      </c>
+      <c r="L57" t="s">
+        <v>144</v>
+      </c>
+      <c r="M57">
         <v>0</v>
       </c>
-      <c r="O57" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15">
+      <c r="N57" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14">
       <c r="A58" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B58" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C58" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D58" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E58" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F58">
         <v>24.362</v>
       </c>
       <c r="G58" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H58">
-        <v>1.689</v>
+        <v>1.73</v>
       </c>
       <c r="I58" s="1">
-        <v>1.73</v>
+        <v>42.146</v>
       </c>
       <c r="J58">
-        <v>42.14626</v>
+        <v>1.77</v>
       </c>
       <c r="K58" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L58" s="1">
-        <v>43.12074</v>
-      </c>
-      <c r="M58" t="s">
-        <v>146</v>
-      </c>
-      <c r="N58">
+        <v>43.121</v>
+      </c>
+      <c r="L58" t="s">
+        <v>145</v>
+      </c>
+      <c r="M58">
         <v>0</v>
       </c>
-      <c r="O58" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15">
+      <c r="N58" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14">
       <c r="A59" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B59" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C59" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D59" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E59" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F59">
         <v>16</v>
       </c>
       <c r="G59" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H59">
-        <v>1.689</v>
+        <v>1.73</v>
       </c>
       <c r="I59" s="1">
-        <v>1.73</v>
+        <v>27.68</v>
       </c>
       <c r="J59">
-        <v>27.68</v>
+        <v>1.77</v>
       </c>
       <c r="K59" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L59" s="1">
         <v>28.32</v>
       </c>
-      <c r="M59" t="s">
-        <v>147</v>
-      </c>
-      <c r="N59">
+      <c r="L59" t="s">
+        <v>146</v>
+      </c>
+      <c r="M59">
         <v>256400</v>
       </c>
-      <c r="O59" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15">
+      <c r="N59" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14">
       <c r="A60" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B60" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C60" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D60" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E60" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F60">
         <v>27.006</v>
       </c>
       <c r="G60" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H60">
-        <v>1.689</v>
+        <v>1.73</v>
       </c>
       <c r="I60" s="1">
-        <v>1.73</v>
+        <v>46.72</v>
       </c>
       <c r="J60">
-        <v>46.72038</v>
+        <v>1.77</v>
       </c>
       <c r="K60" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L60" s="1">
-        <v>47.80062</v>
-      </c>
-      <c r="M60" t="s">
-        <v>116</v>
-      </c>
-      <c r="N60">
+        <v>47.801</v>
+      </c>
+      <c r="L60" t="s">
+        <v>115</v>
+      </c>
+      <c r="M60">
         <v>268295</v>
       </c>
-      <c r="O60" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15">
+      <c r="N60" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14">
       <c r="A61" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C61" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D61" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E61" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F61">
         <v>29.011</v>
       </c>
       <c r="G61" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H61">
-        <v>1.689</v>
+        <v>1.73</v>
       </c>
       <c r="I61" s="1">
-        <v>1.73</v>
+        <v>50.189</v>
       </c>
       <c r="J61">
-        <v>50.18903</v>
+        <v>1.77</v>
       </c>
       <c r="K61" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L61" s="1">
-        <v>51.34947</v>
-      </c>
-      <c r="M61" t="s">
-        <v>148</v>
-      </c>
-      <c r="N61">
+        <v>51.349</v>
+      </c>
+      <c r="L61" t="s">
+        <v>147</v>
+      </c>
+      <c r="M61">
         <v>0</v>
       </c>
-      <c r="O61" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15">
+      <c r="N61" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14">
       <c r="A62" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B62" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C62" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D62" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E62" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F62">
         <v>37.006</v>
       </c>
       <c r="G62" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H62">
-        <v>1.689</v>
+        <v>1.73</v>
       </c>
       <c r="I62" s="1">
-        <v>1.73</v>
+        <v>64.02</v>
       </c>
       <c r="J62">
-        <v>64.02038</v>
+        <v>1.77</v>
       </c>
       <c r="K62" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L62" s="1">
-        <v>65.50062</v>
-      </c>
-      <c r="M62" t="s">
-        <v>133</v>
-      </c>
-      <c r="N62">
+        <v>65.501</v>
+      </c>
+      <c r="L62" t="s">
+        <v>132</v>
+      </c>
+      <c r="M62">
         <v>111500</v>
       </c>
-      <c r="O62" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15">
+      <c r="N62" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14">
       <c r="A63" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B63" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C63" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D63" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E63" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F63">
         <v>22.011</v>
       </c>
       <c r="G63" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H63">
-        <v>1.689</v>
+        <v>1.73</v>
       </c>
       <c r="I63" s="1">
-        <v>1.73</v>
+        <v>38.079</v>
       </c>
       <c r="J63">
-        <v>38.07903</v>
+        <v>1.77</v>
       </c>
       <c r="K63" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L63" s="1">
-        <v>38.95947</v>
-      </c>
-      <c r="M63" t="s">
-        <v>105</v>
-      </c>
-      <c r="N63">
+        <v>38.959</v>
+      </c>
+      <c r="L63" t="s">
+        <v>104</v>
+      </c>
+      <c r="M63">
         <v>42399</v>
       </c>
-      <c r="O63" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15">
+      <c r="N63" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14">
       <c r="A64" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B64" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C64" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D64" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E64" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F64">
         <v>1</v>
       </c>
       <c r="G64" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H64">
         <v>24.99</v>
@@ -4111,275 +3919,257 @@
       <c r="K64" s="1">
         <v>24.99</v>
       </c>
-      <c r="L64" s="1">
-        <v>24.99</v>
-      </c>
-      <c r="M64" t="s">
-        <v>105</v>
-      </c>
-      <c r="N64">
+      <c r="L64" t="s">
+        <v>104</v>
+      </c>
+      <c r="M64">
         <v>42399</v>
       </c>
-      <c r="O64" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="65" spans="1:15">
+      <c r="N64" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14">
       <c r="A65" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B65" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C65" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D65" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E65" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F65">
         <v>6</v>
       </c>
       <c r="G65" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H65">
-        <v>1.459</v>
+        <v>1.5</v>
       </c>
       <c r="I65" s="1">
-        <v>1.5</v>
+        <v>9</v>
       </c>
       <c r="J65">
-        <v>9</v>
+        <v>1.54</v>
       </c>
       <c r="K65" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L65" s="1">
         <v>9.24</v>
       </c>
-      <c r="M65" t="s">
-        <v>149</v>
-      </c>
-      <c r="N65">
+      <c r="L65" t="s">
+        <v>148</v>
+      </c>
+      <c r="M65">
         <v>75676</v>
       </c>
-      <c r="O65" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="66" spans="1:15">
+      <c r="N65" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14">
       <c r="A66" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B66" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C66" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D66" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E66" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F66">
         <v>18</v>
       </c>
       <c r="G66" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H66">
-        <v>1.459</v>
+        <v>1.5</v>
       </c>
       <c r="I66" s="1">
-        <v>1.5</v>
+        <v>27</v>
       </c>
       <c r="J66">
-        <v>27</v>
+        <v>1.54</v>
       </c>
       <c r="K66" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L66" s="1">
         <v>27.72</v>
       </c>
-      <c r="M66" t="s">
-        <v>150</v>
-      </c>
-      <c r="N66">
+      <c r="L66" t="s">
+        <v>149</v>
+      </c>
+      <c r="M66">
         <v>301160</v>
       </c>
-      <c r="O66" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="67" spans="1:15">
+      <c r="N66" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14">
       <c r="A67" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B67" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C67" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D67" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E67" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F67">
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H67">
-        <v>1.459</v>
+        <v>1.5</v>
       </c>
       <c r="I67" s="1">
-        <v>1.5</v>
+        <v>22.5</v>
       </c>
       <c r="J67">
-        <v>22.5</v>
+        <v>1.54</v>
       </c>
       <c r="K67" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L67" s="1">
         <v>23.1</v>
       </c>
-      <c r="M67" t="s">
-        <v>151</v>
-      </c>
-      <c r="N67">
+      <c r="L67" t="s">
+        <v>150</v>
+      </c>
+      <c r="M67">
         <v>7755</v>
       </c>
-      <c r="O67" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="68" spans="1:15">
+      <c r="N67" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14">
       <c r="A68" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B68" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C68" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D68" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E68" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F68">
         <v>29.774</v>
       </c>
       <c r="G68" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H68">
-        <v>1.689</v>
+        <v>1.73</v>
       </c>
       <c r="I68" s="1">
-        <v>1.73</v>
+        <v>51.509</v>
       </c>
       <c r="J68">
-        <v>51.50902</v>
+        <v>1.77</v>
       </c>
       <c r="K68" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L68" s="1">
-        <v>52.69998</v>
-      </c>
-      <c r="M68" t="s">
-        <v>112</v>
-      </c>
-      <c r="N68">
+        <v>52.7</v>
+      </c>
+      <c r="L68" t="s">
+        <v>111</v>
+      </c>
+      <c r="M68">
         <v>236251</v>
       </c>
-      <c r="O68" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="69" spans="1:15">
+      <c r="N68" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14">
       <c r="A69" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B69" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C69" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D69" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E69" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F69">
         <v>29</v>
       </c>
       <c r="G69" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H69">
-        <v>1.689</v>
+        <v>1.73</v>
       </c>
       <c r="I69" s="1">
-        <v>1.73</v>
+        <v>50.17</v>
       </c>
       <c r="J69">
-        <v>50.17</v>
+        <v>1.77</v>
       </c>
       <c r="K69" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L69" s="1">
         <v>51.33</v>
       </c>
-      <c r="M69" t="s">
-        <v>152</v>
-      </c>
-      <c r="N69">
+      <c r="L69" t="s">
+        <v>151</v>
+      </c>
+      <c r="M69">
         <v>27540</v>
       </c>
-      <c r="O69" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="70" spans="1:15">
+      <c r="N69" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14">
       <c r="A70" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B70" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C70" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D70" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E70" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F70">
         <v>1</v>
       </c>
       <c r="G70" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H70">
         <v>14.99</v>
@@ -4393,69 +4183,63 @@
       <c r="K70" s="1">
         <v>14.99</v>
       </c>
-      <c r="L70" s="1">
-        <v>14.99</v>
-      </c>
-      <c r="M70" t="s">
-        <v>152</v>
-      </c>
-      <c r="N70">
+      <c r="L70" t="s">
+        <v>151</v>
+      </c>
+      <c r="M70">
         <v>27540</v>
       </c>
-      <c r="O70" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="71" spans="1:15">
+      <c r="N70" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14">
       <c r="A71" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B71" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C71" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D71" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E71" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F71">
         <v>17.633</v>
       </c>
       <c r="G71" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H71">
-        <v>1.689</v>
+        <v>1.73</v>
       </c>
       <c r="I71" s="1">
-        <v>1.73</v>
+        <v>30.505</v>
       </c>
       <c r="J71">
-        <v>30.50509</v>
+        <v>1.77</v>
       </c>
       <c r="K71" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L71" s="1">
-        <v>31.21041</v>
-      </c>
-      <c r="M71" t="s">
-        <v>153</v>
-      </c>
-      <c r="N71">
+        <v>31.21</v>
+      </c>
+      <c r="L71" t="s">
+        <v>152</v>
+      </c>
+      <c r="M71">
         <v>0</v>
       </c>
-      <c r="O71" t="s">
+      <c r="N71" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14">
+      <c r="A74" s="3" t="s">
         <v>221</v>
-      </c>
-    </row>
-    <row r="74" spans="1:15">
-      <c r="A74" s="3" t="s">
-        <v>222</v>
       </c>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
@@ -4463,129 +4247,129 @@
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
     </row>
-    <row r="75" spans="1:15">
+    <row r="75" spans="1:14">
       <c r="A75" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="B75" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="B75" s="4" t="s">
+      <c r="C75" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="C75" s="4" t="s">
+      <c r="D75" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="D75" s="4" t="s">
-        <v>226</v>
-      </c>
       <c r="E75" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="76" spans="1:15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14">
       <c r="A76" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B76" s="6">
         <v>1817.022</v>
       </c>
-      <c r="C76" s="6">
+      <c r="C76" s="7">
         <v>45</v>
       </c>
       <c r="D76" s="7">
-        <v>1.621598</v>
-      </c>
-      <c r="E76" s="6">
-        <v>2946.48</v>
-      </c>
-      <c r="F76" s="6">
-        <v>3019.16</v>
-      </c>
-    </row>
-    <row r="77" spans="1:15">
+        <v>1.622</v>
+      </c>
+      <c r="E76" s="7">
+        <v>2946.479</v>
+      </c>
+      <c r="F76" s="7">
+        <v>3019.158</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14">
       <c r="A77" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B77" s="6">
         <v>518.5700000000001</v>
       </c>
-      <c r="C77" s="6">
+      <c r="C77" s="7">
         <v>21</v>
       </c>
       <c r="D77" s="7">
-        <v>1.480743</v>
-      </c>
-      <c r="E77" s="6">
-        <v>767.87</v>
-      </c>
-      <c r="F77" s="6">
-        <v>788.61</v>
-      </c>
-    </row>
-    <row r="78" spans="1:15">
+        <v>1.481</v>
+      </c>
+      <c r="E77" s="7">
+        <v>767.8680000000001</v>
+      </c>
+      <c r="F77" s="7">
+        <v>788.611</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14">
       <c r="A78" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B78" s="6">
+        <v>87</v>
+      </c>
+      <c r="C78" s="7">
+        <v>2</v>
+      </c>
+      <c r="D78" s="7">
+        <v>1.72</v>
+      </c>
+      <c r="E78" s="7">
+        <v>149.62</v>
+      </c>
+      <c r="F78" s="7">
+        <v>153.97</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14">
+      <c r="A79" s="5" t="s">
         <v>89</v>
-      </c>
-      <c r="B78" s="6">
-        <v>87</v>
-      </c>
-      <c r="C78" s="6">
-        <v>2</v>
-      </c>
-      <c r="D78" s="7">
-        <v>1.71977</v>
-      </c>
-      <c r="E78" s="6">
-        <v>149.62</v>
-      </c>
-      <c r="F78" s="6">
-        <v>153.97</v>
-      </c>
-    </row>
-    <row r="79" spans="1:15">
-      <c r="A79" s="5" t="s">
-        <v>90</v>
       </c>
       <c r="B79" s="6">
         <v>1</v>
       </c>
-      <c r="C79" s="6">
+      <c r="C79" s="7">
         <v>1</v>
       </c>
       <c r="D79" s="7">
         <v>24.99</v>
       </c>
-      <c r="E79" s="6">
+      <c r="E79" s="7">
         <v>24.99</v>
       </c>
-      <c r="F79" s="6">
+      <c r="F79" s="7">
         <v>24.99</v>
       </c>
     </row>
-    <row r="80" spans="1:15">
+    <row r="80" spans="1:14">
       <c r="A80" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B80" s="6">
         <v>1</v>
       </c>
-      <c r="C80" s="6">
+      <c r="C80" s="7">
         <v>1</v>
       </c>
       <c r="D80" s="7">
         <v>14.99</v>
       </c>
-      <c r="E80" s="6">
+      <c r="E80" s="7">
         <v>14.99</v>
       </c>
-      <c r="F80" s="6">
+      <c r="F80" s="7">
         <v>14.99</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B81" s="9">
         <v>2424.592</v>
@@ -4595,10 +4379,10 @@
       </c>
       <c r="D81" s="7"/>
       <c r="E81" s="9">
-        <v>3903.95</v>
+        <v>3903.947</v>
       </c>
       <c r="F81" s="9">
-        <v>4001.72</v>
+        <v>4001.719</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ДОБРИЧКА/ОБЩИНА ДОБРИЧКА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ДОБРИЧКА/ОБЩИНА ДОБРИЧКА.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\SPLIT_COMPANY_DATA\RESULT\companies_result\ОБЩИНА ДОБРИЧКА\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02250130-3143-440E-8BD4-742DA725C735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ОБЩИНА ДОБРИЧКА" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="227">
   <si>
     <t>Дата</t>
   </si>
@@ -700,12 +706,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.000"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -789,30 +794,38 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -850,7 +863,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -884,6 +897,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -918,9 +932,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1093,9 +1108,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N81"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
     <col min="2" max="2" width="18.7109375" customWidth="1"/>
@@ -1113,7 +1128,7 @@
     <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1157,7 +1172,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1183,7 +1198,7 @@
         <v>1.46</v>
       </c>
       <c r="I2" s="1">
-        <v>49.377</v>
+        <v>49.377000000000002</v>
       </c>
       <c r="J2">
         <v>1.5</v>
@@ -1201,7 +1216,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -1218,7 +1233,7 @@
         <v>87</v>
       </c>
       <c r="F3">
-        <v>49.349</v>
+        <v>49.348999999999997</v>
       </c>
       <c r="G3" t="s">
         <v>91</v>
@@ -1227,13 +1242,13 @@
         <v>1.48</v>
       </c>
       <c r="I3" s="1">
-        <v>73.03700000000001</v>
+        <v>73.037000000000006</v>
       </c>
       <c r="J3">
         <v>1.52</v>
       </c>
       <c r="K3" s="1">
-        <v>75.01000000000001</v>
+        <v>75.010000000000005</v>
       </c>
       <c r="L3" t="s">
         <v>94</v>
@@ -1245,7 +1260,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -1271,7 +1286,7 @@
         <v>1.46</v>
       </c>
       <c r="I4" s="1">
-        <v>24.655</v>
+        <v>24.655000000000001</v>
       </c>
       <c r="J4">
         <v>1.5</v>
@@ -1289,7 +1304,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -1306,7 +1321,7 @@
         <v>87</v>
       </c>
       <c r="F5">
-        <v>45.461</v>
+        <v>45.460999999999999</v>
       </c>
       <c r="G5" t="s">
         <v>91</v>
@@ -1315,13 +1330,13 @@
         <v>1.48</v>
       </c>
       <c r="I5" s="1">
-        <v>67.282</v>
+        <v>67.281999999999996</v>
       </c>
       <c r="J5">
         <v>1.52</v>
       </c>
       <c r="K5" s="1">
-        <v>69.101</v>
+        <v>69.100999999999999</v>
       </c>
       <c r="L5" t="s">
         <v>96</v>
@@ -1333,7 +1348,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -1377,7 +1392,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -1403,7 +1418,7 @@
         <v>1.48</v>
       </c>
       <c r="I7" s="1">
-        <v>35.297</v>
+        <v>35.296999999999997</v>
       </c>
       <c r="J7">
         <v>1.52</v>
@@ -1421,7 +1436,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -1465,7 +1480,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -1491,7 +1506,7 @@
         <v>1.45</v>
       </c>
       <c r="I9" s="1">
-        <v>37.7</v>
+        <v>37.700000000000003</v>
       </c>
       <c r="J9">
         <v>1.49</v>
@@ -1509,7 +1524,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -1526,7 +1541,7 @@
         <v>87</v>
       </c>
       <c r="F10">
-        <v>53.112</v>
+        <v>53.112000000000002</v>
       </c>
       <c r="G10" t="s">
         <v>91</v>
@@ -1535,7 +1550,7 @@
         <v>1.48</v>
       </c>
       <c r="I10" s="1">
-        <v>78.60599999999999</v>
+        <v>78.605999999999995</v>
       </c>
       <c r="J10">
         <v>1.52</v>
@@ -1553,7 +1568,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1597,7 +1612,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -1614,7 +1629,7 @@
         <v>87</v>
       </c>
       <c r="F12">
-        <v>37.623</v>
+        <v>37.622999999999998</v>
       </c>
       <c r="G12" t="s">
         <v>91</v>
@@ -1623,7 +1638,7 @@
         <v>1.5</v>
       </c>
       <c r="I12" s="1">
-        <v>56.434</v>
+        <v>56.433999999999997</v>
       </c>
       <c r="J12">
         <v>1.54</v>
@@ -1641,7 +1656,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -1658,7 +1673,7 @@
         <v>87</v>
       </c>
       <c r="F13">
-        <v>35.071</v>
+        <v>35.070999999999998</v>
       </c>
       <c r="G13" t="s">
         <v>91</v>
@@ -1667,7 +1682,7 @@
         <v>1.5</v>
       </c>
       <c r="I13" s="1">
-        <v>52.606</v>
+        <v>52.606000000000002</v>
       </c>
       <c r="J13">
         <v>1.54</v>
@@ -1685,7 +1700,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -1729,7 +1744,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -1773,7 +1788,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -1790,7 +1805,7 @@
         <v>86</v>
       </c>
       <c r="F16">
-        <v>51.007</v>
+        <v>51.006999999999998</v>
       </c>
       <c r="G16" t="s">
         <v>91</v>
@@ -1799,7 +1814,7 @@
         <v>1.45</v>
       </c>
       <c r="I16" s="1">
-        <v>73.95999999999999</v>
+        <v>73.959999999999994</v>
       </c>
       <c r="J16">
         <v>1.49</v>
@@ -1817,7 +1832,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -1834,7 +1849,7 @@
         <v>87</v>
       </c>
       <c r="F17">
-        <v>45.871</v>
+        <v>45.871000000000002</v>
       </c>
       <c r="G17" t="s">
         <v>91</v>
@@ -1843,13 +1858,13 @@
         <v>1.51</v>
       </c>
       <c r="I17" s="1">
-        <v>69.265</v>
+        <v>69.265000000000001</v>
       </c>
       <c r="J17">
         <v>1.55</v>
       </c>
       <c r="K17" s="1">
-        <v>71.09999999999999</v>
+        <v>71.099999999999994</v>
       </c>
       <c r="L17" t="s">
         <v>108</v>
@@ -1861,7 +1876,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -1878,7 +1893,7 @@
         <v>87</v>
       </c>
       <c r="F18">
-        <v>46.795</v>
+        <v>46.795000000000002</v>
       </c>
       <c r="G18" t="s">
         <v>91</v>
@@ -1905,7 +1920,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -1922,7 +1937,7 @@
         <v>87</v>
       </c>
       <c r="F19">
-        <v>46.608</v>
+        <v>46.607999999999997</v>
       </c>
       <c r="G19" t="s">
         <v>91</v>
@@ -1931,13 +1946,13 @@
         <v>1.54</v>
       </c>
       <c r="I19" s="1">
-        <v>71.776</v>
+        <v>71.775999999999996</v>
       </c>
       <c r="J19">
         <v>1.58</v>
       </c>
       <c r="K19" s="1">
-        <v>73.64100000000001</v>
+        <v>73.641000000000005</v>
       </c>
       <c r="L19" t="s">
         <v>110</v>
@@ -1949,7 +1964,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -1966,7 +1981,7 @@
         <v>87</v>
       </c>
       <c r="F20">
-        <v>51.943</v>
+        <v>51.942999999999998</v>
       </c>
       <c r="G20" t="s">
         <v>91</v>
@@ -1975,13 +1990,13 @@
         <v>1.54</v>
       </c>
       <c r="I20" s="1">
-        <v>79.992</v>
+        <v>79.992000000000004</v>
       </c>
       <c r="J20">
         <v>1.58</v>
       </c>
       <c r="K20" s="1">
-        <v>82.06999999999999</v>
+        <v>82.07</v>
       </c>
       <c r="L20" t="s">
         <v>111</v>
@@ -1993,7 +2008,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -2037,7 +2052,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -2054,7 +2069,7 @@
         <v>86</v>
       </c>
       <c r="F22">
-        <v>43.307</v>
+        <v>43.307000000000002</v>
       </c>
       <c r="G22" t="s">
         <v>91</v>
@@ -2063,13 +2078,13 @@
         <v>1.46</v>
       </c>
       <c r="I22" s="1">
-        <v>63.228</v>
+        <v>63.228000000000002</v>
       </c>
       <c r="J22">
         <v>1.5</v>
       </c>
       <c r="K22" s="1">
-        <v>64.95999999999999</v>
+        <v>64.959999999999994</v>
       </c>
       <c r="L22" t="s">
         <v>113</v>
@@ -2081,7 +2096,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -2125,7 +2140,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -2142,7 +2157,7 @@
         <v>87</v>
       </c>
       <c r="F24">
-        <v>54.589</v>
+        <v>54.588999999999999</v>
       </c>
       <c r="G24" t="s">
         <v>91</v>
@@ -2151,7 +2166,7 @@
         <v>1.59</v>
       </c>
       <c r="I24" s="1">
-        <v>86.797</v>
+        <v>86.796999999999997</v>
       </c>
       <c r="J24">
         <v>1.63</v>
@@ -2169,7 +2184,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -2186,7 +2201,7 @@
         <v>87</v>
       </c>
       <c r="F25">
-        <v>39.393</v>
+        <v>39.393000000000001</v>
       </c>
       <c r="G25" t="s">
         <v>91</v>
@@ -2195,13 +2210,13 @@
         <v>1.64</v>
       </c>
       <c r="I25" s="1">
-        <v>64.605</v>
+        <v>64.605000000000004</v>
       </c>
       <c r="J25">
         <v>1.68</v>
       </c>
       <c r="K25" s="1">
-        <v>66.18000000000001</v>
+        <v>66.180000000000007</v>
       </c>
       <c r="L25" t="s">
         <v>115</v>
@@ -2213,7 +2228,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -2239,13 +2254,13 @@
         <v>1.64</v>
       </c>
       <c r="I26" s="1">
-        <v>90.102</v>
+        <v>90.102000000000004</v>
       </c>
       <c r="J26">
         <v>1.68</v>
       </c>
       <c r="K26" s="1">
-        <v>92.29900000000001</v>
+        <v>92.299000000000007</v>
       </c>
       <c r="L26" t="s">
         <v>116</v>
@@ -2257,7 +2272,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -2301,7 +2316,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="28" spans="1:14">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>25</v>
       </c>
@@ -2345,7 +2360,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="29" spans="1:14">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>25</v>
       </c>
@@ -2362,7 +2377,7 @@
         <v>86</v>
       </c>
       <c r="F29">
-        <v>21.013</v>
+        <v>21.013000000000002</v>
       </c>
       <c r="G29" t="s">
         <v>91</v>
@@ -2371,7 +2386,7 @@
         <v>1.49</v>
       </c>
       <c r="I29" s="1">
-        <v>31.309</v>
+        <v>31.309000000000001</v>
       </c>
       <c r="J29">
         <v>1.53</v>
@@ -2389,7 +2404,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="30" spans="1:14">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>25</v>
       </c>
@@ -2433,7 +2448,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="31" spans="1:14">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>25</v>
       </c>
@@ -2477,7 +2492,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="32" spans="1:14">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>25</v>
       </c>
@@ -2521,7 +2536,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="33" spans="1:14">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>26</v>
       </c>
@@ -2565,7 +2580,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="34" spans="1:14">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>27</v>
       </c>
@@ -2582,7 +2597,7 @@
         <v>87</v>
       </c>
       <c r="F34">
-        <v>48.452</v>
+        <v>48.451999999999998</v>
       </c>
       <c r="G34" t="s">
         <v>91</v>
@@ -2591,13 +2606,13 @@
         <v>1.64</v>
       </c>
       <c r="I34" s="1">
-        <v>79.461</v>
+        <v>79.460999999999999</v>
       </c>
       <c r="J34">
         <v>1.68</v>
       </c>
       <c r="K34" s="1">
-        <v>81.399</v>
+        <v>81.399000000000001</v>
       </c>
       <c r="L34" t="s">
         <v>123</v>
@@ -2609,7 +2624,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="35" spans="1:14">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>27</v>
       </c>
@@ -2653,7 +2668,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="36" spans="1:14">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>28</v>
       </c>
@@ -2697,7 +2712,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="37" spans="1:14">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>28</v>
       </c>
@@ -2714,7 +2729,7 @@
         <v>87</v>
       </c>
       <c r="F37">
-        <v>49.601</v>
+        <v>49.600999999999999</v>
       </c>
       <c r="G37" t="s">
         <v>91</v>
@@ -2723,7 +2738,7 @@
         <v>1.64</v>
       </c>
       <c r="I37" s="1">
-        <v>81.346</v>
+        <v>81.346000000000004</v>
       </c>
       <c r="J37">
         <v>1.68</v>
@@ -2741,7 +2756,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="38" spans="1:14">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>28</v>
       </c>
@@ -2758,7 +2773,7 @@
         <v>86</v>
       </c>
       <c r="F38">
-        <v>16.013</v>
+        <v>16.013000000000002</v>
       </c>
       <c r="G38" t="s">
         <v>91</v>
@@ -2767,7 +2782,7 @@
         <v>1.48</v>
       </c>
       <c r="I38" s="1">
-        <v>23.699</v>
+        <v>23.699000000000002</v>
       </c>
       <c r="J38">
         <v>1.52</v>
@@ -2785,7 +2800,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="39" spans="1:14">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>28</v>
       </c>
@@ -2817,7 +2832,7 @@
         <v>1.68</v>
       </c>
       <c r="K39" s="1">
-        <v>82.31999999999999</v>
+        <v>82.32</v>
       </c>
       <c r="L39" t="s">
         <v>128</v>
@@ -2829,7 +2844,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="40" spans="1:14">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>29</v>
       </c>
@@ -2873,7 +2888,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="41" spans="1:14">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>29</v>
       </c>
@@ -2899,7 +2914,7 @@
         <v>1.74</v>
       </c>
       <c r="I41" s="1">
-        <v>74.81999999999999</v>
+        <v>74.819999999999993</v>
       </c>
       <c r="J41">
         <v>1.79</v>
@@ -2917,7 +2932,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="42" spans="1:14">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>29</v>
       </c>
@@ -2961,7 +2976,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="43" spans="1:14">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>30</v>
       </c>
@@ -2978,7 +2993,7 @@
         <v>87</v>
       </c>
       <c r="F43">
-        <v>29.069</v>
+        <v>29.068999999999999</v>
       </c>
       <c r="G43" t="s">
         <v>91</v>
@@ -2987,7 +3002,7 @@
         <v>1.7</v>
       </c>
       <c r="I43" s="1">
-        <v>49.417</v>
+        <v>49.417000000000002</v>
       </c>
       <c r="J43">
         <v>1.74</v>
@@ -3005,7 +3020,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="44" spans="1:14">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>30</v>
       </c>
@@ -3037,7 +3052,7 @@
         <v>1.55</v>
       </c>
       <c r="K44" s="1">
-        <v>48.841</v>
+        <v>48.841000000000001</v>
       </c>
       <c r="L44" t="s">
         <v>132</v>
@@ -3049,7 +3064,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="45" spans="1:14">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>31</v>
       </c>
@@ -3093,7 +3108,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="46" spans="1:14">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>31</v>
       </c>
@@ -3110,7 +3125,7 @@
         <v>87</v>
       </c>
       <c r="F46">
-        <v>48.103</v>
+        <v>48.103000000000002</v>
       </c>
       <c r="G46" t="s">
         <v>91</v>
@@ -3119,13 +3134,13 @@
         <v>1.7</v>
       </c>
       <c r="I46" s="1">
-        <v>81.77500000000001</v>
+        <v>81.775000000000006</v>
       </c>
       <c r="J46">
         <v>1.74</v>
       </c>
       <c r="K46" s="1">
-        <v>83.699</v>
+        <v>83.698999999999998</v>
       </c>
       <c r="L46" t="s">
         <v>134</v>
@@ -3137,7 +3152,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="47" spans="1:14">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>31</v>
       </c>
@@ -3181,7 +3196,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="48" spans="1:14">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>32</v>
       </c>
@@ -3198,7 +3213,7 @@
         <v>87</v>
       </c>
       <c r="F48">
-        <v>46.149</v>
+        <v>46.149000000000001</v>
       </c>
       <c r="G48" t="s">
         <v>91</v>
@@ -3207,13 +3222,13 @@
         <v>1.7</v>
       </c>
       <c r="I48" s="1">
-        <v>78.453</v>
+        <v>78.453000000000003</v>
       </c>
       <c r="J48">
         <v>1.74</v>
       </c>
       <c r="K48" s="1">
-        <v>80.29900000000001</v>
+        <v>80.299000000000007</v>
       </c>
       <c r="L48" t="s">
         <v>136</v>
@@ -3225,7 +3240,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="49" spans="1:14">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>32</v>
       </c>
@@ -3242,7 +3257,7 @@
         <v>86</v>
       </c>
       <c r="F49">
-        <v>25.013</v>
+        <v>25.013000000000002</v>
       </c>
       <c r="G49" t="s">
         <v>91</v>
@@ -3251,13 +3266,13 @@
         <v>1.5</v>
       </c>
       <c r="I49" s="1">
-        <v>37.52</v>
+        <v>37.520000000000003</v>
       </c>
       <c r="J49">
         <v>1.54</v>
       </c>
       <c r="K49" s="1">
-        <v>38.52</v>
+        <v>38.520000000000003</v>
       </c>
       <c r="L49" t="s">
         <v>137</v>
@@ -3269,7 +3284,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="50" spans="1:14">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>32</v>
       </c>
@@ -3286,7 +3301,7 @@
         <v>87</v>
       </c>
       <c r="F50">
-        <v>51.851</v>
+        <v>51.850999999999999</v>
       </c>
       <c r="G50" t="s">
         <v>91</v>
@@ -3295,13 +3310,13 @@
         <v>1.7</v>
       </c>
       <c r="I50" s="1">
-        <v>88.14700000000001</v>
+        <v>88.147000000000006</v>
       </c>
       <c r="J50">
         <v>1.74</v>
       </c>
       <c r="K50" s="1">
-        <v>90.221</v>
+        <v>90.221000000000004</v>
       </c>
       <c r="L50" t="s">
         <v>138</v>
@@ -3313,7 +3328,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="51" spans="1:14">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>33</v>
       </c>
@@ -3357,7 +3372,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="52" spans="1:14">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>33</v>
       </c>
@@ -3374,7 +3389,7 @@
         <v>87</v>
       </c>
       <c r="F52">
-        <v>54.831</v>
+        <v>54.831000000000003</v>
       </c>
       <c r="G52" t="s">
         <v>91</v>
@@ -3383,13 +3398,13 @@
         <v>1.73</v>
       </c>
       <c r="I52" s="1">
-        <v>94.858</v>
+        <v>94.858000000000004</v>
       </c>
       <c r="J52">
         <v>1.77</v>
       </c>
       <c r="K52" s="1">
-        <v>97.051</v>
+        <v>97.051000000000002</v>
       </c>
       <c r="L52" t="s">
         <v>140</v>
@@ -3401,7 +3416,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="53" spans="1:14">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>33</v>
       </c>
@@ -3445,7 +3460,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="54" spans="1:14">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>33</v>
       </c>
@@ -3489,7 +3504,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="55" spans="1:14">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>33</v>
       </c>
@@ -3533,7 +3548,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="56" spans="1:14">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>33</v>
       </c>
@@ -3565,7 +3580,7 @@
         <v>1.54</v>
       </c>
       <c r="K56" s="1">
-        <v>33.88</v>
+        <v>33.880000000000003</v>
       </c>
       <c r="L56" t="s">
         <v>143</v>
@@ -3577,7 +3592,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="57" spans="1:14">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>33</v>
       </c>
@@ -3594,7 +3609,7 @@
         <v>87</v>
       </c>
       <c r="F57">
-        <v>38.559</v>
+        <v>38.558999999999997</v>
       </c>
       <c r="G57" t="s">
         <v>91</v>
@@ -3603,13 +3618,13 @@
         <v>1.73</v>
       </c>
       <c r="I57" s="1">
-        <v>66.70699999999999</v>
+        <v>66.706999999999994</v>
       </c>
       <c r="J57">
         <v>1.77</v>
       </c>
       <c r="K57" s="1">
-        <v>68.249</v>
+        <v>68.248999999999995</v>
       </c>
       <c r="L57" t="s">
         <v>144</v>
@@ -3621,7 +3636,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="58" spans="1:14">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>33</v>
       </c>
@@ -3638,7 +3653,7 @@
         <v>87</v>
       </c>
       <c r="F58">
-        <v>24.362</v>
+        <v>24.361999999999998</v>
       </c>
       <c r="G58" t="s">
         <v>91</v>
@@ -3647,13 +3662,13 @@
         <v>1.73</v>
       </c>
       <c r="I58" s="1">
-        <v>42.146</v>
+        <v>42.146000000000001</v>
       </c>
       <c r="J58">
         <v>1.77</v>
       </c>
       <c r="K58" s="1">
-        <v>43.121</v>
+        <v>43.121000000000002</v>
       </c>
       <c r="L58" t="s">
         <v>145</v>
@@ -3665,7 +3680,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="59" spans="1:14">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>33</v>
       </c>
@@ -3709,7 +3724,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="60" spans="1:14">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>33</v>
       </c>
@@ -3741,7 +3756,7 @@
         <v>1.77</v>
       </c>
       <c r="K60" s="1">
-        <v>47.801</v>
+        <v>47.801000000000002</v>
       </c>
       <c r="L60" t="s">
         <v>115</v>
@@ -3753,7 +3768,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="61" spans="1:14">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>33</v>
       </c>
@@ -3770,7 +3785,7 @@
         <v>87</v>
       </c>
       <c r="F61">
-        <v>29.011</v>
+        <v>29.010999999999999</v>
       </c>
       <c r="G61" t="s">
         <v>91</v>
@@ -3785,7 +3800,7 @@
         <v>1.77</v>
       </c>
       <c r="K61" s="1">
-        <v>51.349</v>
+        <v>51.348999999999997</v>
       </c>
       <c r="L61" t="s">
         <v>147</v>
@@ -3797,7 +3812,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="62" spans="1:14">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>33</v>
       </c>
@@ -3829,7 +3844,7 @@
         <v>1.77</v>
       </c>
       <c r="K62" s="1">
-        <v>65.501</v>
+        <v>65.501000000000005</v>
       </c>
       <c r="L62" t="s">
         <v>132</v>
@@ -3841,7 +3856,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="63" spans="1:14">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>33</v>
       </c>
@@ -3858,7 +3873,7 @@
         <v>87</v>
       </c>
       <c r="F63">
-        <v>22.011</v>
+        <v>22.010999999999999</v>
       </c>
       <c r="G63" t="s">
         <v>91</v>
@@ -3867,13 +3882,13 @@
         <v>1.73</v>
       </c>
       <c r="I63" s="1">
-        <v>38.079</v>
+        <v>38.079000000000001</v>
       </c>
       <c r="J63">
         <v>1.77</v>
       </c>
       <c r="K63" s="1">
-        <v>38.959</v>
+        <v>38.959000000000003</v>
       </c>
       <c r="L63" t="s">
         <v>104</v>
@@ -3885,7 +3900,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="64" spans="1:14">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>33</v>
       </c>
@@ -3929,7 +3944,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="65" spans="1:14">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>33</v>
       </c>
@@ -3973,7 +3988,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="66" spans="1:14">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>33</v>
       </c>
@@ -4017,7 +4032,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="67" spans="1:14">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>33</v>
       </c>
@@ -4061,7 +4076,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="68" spans="1:14">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>33</v>
       </c>
@@ -4078,7 +4093,7 @@
         <v>87</v>
       </c>
       <c r="F68">
-        <v>29.774</v>
+        <v>29.774000000000001</v>
       </c>
       <c r="G68" t="s">
         <v>91</v>
@@ -4105,7 +4120,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="69" spans="1:14">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>33</v>
       </c>
@@ -4149,7 +4164,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="70" spans="1:14">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>33</v>
       </c>
@@ -4193,7 +4208,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="71" spans="1:14">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>33</v>
       </c>
@@ -4210,7 +4225,7 @@
         <v>87</v>
       </c>
       <c r="F71">
-        <v>17.633</v>
+        <v>17.632999999999999</v>
       </c>
       <c r="G71" t="s">
         <v>91</v>
@@ -4219,7 +4234,7 @@
         <v>1.73</v>
       </c>
       <c r="I71" s="1">
-        <v>30.505</v>
+        <v>30.504999999999999</v>
       </c>
       <c r="J71">
         <v>1.77</v>
@@ -4237,152 +4252,152 @@
         <v>220</v>
       </c>
     </row>
-    <row r="74" spans="1:14">
-      <c r="A74" s="3" t="s">
+    <row r="74" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A74" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="B74" s="3"/>
-      <c r="C74" s="3"/>
-      <c r="D74" s="3"/>
-      <c r="E74" s="3"/>
-      <c r="F74" s="3"/>
-    </row>
-    <row r="75" spans="1:14">
-      <c r="A75" s="4" t="s">
+      <c r="B74" s="9"/>
+      <c r="C74" s="9"/>
+      <c r="D74" s="9"/>
+      <c r="E74" s="9"/>
+      <c r="F74" s="9"/>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="B75" s="4" t="s">
+      <c r="B75" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="C75" s="4" t="s">
+      <c r="C75" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="D75" s="4" t="s">
+      <c r="D75" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="E75" s="4" t="s">
+      <c r="E75" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F75" s="4" t="s">
+      <c r="F75" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="76" spans="1:14">
-      <c r="A76" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="B76" s="6">
-        <v>1817.022</v>
-      </c>
-      <c r="C76" s="7">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A76" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B76" s="5">
+        <v>1817.0219999999999</v>
+      </c>
+      <c r="C76" s="6">
         <v>45</v>
       </c>
-      <c r="D76" s="7">
-        <v>1.622</v>
-      </c>
-      <c r="E76" s="7">
-        <v>2946.479</v>
-      </c>
-      <c r="F76" s="7">
-        <v>3019.158</v>
-      </c>
-    </row>
-    <row r="77" spans="1:14">
-      <c r="A77" s="5" t="s">
+      <c r="D76" s="6">
+        <v>1.6220000000000001</v>
+      </c>
+      <c r="E76" s="6">
+        <v>2946.4789999999998</v>
+      </c>
+      <c r="F76" s="6">
+        <v>3019.1579999999999</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A77" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="B77" s="6">
-        <v>518.5700000000001</v>
-      </c>
-      <c r="C77" s="7">
+      <c r="B77" s="5">
+        <v>518.57000000000005</v>
+      </c>
+      <c r="C77" s="6">
         <v>21</v>
       </c>
-      <c r="D77" s="7">
-        <v>1.481</v>
-      </c>
-      <c r="E77" s="7">
-        <v>767.8680000000001</v>
-      </c>
-      <c r="F77" s="7">
-        <v>788.611</v>
-      </c>
-    </row>
-    <row r="78" spans="1:14">
-      <c r="A78" s="5" t="s">
+      <c r="D77" s="6">
+        <v>1.4810000000000001</v>
+      </c>
+      <c r="E77" s="6">
+        <v>767.86800000000005</v>
+      </c>
+      <c r="F77" s="6">
+        <v>788.61099999999999</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A78" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B78" s="6">
-        <v>87</v>
-      </c>
-      <c r="C78" s="7">
+      <c r="B78" s="5">
+        <v>87</v>
+      </c>
+      <c r="C78" s="6">
         <v>2</v>
       </c>
-      <c r="D78" s="7">
+      <c r="D78" s="6">
         <v>1.72</v>
       </c>
-      <c r="E78" s="7">
+      <c r="E78" s="6">
         <v>149.62</v>
       </c>
-      <c r="F78" s="7">
+      <c r="F78" s="6">
         <v>153.97</v>
       </c>
     </row>
-    <row r="79" spans="1:14">
-      <c r="A79" s="5" t="s">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A79" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B79" s="6">
+      <c r="B79" s="5">
         <v>1</v>
       </c>
-      <c r="C79" s="7">
+      <c r="C79" s="6">
         <v>1</v>
       </c>
-      <c r="D79" s="7">
+      <c r="D79" s="6">
         <v>24.99</v>
       </c>
-      <c r="E79" s="7">
+      <c r="E79" s="6">
         <v>24.99</v>
       </c>
-      <c r="F79" s="7">
+      <c r="F79" s="6">
         <v>24.99</v>
       </c>
     </row>
-    <row r="80" spans="1:14">
-      <c r="A80" s="5" t="s">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A80" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B80" s="6">
+      <c r="B80" s="5">
         <v>1</v>
       </c>
-      <c r="C80" s="7">
+      <c r="C80" s="6">
         <v>1</v>
       </c>
-      <c r="D80" s="7">
+      <c r="D80" s="6">
         <v>14.99</v>
       </c>
-      <c r="E80" s="7">
+      <c r="E80" s="6">
         <v>14.99</v>
       </c>
-      <c r="F80" s="7">
+      <c r="F80" s="6">
         <v>14.99</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
-      <c r="A81" s="8" t="s">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="B81" s="9">
-        <v>2424.592</v>
-      </c>
-      <c r="C81" s="9">
+      <c r="B81" s="8">
+        <v>2424.5920000000001</v>
+      </c>
+      <c r="C81" s="8">
         <v>70</v>
       </c>
-      <c r="D81" s="7"/>
-      <c r="E81" s="9">
-        <v>3903.947</v>
-      </c>
-      <c r="F81" s="9">
-        <v>4001.719</v>
+      <c r="D81" s="6"/>
+      <c r="E81" s="8">
+        <v>3903.9470000000001</v>
+      </c>
+      <c r="F81" s="8">
+        <v>4001.7190000000001</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ДОБРИЧКА/ОБЩИНА ДОБРИЧКА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ДОБРИЧКА/ОБЩИНА ДОБРИЧКА.xlsx
@@ -928,10 +928,10 @@
         <v>64</v>
       </c>
       <c r="H2" s="1">
-        <v>1.659</v>
+        <v>1.74</v>
       </c>
       <c r="I2" s="1">
-        <v>43.781</v>
+        <v>45.919</v>
       </c>
       <c r="J2" s="1">
         <v>1.78</v>
@@ -972,10 +972,10 @@
         <v>64</v>
       </c>
       <c r="H3" s="1">
-        <v>1.419</v>
+        <v>1.5</v>
       </c>
       <c r="I3" s="1">
-        <v>35.489</v>
+        <v>37.515</v>
       </c>
       <c r="J3" s="1">
         <v>1.54</v>
@@ -1016,10 +1016,10 @@
         <v>64</v>
       </c>
       <c r="H4" s="1">
-        <v>1.667</v>
+        <v>1.75</v>
       </c>
       <c r="I4" s="1">
-        <v>88.351</v>
+        <v>92.75</v>
       </c>
       <c r="J4" s="1">
         <v>1.79</v>
@@ -1060,10 +1060,10 @@
         <v>64</v>
       </c>
       <c r="H5" s="1">
-        <v>1.409</v>
+        <v>1.5</v>
       </c>
       <c r="I5" s="1">
-        <v>40.861</v>
+        <v>43.5</v>
       </c>
       <c r="J5" s="1">
         <v>1.54</v>
@@ -1104,10 +1104,10 @@
         <v>64</v>
       </c>
       <c r="H6" s="1">
-        <v>1.653</v>
+        <v>1.75</v>
       </c>
       <c r="I6" s="1">
-        <v>90.13800000000001</v>
+        <v>95.428</v>
       </c>
       <c r="J6" s="1">
         <v>1.79</v>
@@ -1148,10 +1148,10 @@
         <v>64</v>
       </c>
       <c r="H7" s="1">
-        <v>1.634</v>
+        <v>1.75</v>
       </c>
       <c r="I7" s="1">
-        <v>88.00700000000001</v>
+        <v>94.255</v>
       </c>
       <c r="J7" s="1">
         <v>1.79</v>
@@ -1192,10 +1192,10 @@
         <v>64</v>
       </c>
       <c r="H8" s="1">
-        <v>1.636</v>
+        <v>1.76</v>
       </c>
       <c r="I8" s="1">
-        <v>60.532</v>
+        <v>65.12</v>
       </c>
       <c r="J8" s="1">
         <v>1.81</v>
@@ -1236,10 +1236,10 @@
         <v>64</v>
       </c>
       <c r="H9" s="1">
-        <v>1.634</v>
+        <v>1.74</v>
       </c>
       <c r="I9" s="1">
-        <v>53.955</v>
+        <v>57.455</v>
       </c>
       <c r="J9" s="1">
         <v>1.78</v>
@@ -1280,10 +1280,10 @@
         <v>64</v>
       </c>
       <c r="H10" s="1">
-        <v>1.399</v>
+        <v>1.51</v>
       </c>
       <c r="I10" s="1">
-        <v>44.782</v>
+        <v>48.335</v>
       </c>
       <c r="J10" s="1">
         <v>1.55</v>
@@ -1324,10 +1324,10 @@
         <v>64</v>
       </c>
       <c r="H11" s="1">
-        <v>1.667</v>
+        <v>1.75</v>
       </c>
       <c r="I11" s="1">
-        <v>78.33199999999999</v>
+        <v>82.232</v>
       </c>
       <c r="J11" s="1">
         <v>1.79</v>
@@ -1368,10 +1368,10 @@
         <v>64</v>
       </c>
       <c r="H12" s="1">
-        <v>1.667</v>
+        <v>1.75</v>
       </c>
       <c r="I12" s="1">
-        <v>88.351</v>
+        <v>92.75</v>
       </c>
       <c r="J12" s="1">
         <v>1.79</v>
@@ -1412,10 +1412,10 @@
         <v>64</v>
       </c>
       <c r="H13" s="1">
-        <v>1.419</v>
+        <v>1.51</v>
       </c>
       <c r="I13" s="1">
-        <v>32.637</v>
+        <v>34.73</v>
       </c>
       <c r="J13" s="1">
         <v>1.55</v>
@@ -1456,10 +1456,10 @@
         <v>64</v>
       </c>
       <c r="H14" s="1">
-        <v>1.419</v>
+        <v>1.51</v>
       </c>
       <c r="I14" s="1">
-        <v>15.609</v>
+        <v>16.61</v>
       </c>
       <c r="J14" s="1">
         <v>1.55</v>
@@ -1500,10 +1500,10 @@
         <v>64</v>
       </c>
       <c r="H15" s="1">
-        <v>1.419</v>
+        <v>1.51</v>
       </c>
       <c r="I15" s="1">
-        <v>61.684</v>
+        <v>65.64</v>
       </c>
       <c r="J15" s="1">
         <v>1.55</v>
@@ -1544,10 +1544,10 @@
         <v>64</v>
       </c>
       <c r="H16" s="1">
-        <v>1.419</v>
+        <v>1.52</v>
       </c>
       <c r="I16" s="1">
-        <v>24.123</v>
+        <v>25.84</v>
       </c>
       <c r="J16" s="1">
         <v>1.56</v>
@@ -1588,10 +1588,10 @@
         <v>64</v>
       </c>
       <c r="H17" s="1">
-        <v>1.646</v>
+        <v>1.77</v>
       </c>
       <c r="I17" s="1">
-        <v>59.272</v>
+        <v>63.738</v>
       </c>
       <c r="J17" s="1">
         <v>1.82</v>
@@ -1632,10 +1632,10 @@
         <v>64</v>
       </c>
       <c r="H18" s="1">
-        <v>1.679</v>
+        <v>1.79</v>
       </c>
       <c r="I18" s="1">
-        <v>64.658</v>
+        <v>68.93300000000001</v>
       </c>
       <c r="J18" s="1">
         <v>1.83</v>
@@ -1676,10 +1676,10 @@
         <v>64</v>
       </c>
       <c r="H19" s="1">
-        <v>1.679</v>
+        <v>1.79</v>
       </c>
       <c r="I19" s="1">
-        <v>83.967</v>
+        <v>89.518</v>
       </c>
       <c r="J19" s="1">
         <v>1.83</v>
@@ -1720,10 +1720,10 @@
         <v>64</v>
       </c>
       <c r="H20" s="1">
-        <v>1.429</v>
+        <v>1.52</v>
       </c>
       <c r="I20" s="1">
-        <v>42.87</v>
+        <v>45.6</v>
       </c>
       <c r="J20" s="1">
         <v>1.56</v>
@@ -1764,10 +1764,10 @@
         <v>64</v>
       </c>
       <c r="H21" s="1">
-        <v>1.449</v>
+        <v>1.53</v>
       </c>
       <c r="I21" s="1">
-        <v>31.878</v>
+        <v>33.66</v>
       </c>
       <c r="J21" s="1">
         <v>1.57</v>
@@ -1808,10 +1808,10 @@
         <v>64</v>
       </c>
       <c r="H22" s="1">
-        <v>1.449</v>
+        <v>1.54</v>
       </c>
       <c r="I22" s="1">
-        <v>53.41</v>
+        <v>56.764</v>
       </c>
       <c r="J22" s="1">
         <v>1.58</v>
@@ -1852,10 +1852,10 @@
         <v>64</v>
       </c>
       <c r="H23" s="1">
-        <v>1.709</v>
+        <v>1.79</v>
       </c>
       <c r="I23" s="1">
-        <v>83.331</v>
+        <v>87.28</v>
       </c>
       <c r="J23" s="1">
         <v>1.83</v>
@@ -1896,10 +1896,10 @@
         <v>64</v>
       </c>
       <c r="H24" s="1">
-        <v>1.449</v>
+        <v>1.54</v>
       </c>
       <c r="I24" s="1">
-        <v>12.766</v>
+        <v>13.567</v>
       </c>
       <c r="J24" s="1">
         <v>1.58</v>
@@ -1940,10 +1940,10 @@
         <v>64</v>
       </c>
       <c r="H25" s="1">
-        <v>1.709</v>
+        <v>1.79</v>
       </c>
       <c r="I25" s="1">
-        <v>76.58</v>
+        <v>80.20999999999999</v>
       </c>
       <c r="J25" s="1">
         <v>1.83</v>
@@ -1984,10 +1984,10 @@
         <v>64</v>
       </c>
       <c r="H26" s="1">
-        <v>1.449</v>
+        <v>1.56</v>
       </c>
       <c r="I26" s="1">
-        <v>14.519</v>
+        <v>15.631</v>
       </c>
       <c r="J26" s="1">
         <v>1.6</v>
@@ -2028,10 +2028,10 @@
         <v>64</v>
       </c>
       <c r="H27" s="1">
-        <v>1.449</v>
+        <v>1.56</v>
       </c>
       <c r="I27" s="1">
-        <v>15.939</v>
+        <v>17.16</v>
       </c>
       <c r="J27" s="1">
         <v>1.6</v>
@@ -2072,10 +2072,10 @@
         <v>64</v>
       </c>
       <c r="H28" s="1">
-        <v>1.449</v>
+        <v>1.56</v>
       </c>
       <c r="I28" s="1">
-        <v>42.021</v>
+        <v>45.24</v>
       </c>
       <c r="J28" s="1">
         <v>1.6</v>
@@ -2116,10 +2116,10 @@
         <v>64</v>
       </c>
       <c r="H29" s="1">
-        <v>1.709</v>
+        <v>1.78</v>
       </c>
       <c r="I29" s="1">
-        <v>63.233</v>
+        <v>65.86</v>
       </c>
       <c r="J29" s="1">
         <v>1.82</v>
@@ -2160,10 +2160,10 @@
         <v>64</v>
       </c>
       <c r="H30" s="1">
-        <v>1.709</v>
+        <v>1.78</v>
       </c>
       <c r="I30" s="1">
-        <v>17.09</v>
+        <v>17.8</v>
       </c>
       <c r="J30" s="1">
         <v>1.82</v>
@@ -2204,10 +2204,10 @@
         <v>64</v>
       </c>
       <c r="H31" s="1">
-        <v>1.449</v>
+        <v>1.56</v>
       </c>
       <c r="I31" s="1">
-        <v>44.919</v>
+        <v>48.36</v>
       </c>
       <c r="J31" s="1">
         <v>1.6</v>
@@ -2248,10 +2248,10 @@
         <v>64</v>
       </c>
       <c r="H32" s="1">
-        <v>1.709</v>
+        <v>1.78</v>
       </c>
       <c r="I32" s="1">
-        <v>47.869</v>
+        <v>49.858</v>
       </c>
       <c r="J32" s="1">
         <v>1.82</v>
@@ -2292,10 +2292,10 @@
         <v>64</v>
       </c>
       <c r="H33" s="1">
-        <v>1.679</v>
+        <v>1.81</v>
       </c>
       <c r="I33" s="1">
-        <v>72.197</v>
+        <v>77.83</v>
       </c>
       <c r="J33" s="1">
         <v>1.86</v>
@@ -2336,10 +2336,10 @@
         <v>64</v>
       </c>
       <c r="H34" s="1">
-        <v>1.709</v>
+        <v>1.78</v>
       </c>
       <c r="I34" s="1">
-        <v>28.677</v>
+        <v>29.868</v>
       </c>
       <c r="J34" s="1">
         <v>1.82</v>
@@ -2380,10 +2380,10 @@
         <v>64</v>
       </c>
       <c r="H35" s="1">
-        <v>1.449</v>
+        <v>1.56</v>
       </c>
       <c r="I35" s="1">
-        <v>44.919</v>
+        <v>48.36</v>
       </c>
       <c r="J35" s="1">
         <v>1.6</v>
@@ -2424,10 +2424,10 @@
         <v>64</v>
       </c>
       <c r="H36" s="1">
-        <v>1.709</v>
+        <v>1.78</v>
       </c>
       <c r="I36" s="1">
-        <v>105.958</v>
+        <v>110.36</v>
       </c>
       <c r="J36" s="1">
         <v>1.82</v>
@@ -2468,10 +2468,10 @@
         <v>64</v>
       </c>
       <c r="H37" s="1">
-        <v>1.709</v>
+        <v>1.78</v>
       </c>
       <c r="I37" s="1">
-        <v>59.815</v>
+        <v>62.3</v>
       </c>
       <c r="J37" s="1">
         <v>1.82</v>
@@ -2530,10 +2530,10 @@
         <v>17</v>
       </c>
       <c r="D42" s="8">
-        <v>1.68013</v>
+        <v>1.76786</v>
       </c>
       <c r="E42" s="6">
-        <v>1162.09</v>
+        <v>1222.78</v>
       </c>
       <c r="F42" s="6">
         <v>1250.44</v>
@@ -2550,10 +2550,10 @@
         <v>16</v>
       </c>
       <c r="D43" s="8">
-        <v>1.4312</v>
+        <v>1.52881</v>
       </c>
       <c r="E43" s="6">
-        <v>558.4299999999999</v>
+        <v>596.51</v>
       </c>
       <c r="F43" s="6">
         <v>612.12</v>
@@ -2570,10 +2570,10 @@
         <v>3</v>
       </c>
       <c r="D44" s="8">
-        <v>1.65504</v>
+        <v>1.78164</v>
       </c>
       <c r="E44" s="6">
-        <v>192</v>
+        <v>206.69</v>
       </c>
       <c r="F44" s="6">
         <v>212.49</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="D45" s="8"/>
       <c r="E45" s="10">
-        <v>1912.52</v>
+        <v>2025.98</v>
       </c>
       <c r="F45" s="10">
         <v>2075.05</v>
